--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119816681</v>
+        <v>119811966</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,47 +3172,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489415</v>
+        <v>489533</v>
       </c>
       <c r="R24" t="n">
-        <v>6949931</v>
+        <v>6950117</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3281,10 +3272,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119811966</v>
+        <v>119816681</v>
       </c>
       <c r="B25" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3293,38 +3284,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489533</v>
+        <v>489415</v>
       </c>
       <c r="R25" t="n">
-        <v>6950117</v>
+        <v>6949931</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119811101</v>
+        <v>119816455</v>
       </c>
       <c r="B26" t="n">
-        <v>57326</v>
+        <v>56522</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,43 +3405,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489639</v>
+        <v>489402</v>
       </c>
       <c r="R26" t="n">
-        <v>6950268</v>
+        <v>6949888</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119816455</v>
+        <v>119811101</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>57326</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,43 +3522,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489402</v>
+        <v>489639</v>
       </c>
       <c r="R27" t="n">
-        <v>6949888</v>
+        <v>6950268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119849865</v>
+        <v>119848733</v>
       </c>
       <c r="B69" t="n">
-        <v>57679</v>
+        <v>90580</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8354,55 +8354,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489413</v>
+        <v>489600</v>
       </c>
       <c r="R69" t="n">
-        <v>6949801</v>
+        <v>6949713</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8431,7 +8417,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8441,12 +8427,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8473,10 +8454,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119848733</v>
+        <v>119848818</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8489,21 +8470,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8513,10 +8494,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489600</v>
+        <v>489593</v>
       </c>
       <c r="R70" t="n">
-        <v>6949713</v>
+        <v>6949732</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8548,7 +8529,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8558,7 +8539,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8585,10 +8566,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119848818</v>
+        <v>119849865</v>
       </c>
       <c r="B71" t="n">
-        <v>90576</v>
+        <v>57679</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8597,41 +8578,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489593</v>
+        <v>489413</v>
       </c>
       <c r="R71" t="n">
-        <v>6949732</v>
+        <v>6949801</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8660,7 +8655,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8670,7 +8665,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8697,10 +8697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851683</v>
+        <v>119851248</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8713,21 +8713,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489314</v>
+        <v>489366</v>
       </c>
       <c r="R72" t="n">
-        <v>6950058</v>
+        <v>6949996</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8809,10 +8809,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851248</v>
+        <v>119851683</v>
       </c>
       <c r="B73" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489366</v>
+        <v>489314</v>
       </c>
       <c r="R73" t="n">
-        <v>6949996</v>
+        <v>6950058</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119811561</v>
+        <v>119815859</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6870,21 +6870,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6894,13 +6894,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489625</v>
+        <v>489648</v>
       </c>
       <c r="R56" t="n">
-        <v>6950089</v>
+        <v>6949845</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6954,22 +6954,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119815859</v>
+        <v>119811561</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6982,21 +6982,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7006,13 +7006,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489648</v>
+        <v>489625</v>
       </c>
       <c r="R57" t="n">
-        <v>6949845</v>
+        <v>6950089</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7066,12 +7066,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,7 +1556,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119811038</v>
+        <v>119816509</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1589,20 +1589,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489668</v>
+        <v>489392</v>
       </c>
       <c r="R10" t="n">
-        <v>6950267</v>
+        <v>6949873</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,22 +1665,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815902</v>
+        <v>119815905</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,50 +1689,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489634</v>
+        <v>489652</v>
       </c>
       <c r="R11" t="n">
-        <v>6949843</v>
+        <v>6949845</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119811058</v>
+        <v>119815546</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,50 +1801,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489643</v>
+        <v>489670</v>
       </c>
       <c r="R12" t="n">
-        <v>6950272</v>
+        <v>6949842</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,22 +1889,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119816869</v>
+        <v>119819067</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,41 +1913,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489386</v>
+        <v>489590</v>
       </c>
       <c r="R13" t="n">
-        <v>6950031</v>
+        <v>6949764</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,22 +2001,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119811346</v>
+        <v>119815992</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,41 +2025,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489623</v>
+        <v>489517</v>
       </c>
       <c r="R14" t="n">
-        <v>6950102</v>
+        <v>6949756</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,22 +2122,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816490</v>
+        <v>119811826</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,38 +2146,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489416</v>
+        <v>489523</v>
       </c>
       <c r="R15" t="n">
-        <v>6949992</v>
+        <v>6950130</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,22 +2243,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816272</v>
+        <v>119816951</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,38 +2267,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489537</v>
+        <v>489386</v>
       </c>
       <c r="R16" t="n">
-        <v>6949917</v>
+        <v>6950031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119812008</v>
+        <v>119816543</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,47 +2388,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489528</v>
+        <v>489416</v>
       </c>
       <c r="R17" t="n">
-        <v>6950124</v>
+        <v>6949992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,22 +2476,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816697</v>
+        <v>119812085</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,34 +2504,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489413</v>
+        <v>489559</v>
       </c>
       <c r="R18" t="n">
-        <v>6949932</v>
+        <v>6950125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819067</v>
+        <v>119811101</v>
       </c>
       <c r="B19" t="n">
-        <v>74638</v>
+        <v>57326</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,37 +2616,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489590</v>
+        <v>489639</v>
       </c>
       <c r="R19" t="n">
-        <v>6949764</v>
+        <v>6950268</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,7 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119812085</v>
+        <v>119816455</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>56522</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2715,38 +2729,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489559</v>
+        <v>489402</v>
       </c>
       <c r="R20" t="n">
-        <v>6950125</v>
+        <v>6949888</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2834,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816509</v>
+        <v>119815902</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2850,7 +2869,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2860,17 +2879,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489392</v>
+        <v>489634</v>
       </c>
       <c r="R21" t="n">
-        <v>6949873</v>
+        <v>6949843</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2899,7 +2918,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2928,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,22 +2943,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816293</v>
+        <v>119816718</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2952,21 +2971,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2976,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489470</v>
+        <v>489390</v>
       </c>
       <c r="R22" t="n">
-        <v>6949911</v>
+        <v>6949929</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3011,7 +3030,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3040,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,10 +3067,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815546</v>
+        <v>119815982</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,41 +3079,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489670</v>
+        <v>489561</v>
       </c>
       <c r="R23" t="n">
-        <v>6949842</v>
+        <v>6949786</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3123,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3133,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,12 +3176,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3272,10 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816681</v>
+        <v>119811204</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3284,47 +3312,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489415</v>
+        <v>489659</v>
       </c>
       <c r="R25" t="n">
-        <v>6949931</v>
+        <v>6950266</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3356,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,22 +3400,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119816455</v>
+        <v>119811058</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,43 +3424,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489402</v>
+        <v>489643</v>
       </c>
       <c r="R26" t="n">
-        <v>6949888</v>
+        <v>6950272</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,10 +3533,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119811101</v>
+        <v>119816403</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,42 +3549,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489639</v>
+        <v>489456</v>
       </c>
       <c r="R27" t="n">
-        <v>6950268</v>
+        <v>6949922</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3600,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,22 +3633,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119816425</v>
+        <v>119811103</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3639,50 +3657,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489432</v>
+        <v>489639</v>
       </c>
       <c r="R28" t="n">
-        <v>6949876</v>
+        <v>6950275</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3711,7 +3720,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3721,7 +3730,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3736,22 +3745,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119816566</v>
+        <v>119816291</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,47 +3769,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489390</v>
+        <v>489475</v>
       </c>
       <c r="R29" t="n">
-        <v>6949914</v>
+        <v>6949863</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119815905</v>
+        <v>119815720</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489652</v>
+        <v>489670</v>
       </c>
       <c r="R30" t="n">
-        <v>6949845</v>
+        <v>6949846</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,22 +3969,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119816409</v>
+        <v>119811924</v>
       </c>
       <c r="B31" t="n">
-        <v>74638</v>
+        <v>57463</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,37 +3997,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489456</v>
+        <v>489533</v>
       </c>
       <c r="R31" t="n">
-        <v>6949922</v>
+        <v>6950132</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4056,7 +4061,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4066,7 +4071,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4081,22 +4086,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119816403</v>
+        <v>119816571</v>
       </c>
       <c r="B32" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4109,21 +4114,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4133,13 +4138,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489456</v>
+        <v>489386</v>
       </c>
       <c r="R32" t="n">
-        <v>6949922</v>
+        <v>6950002</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4168,7 +4173,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +4183,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4193,22 +4198,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119811768</v>
+        <v>119816697</v>
       </c>
       <c r="B33" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4221,37 +4226,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489601</v>
+        <v>489413</v>
       </c>
       <c r="R33" t="n">
-        <v>6950078</v>
+        <v>6949932</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4280,7 +4285,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4290,7 +4295,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4305,22 +4310,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119817871</v>
+        <v>119817114</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4329,38 +4334,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489587</v>
+        <v>489487</v>
       </c>
       <c r="R34" t="n">
-        <v>6949781</v>
+        <v>6949865</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4429,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119810849</v>
+        <v>119811422</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4441,47 +4455,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489644</v>
+        <v>489633</v>
       </c>
       <c r="R35" t="n">
-        <v>6950252</v>
+        <v>6950101</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4513,7 +4518,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4523,7 +4528,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4550,10 +4555,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119812494</v>
+        <v>119811398</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4562,46 +4567,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489516</v>
+        <v>489626</v>
       </c>
       <c r="R36" t="n">
-        <v>6950124</v>
+        <v>6950077</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4630,7 +4639,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4640,7 +4649,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4655,22 +4664,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119811022</v>
+        <v>119816597</v>
       </c>
       <c r="B37" t="n">
-        <v>95455</v>
+        <v>96862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,41 +4688,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489658</v>
+        <v>489387</v>
       </c>
       <c r="R37" t="n">
-        <v>6950262</v>
+        <v>6949914</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4742,7 +4751,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4752,7 +4761,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4767,22 +4776,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119811103</v>
+        <v>119811038</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4791,25 +4800,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4819,13 +4828,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489639</v>
+        <v>489668</v>
       </c>
       <c r="R38" t="n">
-        <v>6950275</v>
+        <v>6950267</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4854,7 +4863,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4864,7 +4873,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4879,19 +4888,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819157</v>
+        <v>119816293</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4927,17 +4936,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489563</v>
+        <v>489470</v>
       </c>
       <c r="R39" t="n">
-        <v>6949770</v>
+        <v>6949911</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4966,7 +4975,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4976,7 +4985,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4991,22 +5000,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119816571</v>
+        <v>119816409</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5019,21 +5028,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5043,13 +5052,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489386</v>
+        <v>489456</v>
       </c>
       <c r="R40" t="n">
-        <v>6950002</v>
+        <v>6949922</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5078,7 +5087,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5088,7 +5097,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5103,22 +5112,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119813023</v>
+        <v>119811744</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5131,34 +5140,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489483</v>
+        <v>489626</v>
       </c>
       <c r="R41" t="n">
-        <v>6950017</v>
+        <v>6950077</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5190,7 +5204,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5200,7 +5214,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5215,22 +5229,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119816036</v>
+        <v>119817871</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,47 +5253,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489554</v>
+        <v>489587</v>
       </c>
       <c r="R42" t="n">
-        <v>6949859</v>
+        <v>6949781</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5348,10 +5353,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119816402</v>
+        <v>119812494</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5360,50 +5365,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489410</v>
+        <v>489516</v>
       </c>
       <c r="R43" t="n">
-        <v>6949906</v>
+        <v>6950124</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5432,7 +5433,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5442,7 +5443,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5457,22 +5458,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119811924</v>
+        <v>119810875</v>
       </c>
       <c r="B44" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,31 +5482,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5514,10 +5519,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489533</v>
+        <v>489650</v>
       </c>
       <c r="R44" t="n">
-        <v>6950132</v>
+        <v>6950248</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5586,10 +5591,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119811823</v>
+        <v>119811596</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5598,38 +5603,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489565</v>
+        <v>489598</v>
       </c>
       <c r="R45" t="n">
-        <v>6950090</v>
+        <v>6950085</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5661,7 +5675,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5671,7 +5685,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5698,10 +5712,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811204</v>
+        <v>119816036</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5710,38 +5724,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489659</v>
+        <v>489554</v>
       </c>
       <c r="R46" t="n">
-        <v>6950266</v>
+        <v>6949859</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5773,7 +5796,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5783,7 +5806,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5798,22 +5821,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119812106</v>
+        <v>119816681</v>
       </c>
       <c r="B47" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5822,41 +5845,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489537</v>
+        <v>489415</v>
       </c>
       <c r="R47" t="n">
-        <v>6950131</v>
+        <v>6949931</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5885,7 +5917,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5895,7 +5927,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5910,22 +5942,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119818590</v>
+        <v>119812106</v>
       </c>
       <c r="B48" t="n">
-        <v>79635</v>
+        <v>90846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5934,41 +5966,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489596</v>
+        <v>489537</v>
       </c>
       <c r="R48" t="n">
-        <v>6949748</v>
+        <v>6950131</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5997,7 +6029,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6039,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6022,22 +6054,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816597</v>
+        <v>119815859</v>
       </c>
       <c r="B49" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,38 +6078,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489387</v>
+        <v>489648</v>
       </c>
       <c r="R49" t="n">
-        <v>6949914</v>
+        <v>6949845</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6109,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6119,7 +6151,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6134,22 +6166,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810875</v>
+        <v>119819157</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6158,47 +6190,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489650</v>
+        <v>489563</v>
       </c>
       <c r="R50" t="n">
-        <v>6950248</v>
+        <v>6949770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6230,7 +6253,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6240,7 +6263,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6267,10 +6290,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119815992</v>
+        <v>119816272</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6279,47 +6302,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489517</v>
+        <v>489537</v>
       </c>
       <c r="R51" t="n">
-        <v>6949756</v>
+        <v>6949917</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6351,7 +6365,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6361,7 +6375,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,22 +6390,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119811422</v>
+        <v>119811561</v>
       </c>
       <c r="B52" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6404,21 +6418,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6428,10 +6442,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489633</v>
+        <v>489625</v>
       </c>
       <c r="R52" t="n">
-        <v>6950101</v>
+        <v>6950089</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6463,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6473,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6500,10 +6514,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119813032</v>
+        <v>119818590</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>79635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6512,41 +6526,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489482</v>
+        <v>489596</v>
       </c>
       <c r="R53" t="n">
-        <v>6950030</v>
+        <v>6949748</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6575,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6585,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,19 +6614,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119817114</v>
+        <v>119812008</v>
       </c>
       <c r="B54" t="n">
         <v>97907</v>
@@ -6647,7 +6661,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6657,14 +6671,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489487</v>
+        <v>489528</v>
       </c>
       <c r="R54" t="n">
-        <v>6949865</v>
+        <v>6950124</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6733,10 +6747,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119811398</v>
+        <v>119811022</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,50 +6759,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489626</v>
+        <v>489658</v>
       </c>
       <c r="R55" t="n">
-        <v>6950077</v>
+        <v>6950262</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6817,7 +6822,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6827,7 +6832,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6842,22 +6847,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119815859</v>
+        <v>119810849</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6866,41 +6871,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489648</v>
+        <v>489644</v>
       </c>
       <c r="R56" t="n">
-        <v>6949845</v>
+        <v>6950252</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6929,7 +6943,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6939,7 +6953,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6954,22 +6968,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119811561</v>
+        <v>119816425</v>
       </c>
       <c r="B57" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6978,41 +6992,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489625</v>
+        <v>489432</v>
       </c>
       <c r="R57" t="n">
-        <v>6950089</v>
+        <v>6949876</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7041,7 +7064,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7051,7 +7074,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7066,22 +7089,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119815720</v>
+        <v>119816566</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7090,38 +7113,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489670</v>
+        <v>489390</v>
       </c>
       <c r="R58" t="n">
-        <v>6949846</v>
+        <v>6949914</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7190,10 +7222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119817062</v>
+        <v>119813032</v>
       </c>
       <c r="B59" t="n">
-        <v>79144</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7206,21 +7238,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7230,13 +7262,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489451</v>
+        <v>489482</v>
       </c>
       <c r="R59" t="n">
-        <v>6949854</v>
+        <v>6950030</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7265,7 +7297,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7275,7 +7307,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7290,22 +7322,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811826</v>
+        <v>119811823</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7314,50 +7346,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489523</v>
+        <v>489565</v>
       </c>
       <c r="R60" t="n">
-        <v>6950130</v>
+        <v>6950090</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7386,7 +7409,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7396,7 +7419,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7411,22 +7434,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119815982</v>
+        <v>119811768</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7435,50 +7458,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489561</v>
+        <v>489601</v>
       </c>
       <c r="R61" t="n">
-        <v>6949786</v>
+        <v>6950078</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7507,7 +7521,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7517,7 +7531,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,22 +7546,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119811744</v>
+        <v>119816157</v>
       </c>
       <c r="B62" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7556,43 +7570,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489626</v>
+        <v>489537</v>
       </c>
       <c r="R62" t="n">
-        <v>6950077</v>
+        <v>6949917</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7624,7 +7633,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7634,7 +7643,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7649,22 +7658,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119816291</v>
+        <v>119817062</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7677,21 +7686,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7701,10 +7710,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489475</v>
+        <v>489451</v>
       </c>
       <c r="R63" t="n">
-        <v>6949863</v>
+        <v>6949854</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7773,10 +7782,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119811596</v>
+        <v>119813023</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7785,50 +7794,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489598</v>
+        <v>489483</v>
       </c>
       <c r="R64" t="n">
-        <v>6950085</v>
+        <v>6950017</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,22 +7882,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119816718</v>
+        <v>119816402</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7906,41 +7906,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489390</v>
+        <v>489410</v>
       </c>
       <c r="R65" t="n">
-        <v>6949929</v>
+        <v>6949906</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7969,7 +7978,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7988,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,22 +8003,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119816157</v>
+        <v>119811346</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8018,25 +8027,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8046,13 +8055,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489537</v>
+        <v>489623</v>
       </c>
       <c r="R66" t="n">
-        <v>6949917</v>
+        <v>6950102</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8081,7 +8090,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +8100,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8106,22 +8115,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849489</v>
+        <v>119848594</v>
       </c>
       <c r="B67" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8134,21 +8143,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8158,10 +8167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489516</v>
+        <v>489615</v>
       </c>
       <c r="R67" t="n">
-        <v>6949768</v>
+        <v>6949709</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8193,7 +8202,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8203,7 +8212,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8230,10 +8239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119850939</v>
+        <v>119851578</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8246,21 +8255,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8270,10 +8279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489367</v>
+        <v>489328</v>
       </c>
       <c r="R68" t="n">
-        <v>6949918</v>
+        <v>6950055</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8305,7 +8314,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8315,7 +8324,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,10 +8463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119848818</v>
+        <v>119850939</v>
       </c>
       <c r="B70" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8470,34 +8479,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489593</v>
+        <v>489367</v>
       </c>
       <c r="R70" t="n">
-        <v>6949732</v>
+        <v>6949918</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8529,7 +8538,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8539,7 +8548,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8566,10 +8575,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119849865</v>
+        <v>119850950</v>
       </c>
       <c r="B71" t="n">
-        <v>57679</v>
+        <v>82305</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8578,55 +8587,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489413</v>
+        <v>489367</v>
       </c>
       <c r="R71" t="n">
-        <v>6949801</v>
+        <v>6949918</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8655,7 +8650,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8665,12 +8660,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8697,10 +8687,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851248</v>
+        <v>119852338</v>
       </c>
       <c r="B72" t="n">
-        <v>82305</v>
+        <v>56522</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8709,41 +8699,60 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489366</v>
+        <v>489485</v>
       </c>
       <c r="R72" t="n">
-        <v>6949996</v>
+        <v>6950055</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8772,7 +8781,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8782,7 +8791,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8809,7 +8818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851683</v>
+        <v>119850649</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8849,10 +8858,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489314</v>
+        <v>489406</v>
       </c>
       <c r="R73" t="n">
-        <v>6950058</v>
+        <v>6949790</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8884,7 +8893,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8894,7 +8903,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8921,7 +8930,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119852547</v>
+        <v>119849062</v>
       </c>
       <c r="B74" t="n">
         <v>74638</v>
@@ -8957,14 +8966,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489584</v>
+        <v>489573</v>
       </c>
       <c r="R74" t="n">
-        <v>6949881</v>
+        <v>6949724</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8996,7 +9005,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9006,7 +9015,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9033,7 +9042,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849062</v>
+        <v>119852547</v>
       </c>
       <c r="B75" t="n">
         <v>74638</v>
@@ -9069,14 +9078,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489573</v>
+        <v>489584</v>
       </c>
       <c r="R75" t="n">
-        <v>6949724</v>
+        <v>6949881</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9108,7 +9117,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9118,7 +9127,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9145,10 +9154,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851194</v>
+        <v>119849865</v>
       </c>
       <c r="B76" t="n">
-        <v>82305</v>
+        <v>57679</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9157,41 +9166,55 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489391</v>
+        <v>489413</v>
       </c>
       <c r="R76" t="n">
-        <v>6949965</v>
+        <v>6949801</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9220,7 +9243,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9230,7 +9253,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9257,10 +9285,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119849171</v>
+        <v>119848365</v>
       </c>
       <c r="B77" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9269,25 +9297,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9297,10 +9325,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489554</v>
+        <v>489632</v>
       </c>
       <c r="R77" t="n">
-        <v>6949730</v>
+        <v>6949678</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9332,7 +9360,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9342,7 +9370,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9369,10 +9397,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119848688</v>
+        <v>119848818</v>
       </c>
       <c r="B78" t="n">
-        <v>74638</v>
+        <v>90576</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9385,21 +9413,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9409,10 +9437,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489614</v>
+        <v>489593</v>
       </c>
       <c r="R78" t="n">
-        <v>6949692</v>
+        <v>6949732</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9444,7 +9472,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9454,7 +9482,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9481,10 +9509,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119852338</v>
+        <v>119849171</v>
       </c>
       <c r="B79" t="n">
-        <v>56522</v>
+        <v>79643</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9497,56 +9525,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489485</v>
+        <v>489554</v>
       </c>
       <c r="R79" t="n">
-        <v>6950055</v>
+        <v>6949730</v>
       </c>
       <c r="S79" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9575,7 +9584,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9585,7 +9594,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9612,10 +9621,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119848594</v>
+        <v>119851248</v>
       </c>
       <c r="B80" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9628,34 +9637,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489615</v>
+        <v>489366</v>
       </c>
       <c r="R80" t="n">
-        <v>6949709</v>
+        <v>6949996</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9687,7 +9696,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9697,7 +9706,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9836,10 +9845,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850950</v>
+        <v>119848688</v>
       </c>
       <c r="B82" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9852,34 +9861,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489367</v>
+        <v>489614</v>
       </c>
       <c r="R82" t="n">
-        <v>6949918</v>
+        <v>6949692</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9911,7 +9920,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9921,7 +9930,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9948,10 +9957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851578</v>
+        <v>119851683</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9964,21 +9973,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9988,10 +9997,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489328</v>
+        <v>489314</v>
       </c>
       <c r="R83" t="n">
-        <v>6950055</v>
+        <v>6950058</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -10023,7 +10032,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10033,7 +10042,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10060,10 +10069,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119848365</v>
+        <v>119851194</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10076,34 +10085,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489632</v>
+        <v>489391</v>
       </c>
       <c r="R84" t="n">
-        <v>6949678</v>
+        <v>6949965</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -10135,7 +10144,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10145,7 +10154,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10172,10 +10181,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119850649</v>
+        <v>119849489</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10188,34 +10197,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489406</v>
+        <v>489516</v>
       </c>
       <c r="R85" t="n">
-        <v>6949790</v>
+        <v>6949768</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10247,7 +10256,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10257,7 +10266,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119816509</v>
+        <v>119815905</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,47 +1568,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489392</v>
+        <v>489652</v>
       </c>
       <c r="R10" t="n">
-        <v>6949873</v>
+        <v>6949845</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1640,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815905</v>
+        <v>119816509</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,38 +1680,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489652</v>
+        <v>489392</v>
       </c>
       <c r="R11" t="n">
-        <v>6949845</v>
+        <v>6949873</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4443,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119811422</v>
+        <v>119811398</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,41 +4455,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489633</v>
+        <v>489626</v>
       </c>
       <c r="R35" t="n">
-        <v>6950101</v>
+        <v>6950077</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4518,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4528,7 +4537,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,22 +4552,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119811398</v>
+        <v>119816597</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>96862</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4567,47 +4576,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489626</v>
+        <v>489387</v>
       </c>
       <c r="R36" t="n">
-        <v>6950077</v>
+        <v>6949914</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119816597</v>
+        <v>119811422</v>
       </c>
       <c r="B37" t="n">
-        <v>96862</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4688,41 +4688,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489387</v>
+        <v>489633</v>
       </c>
       <c r="R37" t="n">
-        <v>6949914</v>
+        <v>6950101</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4776,22 +4776,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119811038</v>
+        <v>119816293</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4800,41 +4800,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489668</v>
+        <v>489470</v>
       </c>
       <c r="R38" t="n">
-        <v>6950267</v>
+        <v>6949911</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4888,22 +4888,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119816293</v>
+        <v>119816409</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4916,21 +4916,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489470</v>
+        <v>489456</v>
       </c>
       <c r="R39" t="n">
-        <v>6949911</v>
+        <v>6949922</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +5012,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119816409</v>
+        <v>119811744</v>
       </c>
       <c r="B40" t="n">
-        <v>74638</v>
+        <v>57326</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5028,37 +5028,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489456</v>
+        <v>489626</v>
       </c>
       <c r="R40" t="n">
-        <v>6949922</v>
+        <v>6950077</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5087,7 +5092,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5097,7 +5102,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5112,22 +5117,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119811744</v>
+        <v>119811038</v>
       </c>
       <c r="B41" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5136,43 +5141,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489626</v>
+        <v>489668</v>
       </c>
       <c r="R41" t="n">
-        <v>6950077</v>
+        <v>6950267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,12 +5229,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119811561</v>
+        <v>119811022</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>95455</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6418,34 +6418,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489625</v>
+        <v>489658</v>
       </c>
       <c r="R52" t="n">
-        <v>6950089</v>
+        <v>6950262</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119812008</v>
+        <v>119811561</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6638,50 +6638,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489528</v>
+        <v>489625</v>
       </c>
       <c r="R54" t="n">
-        <v>6950124</v>
+        <v>6950089</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6710,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6720,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6735,22 +6726,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119811022</v>
+        <v>119812008</v>
       </c>
       <c r="B55" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6759,41 +6750,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489658</v>
+        <v>489528</v>
       </c>
       <c r="R55" t="n">
-        <v>6950262</v>
+        <v>6950124</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6847,12 +6847,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6980,10 +6980,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119816425</v>
+        <v>119813032</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6992,50 +6992,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489432</v>
+        <v>489482</v>
       </c>
       <c r="R57" t="n">
-        <v>6949876</v>
+        <v>6950030</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7064,7 +7055,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7074,7 +7065,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7089,22 +7080,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119816566</v>
+        <v>119811823</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7113,50 +7104,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489390</v>
+        <v>489565</v>
       </c>
       <c r="R58" t="n">
-        <v>6949914</v>
+        <v>6950090</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7185,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7195,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7210,22 +7192,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119813032</v>
+        <v>119816425</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7234,41 +7216,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489482</v>
+        <v>489432</v>
       </c>
       <c r="R59" t="n">
-        <v>6950030</v>
+        <v>6949876</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7297,7 +7288,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7307,7 +7298,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7322,22 +7313,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811823</v>
+        <v>119816566</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7346,41 +7337,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489565</v>
+        <v>489390</v>
       </c>
       <c r="R60" t="n">
-        <v>6950090</v>
+        <v>6949914</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7434,22 +7434,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119811768</v>
+        <v>119811346</v>
       </c>
       <c r="B61" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7462,21 +7462,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489601</v>
+        <v>489623</v>
       </c>
       <c r="R61" t="n">
-        <v>6950078</v>
+        <v>6950102</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7670,10 +7670,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119817062</v>
+        <v>119813023</v>
       </c>
       <c r="B63" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489451</v>
+        <v>489483</v>
       </c>
       <c r="R63" t="n">
-        <v>6949854</v>
+        <v>6950017</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7770,22 +7770,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119813023</v>
+        <v>119816402</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7794,38 +7794,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489483</v>
+        <v>489410</v>
       </c>
       <c r="R64" t="n">
-        <v>6950017</v>
+        <v>6949906</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7857,7 +7866,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7867,7 +7876,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,22 +7891,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119816402</v>
+        <v>119811768</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7906,50 +7915,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489410</v>
+        <v>489601</v>
       </c>
       <c r="R65" t="n">
-        <v>6949906</v>
+        <v>6950078</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8003,22 +8003,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119811346</v>
+        <v>119817062</v>
       </c>
       <c r="B66" t="n">
-        <v>90562</v>
+        <v>79144</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8031,37 +8031,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489623</v>
+        <v>489451</v>
       </c>
       <c r="R66" t="n">
-        <v>6950102</v>
+        <v>6949854</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8115,12 +8115,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8687,10 +8687,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119852338</v>
+        <v>119850649</v>
       </c>
       <c r="B72" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8699,60 +8699,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489485</v>
+        <v>489406</v>
       </c>
       <c r="R72" t="n">
-        <v>6950055</v>
+        <v>6949790</v>
       </c>
       <c r="S72" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8781,7 +8762,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8791,7 +8772,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8818,10 +8799,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850649</v>
+        <v>119852338</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8830,41 +8811,60 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489406</v>
+        <v>489485</v>
       </c>
       <c r="R73" t="n">
-        <v>6949790</v>
+        <v>6950055</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815905</v>
+        <v>119816455</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>56522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,37 +1572,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489652</v>
+        <v>489402</v>
       </c>
       <c r="R10" t="n">
-        <v>6949845</v>
+        <v>6949888</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,22 +1661,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816509</v>
+        <v>119813023</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,50 +1685,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489392</v>
+        <v>489483</v>
       </c>
       <c r="R11" t="n">
-        <v>6949873</v>
+        <v>6950017</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,22 +1773,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119815546</v>
+        <v>119811768</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>95455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489670</v>
+        <v>489601</v>
       </c>
       <c r="R12" t="n">
-        <v>6949842</v>
+        <v>6950078</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819067</v>
+        <v>119811924</v>
       </c>
       <c r="B13" t="n">
-        <v>74638</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489590</v>
+        <v>489533</v>
       </c>
       <c r="R13" t="n">
-        <v>6949764</v>
+        <v>6950132</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,22 +2002,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119815992</v>
+        <v>119816718</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,50 +2026,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489517</v>
+        <v>489390</v>
       </c>
       <c r="R14" t="n">
-        <v>6949756</v>
+        <v>6949929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,19 +2114,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119811826</v>
+        <v>119811398</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2169,7 +2161,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2179,14 +2171,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489523</v>
+        <v>489626</v>
       </c>
       <c r="R15" t="n">
-        <v>6950130</v>
+        <v>6950077</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816951</v>
+        <v>119816697</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,47 +2259,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489386</v>
+        <v>489413</v>
       </c>
       <c r="R16" t="n">
-        <v>6950031</v>
+        <v>6949932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,22 +2347,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119816543</v>
+        <v>119811422</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,37 +2375,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489416</v>
+        <v>489633</v>
       </c>
       <c r="R17" t="n">
-        <v>6949992</v>
+        <v>6950101</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2459,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119812085</v>
+        <v>119816597</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>96862</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,38 +2483,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489559</v>
+        <v>489387</v>
       </c>
       <c r="R18" t="n">
-        <v>6950125</v>
+        <v>6949914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2717,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816455</v>
+        <v>119812085</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,43 +2712,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489402</v>
+        <v>489559</v>
       </c>
       <c r="R20" t="n">
-        <v>6949888</v>
+        <v>6950125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119815902</v>
+        <v>119816490</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,47 +2824,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489634</v>
+        <v>489416</v>
       </c>
       <c r="R21" t="n">
-        <v>6949843</v>
+        <v>6949992</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2928,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,22 +2912,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816718</v>
+        <v>119816272</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,37 +2940,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489390</v>
+        <v>489537</v>
       </c>
       <c r="R22" t="n">
-        <v>6949929</v>
+        <v>6949917</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3030,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3040,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,22 +3024,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815982</v>
+        <v>119817871</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,47 +3048,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489561</v>
+        <v>489587</v>
       </c>
       <c r="R23" t="n">
-        <v>6949786</v>
+        <v>6949781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119811966</v>
+        <v>119812494</v>
       </c>
       <c r="B24" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,37 +3164,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489533</v>
+        <v>489516</v>
       </c>
       <c r="R24" t="n">
-        <v>6950117</v>
+        <v>6950124</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3263,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,22 +3253,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119811204</v>
+        <v>119812008</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3312,38 +3277,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489659</v>
+        <v>489528</v>
       </c>
       <c r="R25" t="n">
-        <v>6950266</v>
+        <v>6950124</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3349,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3359,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,22 +3374,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119811058</v>
+        <v>119816291</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,47 +3398,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489643</v>
+        <v>489475</v>
       </c>
       <c r="R26" t="n">
-        <v>6950272</v>
+        <v>6949863</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3533,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119816403</v>
+        <v>119815992</v>
       </c>
       <c r="B27" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3545,41 +3510,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489456</v>
+        <v>489517</v>
       </c>
       <c r="R27" t="n">
-        <v>6949922</v>
+        <v>6949756</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3608,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3633,22 +3607,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119811103</v>
+        <v>119811058</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3657,41 +3631,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489639</v>
+        <v>489643</v>
       </c>
       <c r="R28" t="n">
-        <v>6950275</v>
+        <v>6950272</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,7 +3703,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3730,7 +3713,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3745,22 +3728,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119816291</v>
+        <v>119816409</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,21 +3756,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3797,13 +3780,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489475</v>
+        <v>489456</v>
       </c>
       <c r="R29" t="n">
-        <v>6949863</v>
+        <v>6949922</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3832,7 +3815,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3842,7 +3825,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3857,22 +3840,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119815720</v>
+        <v>119811596</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3881,41 +3864,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489670</v>
+        <v>489598</v>
       </c>
       <c r="R30" t="n">
-        <v>6949846</v>
+        <v>6950085</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3944,7 +3936,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3954,7 +3946,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,22 +3961,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119811924</v>
+        <v>119811204</v>
       </c>
       <c r="B31" t="n">
-        <v>57463</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3997,39 +3989,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489533</v>
+        <v>489659</v>
       </c>
       <c r="R31" t="n">
-        <v>6950132</v>
+        <v>6950266</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4061,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4071,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4086,22 +4073,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119816571</v>
+        <v>119816157</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4110,38 +4097,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489386</v>
+        <v>489537</v>
       </c>
       <c r="R32" t="n">
-        <v>6950002</v>
+        <v>6949917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4173,7 +4160,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4183,7 +4170,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,10 +4197,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119816697</v>
+        <v>119816566</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,38 +4209,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489413</v>
+        <v>489390</v>
       </c>
       <c r="R33" t="n">
-        <v>6949932</v>
+        <v>6949914</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4322,10 +4318,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119817114</v>
+        <v>119811022</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4334,50 +4330,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489487</v>
+        <v>489658</v>
       </c>
       <c r="R34" t="n">
-        <v>6949865</v>
+        <v>6950262</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4406,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4416,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4431,19 +4418,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119811398</v>
+        <v>119810875</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4478,7 +4465,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4488,14 +4475,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489626</v>
+        <v>489650</v>
       </c>
       <c r="R35" t="n">
-        <v>6950077</v>
+        <v>6950248</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4564,10 +4551,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119816597</v>
+        <v>119816869</v>
       </c>
       <c r="B36" t="n">
-        <v>96862</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4576,25 +4563,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4604,10 +4591,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489387</v>
+        <v>489386</v>
       </c>
       <c r="R36" t="n">
-        <v>6949914</v>
+        <v>6950031</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4639,7 +4626,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4649,7 +4636,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4664,22 +4651,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119811422</v>
+        <v>119811966</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>95455</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4692,37 +4679,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489633</v>
+        <v>489533</v>
       </c>
       <c r="R37" t="n">
-        <v>6950101</v>
+        <v>6950117</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4751,7 +4738,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4761,7 +4748,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4776,22 +4763,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119816293</v>
+        <v>119818590</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4800,41 +4787,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489470</v>
+        <v>489596</v>
       </c>
       <c r="R38" t="n">
-        <v>6949911</v>
+        <v>6949748</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4863,7 +4850,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4873,7 +4860,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4888,19 +4875,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119816409</v>
+        <v>119819067</v>
       </c>
       <c r="B39" t="n">
         <v>74638</v>
@@ -4936,14 +4923,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489456</v>
+        <v>489590</v>
       </c>
       <c r="R39" t="n">
-        <v>6949922</v>
+        <v>6949764</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4975,7 +4962,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4985,7 +4972,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5012,10 +4999,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119811744</v>
+        <v>119815546</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5028,42 +5015,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489626</v>
+        <v>489670</v>
       </c>
       <c r="R40" t="n">
-        <v>6950077</v>
+        <v>6949842</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5092,7 +5074,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5102,7 +5084,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5117,22 +5099,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119811038</v>
+        <v>119815720</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5141,38 +5123,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489668</v>
+        <v>489670</v>
       </c>
       <c r="R41" t="n">
-        <v>6950267</v>
+        <v>6949846</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5204,7 +5186,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5214,7 +5196,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,22 +5211,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119817871</v>
+        <v>119811346</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5257,37 +5239,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489587</v>
+        <v>489623</v>
       </c>
       <c r="R42" t="n">
-        <v>6949781</v>
+        <v>6950102</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5316,7 +5298,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5326,7 +5308,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,22 +5323,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119812494</v>
+        <v>119816403</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5369,39 +5351,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489516</v>
+        <v>489456</v>
       </c>
       <c r="R43" t="n">
-        <v>6950124</v>
+        <v>6949922</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5433,7 +5410,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5443,7 +5420,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,7 +5447,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810875</v>
+        <v>119815982</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5505,7 +5482,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5515,14 +5492,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489650</v>
+        <v>489561</v>
       </c>
       <c r="R44" t="n">
-        <v>6950248</v>
+        <v>6949786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5591,7 +5568,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119811596</v>
+        <v>119816681</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5626,7 +5603,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5636,17 +5613,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489598</v>
+        <v>489415</v>
       </c>
       <c r="R45" t="n">
-        <v>6950085</v>
+        <v>6949931</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5675,7 +5652,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5685,7 +5662,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,22 +5677,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119816036</v>
+        <v>119811823</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5724,50 +5701,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489554</v>
+        <v>489565</v>
       </c>
       <c r="R46" t="n">
-        <v>6949859</v>
+        <v>6950090</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5796,7 +5764,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5806,7 +5774,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5821,22 +5789,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119816681</v>
+        <v>119811744</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5845,47 +5813,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489415</v>
+        <v>489626</v>
       </c>
       <c r="R47" t="n">
-        <v>6949931</v>
+        <v>6950077</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5954,10 +5918,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119812106</v>
+        <v>119815902</v>
       </c>
       <c r="B48" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,41 +5930,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489537</v>
+        <v>489634</v>
       </c>
       <c r="R48" t="n">
-        <v>6950131</v>
+        <v>6949843</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6029,7 +6002,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6039,7 +6012,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,22 +6027,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119815859</v>
+        <v>119816425</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6078,38 +6051,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489648</v>
+        <v>489432</v>
       </c>
       <c r="R49" t="n">
-        <v>6949845</v>
+        <v>6949876</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,7 +6123,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,7 +6133,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6166,22 +6148,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119819157</v>
+        <v>119816402</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6190,38 +6172,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489563</v>
+        <v>489410</v>
       </c>
       <c r="R50" t="n">
-        <v>6949770</v>
+        <v>6949906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6253,7 +6244,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6263,7 +6254,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6290,10 +6281,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119816272</v>
+        <v>119811038</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6302,38 +6293,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489537</v>
+        <v>489668</v>
       </c>
       <c r="R51" t="n">
-        <v>6949917</v>
+        <v>6950267</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6365,7 +6356,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6375,7 +6366,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6402,10 +6393,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119811022</v>
+        <v>119816293</v>
       </c>
       <c r="B52" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6418,34 +6409,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489658</v>
+        <v>489470</v>
       </c>
       <c r="R52" t="n">
-        <v>6950262</v>
+        <v>6949911</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6477,7 +6468,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6487,7 +6478,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6514,10 +6505,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119818590</v>
+        <v>119815859</v>
       </c>
       <c r="B53" t="n">
-        <v>79635</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6526,38 +6517,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489596</v>
+        <v>489648</v>
       </c>
       <c r="R53" t="n">
-        <v>6949748</v>
+        <v>6949845</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6589,7 +6580,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6590,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6614,22 +6605,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119811561</v>
+        <v>119817062</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>79144</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6642,37 +6633,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489625</v>
+        <v>489451</v>
       </c>
       <c r="R54" t="n">
-        <v>6950089</v>
+        <v>6949854</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6701,7 +6692,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6711,7 +6702,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6726,19 +6717,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119812008</v>
+        <v>119816036</v>
       </c>
       <c r="B55" t="n">
         <v>97907</v>
@@ -6773,7 +6764,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6783,14 +6774,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489528</v>
+        <v>489554</v>
       </c>
       <c r="R55" t="n">
-        <v>6950124</v>
+        <v>6949859</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6859,10 +6850,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810849</v>
+        <v>119816571</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6871,50 +6862,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489644</v>
+        <v>489386</v>
       </c>
       <c r="R56" t="n">
-        <v>6950252</v>
+        <v>6950002</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6943,7 +6925,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6953,7 +6935,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6968,19 +6950,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119813032</v>
+        <v>119811103</v>
       </c>
       <c r="B57" t="n">
         <v>90562</v>
@@ -7016,14 +6998,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489482</v>
+        <v>489639</v>
       </c>
       <c r="R57" t="n">
-        <v>6950030</v>
+        <v>6950275</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7055,7 +7037,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7065,7 +7047,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7092,10 +7074,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119811823</v>
+        <v>119813032</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,34 +7090,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489565</v>
+        <v>489482</v>
       </c>
       <c r="R58" t="n">
-        <v>6950090</v>
+        <v>6950030</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7167,7 +7149,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7159,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7204,7 +7186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119816425</v>
+        <v>119811826</v>
       </c>
       <c r="B59" t="n">
         <v>97907</v>
@@ -7239,7 +7221,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7249,14 +7231,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489432</v>
+        <v>489523</v>
       </c>
       <c r="R59" t="n">
-        <v>6949876</v>
+        <v>6950130</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7325,10 +7307,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119816566</v>
+        <v>119811561</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7337,50 +7319,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489390</v>
+        <v>489625</v>
       </c>
       <c r="R60" t="n">
-        <v>6949914</v>
+        <v>6950089</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7409,7 +7382,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7419,7 +7392,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7434,22 +7407,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119811346</v>
+        <v>119815905</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7458,25 +7431,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7486,10 +7459,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489623</v>
+        <v>489652</v>
       </c>
       <c r="R61" t="n">
-        <v>6950102</v>
+        <v>6949845</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7521,7 +7494,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7531,7 +7504,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7558,10 +7531,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119816157</v>
+        <v>119817114</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7570,38 +7543,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489537</v>
+        <v>489487</v>
       </c>
       <c r="R62" t="n">
-        <v>6949917</v>
+        <v>6949865</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7633,7 +7615,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7643,7 +7625,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7658,22 +7640,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119813023</v>
+        <v>119816509</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7682,41 +7664,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489483</v>
+        <v>489392</v>
       </c>
       <c r="R63" t="n">
-        <v>6950017</v>
+        <v>6949873</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7745,7 +7736,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7755,7 +7746,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7770,19 +7761,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119816402</v>
+        <v>119810849</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7817,7 +7808,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7827,17 +7818,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489410</v>
+        <v>489644</v>
       </c>
       <c r="R64" t="n">
-        <v>6949906</v>
+        <v>6950252</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7866,7 +7857,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7876,7 +7867,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7891,22 +7882,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119811768</v>
+        <v>119812106</v>
       </c>
       <c r="B65" t="n">
-        <v>95455</v>
+        <v>90846</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7919,34 +7910,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489601</v>
+        <v>489537</v>
       </c>
       <c r="R65" t="n">
-        <v>6950078</v>
+        <v>6950131</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7978,7 +7969,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7988,7 +7979,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8015,10 +8006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119817062</v>
+        <v>119819157</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8031,34 +8022,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489451</v>
+        <v>489563</v>
       </c>
       <c r="R66" t="n">
-        <v>6949854</v>
+        <v>6949770</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8090,7 +8081,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8100,7 +8091,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8127,10 +8118,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119848594</v>
+        <v>119850950</v>
       </c>
       <c r="B67" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8143,34 +8134,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489615</v>
+        <v>489367</v>
       </c>
       <c r="R67" t="n">
-        <v>6949709</v>
+        <v>6949918</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8202,7 +8193,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8212,7 +8203,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8239,10 +8230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851578</v>
+        <v>119848594</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8255,34 +8246,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489328</v>
+        <v>489615</v>
       </c>
       <c r="R68" t="n">
-        <v>6950055</v>
+        <v>6949709</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8314,7 +8305,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8324,7 +8315,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8351,10 +8342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119848733</v>
+        <v>119851248</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8367,34 +8358,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489600</v>
+        <v>489366</v>
       </c>
       <c r="R69" t="n">
-        <v>6949713</v>
+        <v>6949996</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8426,7 +8417,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8436,7 +8427,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8463,10 +8454,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119850939</v>
+        <v>119849062</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8479,34 +8470,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489367</v>
+        <v>489573</v>
       </c>
       <c r="R70" t="n">
-        <v>6949918</v>
+        <v>6949724</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8538,7 +8529,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8548,7 +8539,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8575,10 +8566,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119850950</v>
+        <v>119850649</v>
       </c>
       <c r="B71" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8591,21 +8582,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8615,10 +8606,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489367</v>
+        <v>489406</v>
       </c>
       <c r="R71" t="n">
-        <v>6949918</v>
+        <v>6949790</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8650,7 +8641,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8660,7 +8651,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8687,10 +8678,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850649</v>
+        <v>119848818</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8703,34 +8694,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489406</v>
+        <v>489593</v>
       </c>
       <c r="R72" t="n">
-        <v>6949790</v>
+        <v>6949732</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8762,7 +8753,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8772,7 +8763,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8799,10 +8790,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119852338</v>
+        <v>119851194</v>
       </c>
       <c r="B73" t="n">
-        <v>56522</v>
+        <v>82305</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8811,60 +8802,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489485</v>
+        <v>489391</v>
       </c>
       <c r="R73" t="n">
-        <v>6950055</v>
+        <v>6949965</v>
       </c>
       <c r="S73" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8893,7 +8865,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8903,7 +8875,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8930,10 +8902,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849062</v>
+        <v>119849171</v>
       </c>
       <c r="B74" t="n">
-        <v>74638</v>
+        <v>79643</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8942,25 +8914,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8970,10 +8942,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489573</v>
+        <v>489554</v>
       </c>
       <c r="R74" t="n">
-        <v>6949724</v>
+        <v>6949730</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9005,7 +8977,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9015,7 +8987,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9154,10 +9126,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849865</v>
+        <v>119850939</v>
       </c>
       <c r="B76" t="n">
-        <v>57679</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9166,55 +9138,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489413</v>
+        <v>489367</v>
       </c>
       <c r="R76" t="n">
-        <v>6949801</v>
+        <v>6949918</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9243,7 +9201,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9253,12 +9211,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9285,10 +9238,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119848365</v>
+        <v>119848733</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9301,21 +9254,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9325,10 +9278,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489632</v>
+        <v>489600</v>
       </c>
       <c r="R77" t="n">
-        <v>6949678</v>
+        <v>6949713</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9360,7 +9313,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9370,7 +9323,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9397,10 +9350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119848818</v>
+        <v>119848688</v>
       </c>
       <c r="B78" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9413,21 +9366,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9437,10 +9390,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489593</v>
+        <v>489614</v>
       </c>
       <c r="R78" t="n">
-        <v>6949732</v>
+        <v>6949692</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9472,7 +9425,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9482,7 +9435,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9509,10 +9462,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119849171</v>
+        <v>119848365</v>
       </c>
       <c r="B79" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9521,25 +9474,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9549,10 +9502,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489554</v>
+        <v>489632</v>
       </c>
       <c r="R79" t="n">
-        <v>6949730</v>
+        <v>6949678</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9584,7 +9537,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9594,7 +9547,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9621,10 +9574,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851248</v>
+        <v>119851578</v>
       </c>
       <c r="B80" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9637,21 +9590,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9661,10 +9614,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489366</v>
+        <v>489328</v>
       </c>
       <c r="R80" t="n">
-        <v>6949996</v>
+        <v>6950055</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9696,7 +9649,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9706,7 +9659,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9845,10 +9798,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119848688</v>
+        <v>119849489</v>
       </c>
       <c r="B82" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9861,21 +9814,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9885,10 +9838,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489614</v>
+        <v>489516</v>
       </c>
       <c r="R82" t="n">
-        <v>6949692</v>
+        <v>6949768</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9920,7 +9873,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9930,7 +9883,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9957,10 +9910,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851683</v>
+        <v>119852338</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9969,41 +9922,60 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489314</v>
+        <v>489485</v>
       </c>
       <c r="R83" t="n">
-        <v>6950058</v>
+        <v>6950055</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10032,7 +10004,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10042,7 +10014,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10069,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851194</v>
+        <v>119851683</v>
       </c>
       <c r="B84" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10085,21 +10057,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10109,10 +10081,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489391</v>
+        <v>489314</v>
       </c>
       <c r="R84" t="n">
-        <v>6949965</v>
+        <v>6950058</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -10144,7 +10116,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10154,7 +10126,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10181,10 +10153,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849489</v>
+        <v>119849865</v>
       </c>
       <c r="B85" t="n">
-        <v>82305</v>
+        <v>57679</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10193,41 +10165,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489516</v>
+        <v>489413</v>
       </c>
       <c r="R85" t="n">
-        <v>6949768</v>
+        <v>6949801</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10256,7 +10242,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10266,7 +10252,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119811768</v>
+        <v>119811924</v>
       </c>
       <c r="B12" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,37 +1801,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489601</v>
+        <v>489533</v>
       </c>
       <c r="R12" t="n">
-        <v>6950078</v>
+        <v>6950132</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,22 +1890,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119811924</v>
+        <v>119811398</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,43 +1914,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489533</v>
+        <v>489626</v>
       </c>
       <c r="R13" t="n">
-        <v>6950132</v>
+        <v>6950077</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816718</v>
+        <v>119811768</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>95455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,34 +2039,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489390</v>
+        <v>489601</v>
       </c>
       <c r="R14" t="n">
-        <v>6949929</v>
+        <v>6950078</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2089,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119811398</v>
+        <v>119816718</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,50 +2147,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489626</v>
+        <v>489390</v>
       </c>
       <c r="R15" t="n">
-        <v>6950077</v>
+        <v>6949929</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,22 +2235,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816697</v>
+        <v>119816597</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489413</v>
+        <v>489387</v>
       </c>
       <c r="R16" t="n">
-        <v>6949932</v>
+        <v>6949914</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811422</v>
+        <v>119811101</v>
       </c>
       <c r="B17" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,37 +2375,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489633</v>
+        <v>489639</v>
       </c>
       <c r="R17" t="n">
-        <v>6950101</v>
+        <v>6950268</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,22 +2464,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816597</v>
+        <v>119816697</v>
       </c>
       <c r="B18" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489387</v>
+        <v>489413</v>
       </c>
       <c r="R18" t="n">
-        <v>6949914</v>
+        <v>6949932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119811101</v>
+        <v>119811422</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
+        <v>90558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,42 +2604,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489639</v>
+        <v>489633</v>
       </c>
       <c r="R19" t="n">
-        <v>6950268</v>
+        <v>6950101</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2688,12 +2688,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816490</v>
+        <v>119816272</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2848,14 +2848,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489416</v>
+        <v>489537</v>
       </c>
       <c r="R21" t="n">
-        <v>6949992</v>
+        <v>6949917</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,7 +2924,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816272</v>
+        <v>119817871</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2960,14 +2960,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489537</v>
+        <v>489587</v>
       </c>
       <c r="R22" t="n">
-        <v>6949917</v>
+        <v>6949781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,19 +3024,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119817871</v>
+        <v>119816490</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -3072,14 +3072,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489587</v>
+        <v>489416</v>
       </c>
       <c r="R23" t="n">
-        <v>6949781</v>
+        <v>6949992</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,12 +3136,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811823</v>
+        <v>119811744</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5705,37 +5705,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489565</v>
+        <v>489626</v>
       </c>
       <c r="R46" t="n">
-        <v>6950090</v>
+        <v>6950077</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5764,7 +5769,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5774,7 +5779,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5789,22 +5794,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119811744</v>
+        <v>119815902</v>
       </c>
       <c r="B47" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5813,31 +5818,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5846,10 +5855,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489626</v>
+        <v>489634</v>
       </c>
       <c r="R47" t="n">
-        <v>6950077</v>
+        <v>6949843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5918,7 +5927,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119815902</v>
+        <v>119816425</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5953,7 +5962,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5963,14 +5972,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489634</v>
+        <v>489432</v>
       </c>
       <c r="R48" t="n">
-        <v>6949843</v>
+        <v>6949876</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6039,7 +6048,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816425</v>
+        <v>119816402</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -6074,7 +6083,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6088,10 +6097,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489432</v>
+        <v>489410</v>
       </c>
       <c r="R49" t="n">
-        <v>6949876</v>
+        <v>6949906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6160,10 +6169,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119816402</v>
+        <v>119811823</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6172,50 +6181,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489410</v>
+        <v>489565</v>
       </c>
       <c r="R50" t="n">
-        <v>6949906</v>
+        <v>6950090</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6269,22 +6269,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119811038</v>
+        <v>119816293</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6293,41 +6293,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489668</v>
+        <v>489470</v>
       </c>
       <c r="R51" t="n">
-        <v>6950267</v>
+        <v>6949911</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6381,19 +6381,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119816293</v>
+        <v>119815859</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6429,17 +6429,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489470</v>
+        <v>489648</v>
       </c>
       <c r="R52" t="n">
-        <v>6949911</v>
+        <v>6949845</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6493,22 +6493,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119815859</v>
+        <v>119817062</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6521,34 +6521,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489648</v>
+        <v>489451</v>
       </c>
       <c r="R53" t="n">
-        <v>6949845</v>
+        <v>6949854</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6605,22 +6605,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119817062</v>
+        <v>119811038</v>
       </c>
       <c r="B54" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6629,38 +6629,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489451</v>
+        <v>489668</v>
       </c>
       <c r="R54" t="n">
-        <v>6949854</v>
+        <v>6950267</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6717,12 +6717,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -9462,10 +9462,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119848365</v>
+        <v>119851578</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9478,34 +9478,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489632</v>
+        <v>489328</v>
       </c>
       <c r="R79" t="n">
-        <v>6949678</v>
+        <v>6950055</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9574,10 +9574,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851578</v>
+        <v>119848365</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9590,34 +9590,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489328</v>
+        <v>489632</v>
       </c>
       <c r="R80" t="n">
-        <v>6950055</v>
+        <v>6949678</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119816455</v>
+        <v>119811561</v>
       </c>
       <c r="B10" t="n">
-        <v>56522</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,46 +1568,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489402</v>
+        <v>489625</v>
       </c>
       <c r="R10" t="n">
-        <v>6949888</v>
+        <v>6950089</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1656,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119813023</v>
+        <v>119816293</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489483</v>
+        <v>489470</v>
       </c>
       <c r="R11" t="n">
-        <v>6950017</v>
+        <v>6949911</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,22 +1768,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119811924</v>
+        <v>119816571</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,39 +1796,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489533</v>
+        <v>489386</v>
       </c>
       <c r="R12" t="n">
-        <v>6950132</v>
+        <v>6950002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,19 +1880,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119811398</v>
+        <v>119811038</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1935,26 +1925,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489626</v>
+        <v>489668</v>
       </c>
       <c r="R13" t="n">
-        <v>6950077</v>
+        <v>6950267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,22 +1992,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119811768</v>
+        <v>119812008</v>
       </c>
       <c r="B14" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,41 +2016,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489601</v>
+        <v>489528</v>
       </c>
       <c r="R14" t="n">
-        <v>6950078</v>
+        <v>6950124</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2113,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816718</v>
+        <v>119816402</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,41 +2137,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489390</v>
+        <v>489410</v>
       </c>
       <c r="R15" t="n">
-        <v>6949929</v>
+        <v>6949906</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,22 +2234,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816597</v>
+        <v>119817114</v>
       </c>
       <c r="B16" t="n">
-        <v>96862</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,38 +2258,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489387</v>
+        <v>489487</v>
       </c>
       <c r="R16" t="n">
-        <v>6949914</v>
+        <v>6949865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811101</v>
+        <v>119811398</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,43 +2379,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489639</v>
+        <v>489626</v>
       </c>
       <c r="R17" t="n">
-        <v>6950268</v>
+        <v>6950077</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816697</v>
+        <v>119816403</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2504,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,13 +2528,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489413</v>
+        <v>489456</v>
       </c>
       <c r="R18" t="n">
-        <v>6949932</v>
+        <v>6949922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,22 +2588,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119811422</v>
+        <v>119816291</v>
       </c>
       <c r="B19" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,37 +2616,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489633</v>
+        <v>489475</v>
       </c>
       <c r="R19" t="n">
-        <v>6950101</v>
+        <v>6949863</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2688,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119812085</v>
+        <v>119816509</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,41 +2724,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489559</v>
+        <v>489392</v>
       </c>
       <c r="R20" t="n">
-        <v>6950125</v>
+        <v>6949873</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2775,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,22 +2821,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816272</v>
+        <v>119811101</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,34 +2849,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489537</v>
+        <v>489639</v>
       </c>
       <c r="R21" t="n">
-        <v>6949917</v>
+        <v>6950268</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,19 +2938,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119817871</v>
+        <v>119816543</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2960,14 +2986,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489587</v>
+        <v>489416</v>
       </c>
       <c r="R22" t="n">
-        <v>6949781</v>
+        <v>6949992</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,7 +3025,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3035,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,22 +3050,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119816490</v>
+        <v>119815905</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,41 +3074,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489416</v>
+        <v>489652</v>
       </c>
       <c r="R23" t="n">
-        <v>6949992</v>
+        <v>6949845</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3111,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,22 +3162,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119812494</v>
+        <v>119811022</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>95455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,39 +3190,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489516</v>
+        <v>489658</v>
       </c>
       <c r="R24" t="n">
-        <v>6950124</v>
+        <v>6950262</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3228,7 +3249,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3259,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,7 +3286,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119812008</v>
+        <v>119816566</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3300,7 +3321,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3310,14 +3331,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489528</v>
+        <v>489390</v>
       </c>
       <c r="R25" t="n">
-        <v>6950124</v>
+        <v>6949914</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3386,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119816291</v>
+        <v>119816869</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3398,25 +3419,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3426,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489475</v>
+        <v>489386</v>
       </c>
       <c r="R26" t="n">
-        <v>6949863</v>
+        <v>6950031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,19 +3507,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119815992</v>
+        <v>119816425</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3533,7 +3554,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3543,14 +3564,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489517</v>
+        <v>489432</v>
       </c>
       <c r="R27" t="n">
-        <v>6949756</v>
+        <v>6949876</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119811058</v>
+        <v>119813023</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3631,47 +3652,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489643</v>
+        <v>489483</v>
       </c>
       <c r="R28" t="n">
-        <v>6950272</v>
+        <v>6950017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3703,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,22 +3740,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119816409</v>
+        <v>119813032</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>90562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3756,21 +3768,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3780,10 +3792,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489456</v>
+        <v>489482</v>
       </c>
       <c r="R29" t="n">
-        <v>6949922</v>
+        <v>6950030</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3815,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3825,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119811596</v>
+        <v>119812085</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3864,50 +3876,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489598</v>
+        <v>489559</v>
       </c>
       <c r="R30" t="n">
-        <v>6950085</v>
+        <v>6950125</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,7 +3939,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3946,7 +3949,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,19 +3964,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119811204</v>
+        <v>119811823</v>
       </c>
       <c r="B31" t="n">
         <v>90580</v>
@@ -4009,17 +4012,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489659</v>
+        <v>489565</v>
       </c>
       <c r="R31" t="n">
-        <v>6950266</v>
+        <v>6950090</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4048,7 +4051,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4061,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4073,22 +4076,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119816157</v>
+        <v>119811204</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4097,38 +4100,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489537</v>
+        <v>489659</v>
       </c>
       <c r="R32" t="n">
-        <v>6949917</v>
+        <v>6950266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4160,7 +4163,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4170,7 +4173,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4197,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119816566</v>
+        <v>119817871</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4209,47 +4212,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489390</v>
+        <v>489587</v>
       </c>
       <c r="R33" t="n">
-        <v>6949914</v>
+        <v>6949781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4318,10 +4312,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119811022</v>
+        <v>119819067</v>
       </c>
       <c r="B34" t="n">
-        <v>95455</v>
+        <v>74638</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4334,34 +4328,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489658</v>
+        <v>489590</v>
       </c>
       <c r="R34" t="n">
-        <v>6950262</v>
+        <v>6949764</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4393,7 +4387,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4397,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,10 +4424,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119810875</v>
+        <v>119811346</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4442,50 +4436,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489650</v>
+        <v>489623</v>
       </c>
       <c r="R35" t="n">
-        <v>6950248</v>
+        <v>6950102</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4514,7 +4499,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4524,7 +4509,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4539,22 +4524,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119816869</v>
+        <v>119816272</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4563,38 +4548,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489386</v>
+        <v>489537</v>
       </c>
       <c r="R36" t="n">
-        <v>6950031</v>
+        <v>6949917</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4626,7 +4611,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4636,7 +4621,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4663,10 +4648,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119811966</v>
+        <v>119819157</v>
       </c>
       <c r="B37" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,34 +4664,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489533</v>
+        <v>489563</v>
       </c>
       <c r="R37" t="n">
-        <v>6950117</v>
+        <v>6949770</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4738,7 +4723,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4748,7 +4733,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119818590</v>
+        <v>119812106</v>
       </c>
       <c r="B38" t="n">
-        <v>79635</v>
+        <v>90846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,41 +4772,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489596</v>
+        <v>489537</v>
       </c>
       <c r="R38" t="n">
-        <v>6949748</v>
+        <v>6950131</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4850,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4860,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4875,22 +4860,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819067</v>
+        <v>119818590</v>
       </c>
       <c r="B39" t="n">
-        <v>74638</v>
+        <v>79635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4899,25 +4884,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4927,13 +4912,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489590</v>
+        <v>489596</v>
       </c>
       <c r="R39" t="n">
-        <v>6949764</v>
+        <v>6949748</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4962,7 +4947,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4972,7 +4957,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,22 +4972,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119815546</v>
+        <v>119817062</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5015,37 +5000,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489670</v>
+        <v>489451</v>
       </c>
       <c r="R40" t="n">
-        <v>6949842</v>
+        <v>6949854</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5074,7 +5059,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5084,7 +5069,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5099,12 +5084,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5223,10 +5208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119811346</v>
+        <v>119815546</v>
       </c>
       <c r="B42" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5239,21 +5224,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5263,10 +5248,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489623</v>
+        <v>489670</v>
       </c>
       <c r="R42" t="n">
-        <v>6950102</v>
+        <v>6949842</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5298,7 +5283,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5308,7 +5293,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5335,10 +5320,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119816403</v>
+        <v>119811058</v>
       </c>
       <c r="B43" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5347,41 +5332,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489456</v>
+        <v>489643</v>
       </c>
       <c r="R43" t="n">
-        <v>6949922</v>
+        <v>6950272</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5410,7 +5404,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5420,7 +5414,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5435,19 +5429,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119815982</v>
+        <v>119815992</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5482,7 +5476,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5496,10 +5490,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489561</v>
+        <v>489517</v>
       </c>
       <c r="R44" t="n">
-        <v>6949786</v>
+        <v>6949756</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5568,10 +5562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119816681</v>
+        <v>119811103</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5580,50 +5574,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489415</v>
+        <v>489639</v>
       </c>
       <c r="R45" t="n">
-        <v>6949931</v>
+        <v>6950275</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5652,7 +5637,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5662,7 +5647,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5677,22 +5662,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811744</v>
+        <v>119816455</v>
       </c>
       <c r="B46" t="n">
-        <v>57326</v>
+        <v>56522</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5701,43 +5686,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489626</v>
+        <v>489402</v>
       </c>
       <c r="R46" t="n">
-        <v>6950077</v>
+        <v>6949888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5806,10 +5791,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119815902</v>
+        <v>119811924</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,47 +5803,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489634</v>
+        <v>489533</v>
       </c>
       <c r="R47" t="n">
-        <v>6949843</v>
+        <v>6950132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5927,7 +5908,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119816425</v>
+        <v>119811596</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5962,7 +5943,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5972,17 +5953,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489432</v>
+        <v>489598</v>
       </c>
       <c r="R48" t="n">
-        <v>6949876</v>
+        <v>6950085</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6011,7 +5992,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6021,7 +6002,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6036,19 +6017,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816402</v>
+        <v>119810875</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -6083,7 +6064,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6093,14 +6074,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489410</v>
+        <v>489650</v>
       </c>
       <c r="R49" t="n">
-        <v>6949906</v>
+        <v>6950248</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6169,10 +6150,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119811823</v>
+        <v>119815859</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6185,21 +6166,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6209,13 +6190,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489565</v>
+        <v>489648</v>
       </c>
       <c r="R50" t="n">
-        <v>6950090</v>
+        <v>6949845</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6244,7 +6225,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6254,7 +6235,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6269,22 +6250,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119816293</v>
+        <v>119812494</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6297,34 +6278,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489470</v>
+        <v>489516</v>
       </c>
       <c r="R51" t="n">
-        <v>6949911</v>
+        <v>6950124</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6356,7 +6342,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6366,7 +6352,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6393,10 +6379,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119815859</v>
+        <v>119816718</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6409,37 +6395,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489648</v>
+        <v>489390</v>
       </c>
       <c r="R52" t="n">
-        <v>6949845</v>
+        <v>6949929</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6468,7 +6454,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6478,7 +6464,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6493,22 +6479,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119817062</v>
+        <v>119816697</v>
       </c>
       <c r="B53" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6521,21 +6507,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6545,10 +6531,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489451</v>
+        <v>489413</v>
       </c>
       <c r="R53" t="n">
-        <v>6949854</v>
+        <v>6949932</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6603,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119811038</v>
+        <v>119816597</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>96862</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6629,38 +6615,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489668</v>
+        <v>489387</v>
       </c>
       <c r="R54" t="n">
-        <v>6950267</v>
+        <v>6949914</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6692,7 +6678,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6702,7 +6688,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6717,19 +6703,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119816036</v>
+        <v>119815982</v>
       </c>
       <c r="B55" t="n">
         <v>97907</v>
@@ -6764,7 +6750,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6774,14 +6760,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489554</v>
+        <v>489561</v>
       </c>
       <c r="R55" t="n">
-        <v>6949859</v>
+        <v>6949786</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6850,10 +6836,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119816571</v>
+        <v>119816681</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6862,38 +6848,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489386</v>
+        <v>489415</v>
       </c>
       <c r="R56" t="n">
-        <v>6950002</v>
+        <v>6949931</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6925,7 +6920,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6935,7 +6930,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6950,22 +6945,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119811103</v>
+        <v>119816157</v>
       </c>
       <c r="B57" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6974,41 +6969,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489639</v>
+        <v>489537</v>
       </c>
       <c r="R57" t="n">
-        <v>6950275</v>
+        <v>6949917</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7037,7 +7032,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7047,7 +7042,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7062,22 +7057,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119813032</v>
+        <v>119816409</v>
       </c>
       <c r="B58" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7090,21 +7085,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7114,10 +7109,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489482</v>
+        <v>489456</v>
       </c>
       <c r="R58" t="n">
-        <v>6950030</v>
+        <v>6949922</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7149,7 +7144,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7159,7 +7154,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7186,7 +7181,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119811826</v>
+        <v>119815902</v>
       </c>
       <c r="B59" t="n">
         <v>97907</v>
@@ -7221,7 +7216,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7231,14 +7226,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489523</v>
+        <v>489634</v>
       </c>
       <c r="R59" t="n">
-        <v>6950130</v>
+        <v>6949843</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7307,10 +7302,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811561</v>
+        <v>119811826</v>
       </c>
       <c r="B60" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7319,41 +7314,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489625</v>
+        <v>489523</v>
       </c>
       <c r="R60" t="n">
-        <v>6950089</v>
+        <v>6950130</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7382,7 +7386,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7392,7 +7396,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7407,22 +7411,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119815905</v>
+        <v>119816036</v>
       </c>
       <c r="B61" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7431,41 +7435,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489652</v>
+        <v>489554</v>
       </c>
       <c r="R61" t="n">
-        <v>6949845</v>
+        <v>6949859</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7494,7 +7507,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7504,7 +7517,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7519,22 +7532,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119817114</v>
+        <v>119811768</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7543,50 +7556,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489487</v>
+        <v>489601</v>
       </c>
       <c r="R62" t="n">
-        <v>6949865</v>
+        <v>6950078</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7615,7 +7619,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7629,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7640,22 +7644,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119816509</v>
+        <v>119811744</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7664,50 +7668,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489392</v>
+        <v>489626</v>
       </c>
       <c r="R63" t="n">
-        <v>6949873</v>
+        <v>6950077</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,22 +7761,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810849</v>
+        <v>119811966</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7785,50 +7785,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489644</v>
+        <v>489533</v>
       </c>
       <c r="R64" t="n">
-        <v>6950252</v>
+        <v>6950117</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7857,7 +7848,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7867,7 +7858,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,22 +7873,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119812106</v>
+        <v>119810849</v>
       </c>
       <c r="B65" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7906,38 +7897,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489537</v>
+        <v>489644</v>
       </c>
       <c r="R65" t="n">
-        <v>6950131</v>
+        <v>6950252</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8006,10 +8006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119819157</v>
+        <v>119811422</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,37 +8022,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489563</v>
+        <v>489633</v>
       </c>
       <c r="R66" t="n">
-        <v>6949770</v>
+        <v>6950101</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8106,19 +8106,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119850950</v>
+        <v>119852071</v>
       </c>
       <c r="B67" t="n">
         <v>82305</v>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489367</v>
+        <v>489392</v>
       </c>
       <c r="R67" t="n">
-        <v>6949918</v>
+        <v>6950011</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8230,10 +8230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119848594</v>
+        <v>119851248</v>
       </c>
       <c r="B68" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8246,34 +8246,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489615</v>
+        <v>489366</v>
       </c>
       <c r="R68" t="n">
-        <v>6949709</v>
+        <v>6949996</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8342,10 +8342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851248</v>
+        <v>119851683</v>
       </c>
       <c r="B69" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489366</v>
+        <v>489314</v>
       </c>
       <c r="R69" t="n">
-        <v>6949996</v>
+        <v>6950058</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8454,7 +8454,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119849062</v>
+        <v>119848688</v>
       </c>
       <c r="B70" t="n">
         <v>74638</v>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489573</v>
+        <v>489614</v>
       </c>
       <c r="R70" t="n">
-        <v>6949724</v>
+        <v>6949692</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8566,10 +8566,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119850649</v>
+        <v>119851578</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8582,21 +8582,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489406</v>
+        <v>489328</v>
       </c>
       <c r="R71" t="n">
-        <v>6949790</v>
+        <v>6950055</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,10 +8678,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119848818</v>
+        <v>119849489</v>
       </c>
       <c r="B72" t="n">
-        <v>90576</v>
+        <v>82305</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8694,21 +8694,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489593</v>
+        <v>489516</v>
       </c>
       <c r="R72" t="n">
-        <v>6949732</v>
+        <v>6949768</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8790,10 +8790,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851194</v>
+        <v>119850939</v>
       </c>
       <c r="B73" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8806,21 +8806,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8830,10 +8830,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489391</v>
+        <v>489367</v>
       </c>
       <c r="R73" t="n">
-        <v>6949965</v>
+        <v>6949918</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8902,10 +8902,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849171</v>
+        <v>119852547</v>
       </c>
       <c r="B74" t="n">
-        <v>79643</v>
+        <v>74638</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8914,38 +8914,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489554</v>
+        <v>489584</v>
       </c>
       <c r="R74" t="n">
-        <v>6949730</v>
+        <v>6949881</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9014,7 +9014,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119852547</v>
+        <v>119849062</v>
       </c>
       <c r="B75" t="n">
         <v>74638</v>
@@ -9050,14 +9050,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489584</v>
+        <v>489573</v>
       </c>
       <c r="R75" t="n">
-        <v>6949881</v>
+        <v>6949724</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850939</v>
+        <v>119850950</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9142,21 +9142,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9238,10 +9238,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119848733</v>
+        <v>119851194</v>
       </c>
       <c r="B77" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9254,34 +9254,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489600</v>
+        <v>489391</v>
       </c>
       <c r="R77" t="n">
-        <v>6949713</v>
+        <v>6949965</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9350,10 +9350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119848688</v>
+        <v>119848818</v>
       </c>
       <c r="B78" t="n">
-        <v>74638</v>
+        <v>90576</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489614</v>
+        <v>489593</v>
       </c>
       <c r="R78" t="n">
-        <v>6949692</v>
+        <v>6949732</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851578</v>
+        <v>119848733</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9478,34 +9478,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489328</v>
+        <v>489600</v>
       </c>
       <c r="R79" t="n">
-        <v>6950055</v>
+        <v>6949713</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9574,10 +9574,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119848365</v>
+        <v>119852338</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9586,41 +9586,60 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489632</v>
+        <v>489485</v>
       </c>
       <c r="R80" t="n">
-        <v>6949678</v>
+        <v>6950055</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9649,7 +9668,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9659,7 +9678,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9686,10 +9705,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119852071</v>
+        <v>119848365</v>
       </c>
       <c r="B81" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9702,34 +9721,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489392</v>
+        <v>489632</v>
       </c>
       <c r="R81" t="n">
-        <v>6950011</v>
+        <v>6949678</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9761,7 +9780,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9771,7 +9790,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9798,10 +9817,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119849489</v>
+        <v>119849171</v>
       </c>
       <c r="B82" t="n">
-        <v>82305</v>
+        <v>79643</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9810,25 +9829,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9838,10 +9857,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489516</v>
+        <v>489554</v>
       </c>
       <c r="R82" t="n">
-        <v>6949768</v>
+        <v>6949730</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9873,7 +9892,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9883,7 +9902,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9910,10 +9929,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119852338</v>
+        <v>119850649</v>
       </c>
       <c r="B83" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9922,60 +9941,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489485</v>
+        <v>489406</v>
       </c>
       <c r="R83" t="n">
-        <v>6950055</v>
+        <v>6949790</v>
       </c>
       <c r="S83" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10041,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851683</v>
+        <v>119848594</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10057,34 +10057,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489314</v>
+        <v>489615</v>
       </c>
       <c r="R84" t="n">
-        <v>6950058</v>
+        <v>6949709</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119811101</v>
+        <v>119816543</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,39 +2849,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489639</v>
+        <v>489416</v>
       </c>
       <c r="R21" t="n">
-        <v>6950268</v>
+        <v>6949992</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816543</v>
+        <v>119815905</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,41 +2957,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489416</v>
+        <v>489652</v>
       </c>
       <c r="R22" t="n">
-        <v>6949992</v>
+        <v>6949845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3035,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,22 +3045,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815905</v>
+        <v>119811101</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,41 +3069,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489652</v>
+        <v>489639</v>
       </c>
       <c r="R23" t="n">
-        <v>6949845</v>
+        <v>6950268</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816566</v>
+        <v>119813032</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,50 +3298,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489390</v>
+        <v>489482</v>
       </c>
       <c r="R25" t="n">
-        <v>6949914</v>
+        <v>6950030</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3370,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,22 +3386,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119816869</v>
+        <v>119812085</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,38 +3410,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489386</v>
+        <v>489559</v>
       </c>
       <c r="R26" t="n">
-        <v>6950031</v>
+        <v>6950125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,22 +3498,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119816425</v>
+        <v>119811823</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,50 +3522,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489432</v>
+        <v>489565</v>
       </c>
       <c r="R27" t="n">
-        <v>6949876</v>
+        <v>6950090</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3603,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,22 +3610,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119813023</v>
+        <v>119811204</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,34 +3638,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489483</v>
+        <v>489659</v>
       </c>
       <c r="R28" t="n">
-        <v>6950017</v>
+        <v>6950266</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119813032</v>
+        <v>119813023</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3768,21 +3750,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3792,13 +3774,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489482</v>
+        <v>489483</v>
       </c>
       <c r="R29" t="n">
-        <v>6950030</v>
+        <v>6950017</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3827,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,22 +3834,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119812085</v>
+        <v>119817871</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,34 +3862,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489559</v>
+        <v>489587</v>
       </c>
       <c r="R30" t="n">
-        <v>6950125</v>
+        <v>6949781</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119811823</v>
+        <v>119816566</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,41 +3970,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489565</v>
+        <v>489390</v>
       </c>
       <c r="R31" t="n">
-        <v>6950090</v>
+        <v>6949914</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4051,7 +4042,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4061,7 +4052,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,22 +4067,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119811204</v>
+        <v>119816869</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4100,38 +4091,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489659</v>
+        <v>489386</v>
       </c>
       <c r="R32" t="n">
-        <v>6950266</v>
+        <v>6950031</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4163,7 +4154,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4173,7 +4164,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4200,10 +4191,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119817871</v>
+        <v>119816425</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,38 +4203,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489587</v>
+        <v>489432</v>
       </c>
       <c r="R33" t="n">
-        <v>6949781</v>
+        <v>6949876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119815546</v>
+        <v>119811058</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,41 +5220,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489670</v>
+        <v>489643</v>
       </c>
       <c r="R42" t="n">
-        <v>6949842</v>
+        <v>6950272</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5283,7 +5292,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5293,7 +5302,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,19 +5317,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119811058</v>
+        <v>119815992</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -5355,7 +5364,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5365,14 +5374,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489643</v>
+        <v>489517</v>
       </c>
       <c r="R43" t="n">
-        <v>6950272</v>
+        <v>6949756</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,10 +5450,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119815992</v>
+        <v>119815546</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5453,50 +5462,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489517</v>
+        <v>489670</v>
       </c>
       <c r="R44" t="n">
-        <v>6949756</v>
+        <v>6949842</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119852547</v>
+        <v>119849062</v>
       </c>
       <c r="B74" t="n">
         <v>74638</v>
@@ -8938,14 +8938,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489584</v>
+        <v>489573</v>
       </c>
       <c r="R74" t="n">
-        <v>6949881</v>
+        <v>6949724</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9014,7 +9014,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849062</v>
+        <v>119852547</v>
       </c>
       <c r="B75" t="n">
         <v>74638</v>
@@ -9050,14 +9050,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489573</v>
+        <v>489584</v>
       </c>
       <c r="R75" t="n">
-        <v>6949724</v>
+        <v>6949881</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10041,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119848594</v>
+        <v>119849865</v>
       </c>
       <c r="B84" t="n">
-        <v>74638</v>
+        <v>57679</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,41 +10053,55 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489615</v>
+        <v>489413</v>
       </c>
       <c r="R84" t="n">
-        <v>6949709</v>
+        <v>6949801</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10116,7 +10130,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10126,7 +10140,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10153,10 +10172,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849865</v>
+        <v>119848594</v>
       </c>
       <c r="B85" t="n">
-        <v>57679</v>
+        <v>74638</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10165,55 +10184,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489413</v>
+        <v>489615</v>
       </c>
       <c r="R85" t="n">
-        <v>6949801</v>
+        <v>6949709</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10242,7 +10247,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10252,12 +10257,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816543</v>
+        <v>119811101</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,34 +2849,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489416</v>
+        <v>489639</v>
       </c>
       <c r="R21" t="n">
-        <v>6949992</v>
+        <v>6950268</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,22 +2938,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119815905</v>
+        <v>119816543</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,41 +2962,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489652</v>
+        <v>489416</v>
       </c>
       <c r="R22" t="n">
-        <v>6949845</v>
+        <v>6949992</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3025,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3035,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,22 +3050,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119811101</v>
+        <v>119815905</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3069,46 +3074,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489639</v>
+        <v>489652</v>
       </c>
       <c r="R23" t="n">
-        <v>6950268</v>
+        <v>6949845</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119813032</v>
+        <v>119816566</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,41 +3298,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489482</v>
+        <v>489390</v>
       </c>
       <c r="R25" t="n">
-        <v>6950030</v>
+        <v>6949914</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,22 +3395,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119812085</v>
+        <v>119816869</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,38 +3419,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489559</v>
+        <v>489386</v>
       </c>
       <c r="R26" t="n">
-        <v>6950125</v>
+        <v>6950031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,22 +3507,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119811823</v>
+        <v>119816425</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,41 +3531,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489565</v>
+        <v>489432</v>
       </c>
       <c r="R27" t="n">
-        <v>6950090</v>
+        <v>6949876</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3603,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3613,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,22 +3628,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119811204</v>
+        <v>119813023</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3638,34 +3656,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489659</v>
+        <v>489483</v>
       </c>
       <c r="R28" t="n">
-        <v>6950266</v>
+        <v>6950017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3697,7 +3715,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3725,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,10 +3752,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119813023</v>
+        <v>119813032</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,21 +3768,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,13 +3792,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489483</v>
+        <v>489482</v>
       </c>
       <c r="R29" t="n">
-        <v>6950017</v>
+        <v>6950030</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3809,7 +3827,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3837,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,22 +3852,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119817871</v>
+        <v>119812085</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,34 +3880,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489587</v>
+        <v>489559</v>
       </c>
       <c r="R30" t="n">
-        <v>6949781</v>
+        <v>6950125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3976,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119816566</v>
+        <v>119811823</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,50 +3988,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489390</v>
+        <v>489565</v>
       </c>
       <c r="R31" t="n">
-        <v>6949914</v>
+        <v>6950090</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4042,7 +4051,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4052,7 +4061,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,22 +4076,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119816869</v>
+        <v>119811204</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4091,38 +4100,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489386</v>
+        <v>489659</v>
       </c>
       <c r="R32" t="n">
-        <v>6950031</v>
+        <v>6950266</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,7 +4163,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4164,7 +4173,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4191,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119816425</v>
+        <v>119817871</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4203,47 +4212,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489432</v>
+        <v>489587</v>
       </c>
       <c r="R33" t="n">
-        <v>6949876</v>
+        <v>6949781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119817062</v>
+        <v>119815720</v>
       </c>
       <c r="B40" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,34 +5000,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489451</v>
+        <v>489670</v>
       </c>
       <c r="R40" t="n">
-        <v>6949854</v>
+        <v>6949846</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119815720</v>
+        <v>119817062</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,34 +5112,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489670</v>
+        <v>489451</v>
       </c>
       <c r="R41" t="n">
-        <v>6949846</v>
+        <v>6949854</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119811058</v>
+        <v>119815546</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,50 +5220,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489643</v>
+        <v>489670</v>
       </c>
       <c r="R42" t="n">
-        <v>6950272</v>
+        <v>6949842</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5292,7 +5283,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5302,7 +5293,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5317,19 +5308,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119815992</v>
+        <v>119811058</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -5364,7 +5355,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5374,14 +5365,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489517</v>
+        <v>489643</v>
       </c>
       <c r="R43" t="n">
-        <v>6949756</v>
+        <v>6950272</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5450,10 +5441,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119815546</v>
+        <v>119815992</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5462,41 +5453,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489670</v>
+        <v>489517</v>
       </c>
       <c r="R44" t="n">
-        <v>6949842</v>
+        <v>6949756</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -10041,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119849865</v>
+        <v>119848594</v>
       </c>
       <c r="B84" t="n">
-        <v>57679</v>
+        <v>74638</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,55 +10053,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489413</v>
+        <v>489615</v>
       </c>
       <c r="R84" t="n">
-        <v>6949801</v>
+        <v>6949709</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10130,7 +10116,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10140,12 +10126,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10172,10 +10153,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119848594</v>
+        <v>119849865</v>
       </c>
       <c r="B85" t="n">
-        <v>74638</v>
+        <v>57679</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10184,41 +10165,55 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489615</v>
+        <v>489413</v>
       </c>
       <c r="R85" t="n">
-        <v>6949709</v>
+        <v>6949801</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10247,7 +10242,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10257,7 +10252,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119811101</v>
+        <v>119816543</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,39 +2849,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489639</v>
+        <v>489416</v>
       </c>
       <c r="R21" t="n">
-        <v>6950268</v>
+        <v>6949992</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816543</v>
+        <v>119815905</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,41 +2957,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489416</v>
+        <v>489652</v>
       </c>
       <c r="R22" t="n">
-        <v>6949992</v>
+        <v>6949845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3035,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,22 +3045,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815905</v>
+        <v>119811101</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,41 +3069,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489652</v>
+        <v>489639</v>
       </c>
       <c r="R23" t="n">
-        <v>6949845</v>
+        <v>6950268</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119815720</v>
+        <v>119817062</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,34 +5000,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489670</v>
+        <v>489451</v>
       </c>
       <c r="R40" t="n">
-        <v>6949846</v>
+        <v>6949854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119817062</v>
+        <v>119815720</v>
       </c>
       <c r="B41" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,34 +5112,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489451</v>
+        <v>489670</v>
       </c>
       <c r="R41" t="n">
-        <v>6949854</v>
+        <v>6949846</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -7885,10 +7885,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810849</v>
+        <v>119811422</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>90558</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7897,47 +7897,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489644</v>
+        <v>489633</v>
       </c>
       <c r="R65" t="n">
-        <v>6950252</v>
+        <v>6950101</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7969,7 +7960,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7970,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8006,10 +7997,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119811422</v>
+        <v>119810849</v>
       </c>
       <c r="B66" t="n">
-        <v>90558</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8018,38 +8009,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489633</v>
+        <v>489644</v>
       </c>
       <c r="R66" t="n">
-        <v>6950101</v>
+        <v>6950252</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8902,7 +8902,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849062</v>
+        <v>119852547</v>
       </c>
       <c r="B74" t="n">
         <v>74638</v>
@@ -8938,14 +8938,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489573</v>
+        <v>489584</v>
       </c>
       <c r="R74" t="n">
-        <v>6949724</v>
+        <v>6949881</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9014,7 +9014,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119852547</v>
+        <v>119849062</v>
       </c>
       <c r="B75" t="n">
         <v>74638</v>
@@ -9050,14 +9050,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489584</v>
+        <v>489573</v>
       </c>
       <c r="R75" t="n">
-        <v>6949881</v>
+        <v>6949724</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2367,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811398</v>
+        <v>119816403</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,50 +2379,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489626</v>
+        <v>489456</v>
       </c>
       <c r="R17" t="n">
-        <v>6950077</v>
+        <v>6949922</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2452,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2467,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816403</v>
+        <v>119811398</v>
       </c>
       <c r="B18" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,41 +2491,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489456</v>
+        <v>489626</v>
       </c>
       <c r="R18" t="n">
-        <v>6949922</v>
+        <v>6950077</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,12 +2588,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816543</v>
+        <v>119811101</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,34 +2849,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489416</v>
+        <v>489639</v>
       </c>
       <c r="R21" t="n">
-        <v>6949992</v>
+        <v>6950268</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2923,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,22 +2938,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119815905</v>
+        <v>119816543</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,41 +2962,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489652</v>
+        <v>489416</v>
       </c>
       <c r="R22" t="n">
-        <v>6949845</v>
+        <v>6949992</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3025,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3035,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,22 +3050,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119811101</v>
+        <v>119815905</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3069,46 +3074,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489639</v>
+        <v>489652</v>
       </c>
       <c r="R23" t="n">
-        <v>6950268</v>
+        <v>6949845</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119815859</v>
+        <v>119816718</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6166,37 +6166,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489648</v>
+        <v>489390</v>
       </c>
       <c r="R50" t="n">
-        <v>6949845</v>
+        <v>6949929</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,12 +6250,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119816718</v>
+        <v>119815859</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,37 +6395,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489390</v>
+        <v>489648</v>
       </c>
       <c r="R52" t="n">
-        <v>6949929</v>
+        <v>6949845</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6479,12 +6479,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7885,10 +7885,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119811422</v>
+        <v>119810849</v>
       </c>
       <c r="B65" t="n">
-        <v>90558</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7897,38 +7897,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489633</v>
+        <v>489644</v>
       </c>
       <c r="R65" t="n">
-        <v>6950101</v>
+        <v>6950252</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7960,7 +7969,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7970,7 +7979,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7997,10 +8006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810849</v>
+        <v>119811422</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>90558</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8009,47 +8018,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489644</v>
+        <v>489633</v>
       </c>
       <c r="R66" t="n">
-        <v>6950252</v>
+        <v>6950101</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -10041,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119848594</v>
+        <v>119849865</v>
       </c>
       <c r="B84" t="n">
-        <v>74638</v>
+        <v>57679</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,41 +10053,55 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489615</v>
+        <v>489413</v>
       </c>
       <c r="R84" t="n">
-        <v>6949709</v>
+        <v>6949801</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10116,7 +10130,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10126,7 +10140,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10153,10 +10172,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849865</v>
+        <v>119848594</v>
       </c>
       <c r="B85" t="n">
-        <v>57679</v>
+        <v>74638</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10165,55 +10184,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489413</v>
+        <v>489615</v>
       </c>
       <c r="R85" t="n">
-        <v>6949801</v>
+        <v>6949709</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10242,7 +10247,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10252,12 +10257,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -4984,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119817062</v>
+        <v>119815720</v>
       </c>
       <c r="B40" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,34 +5000,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489451</v>
+        <v>489670</v>
       </c>
       <c r="R40" t="n">
-        <v>6949854</v>
+        <v>6949846</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119815720</v>
+        <v>119817062</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,34 +5112,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489670</v>
+        <v>489451</v>
       </c>
       <c r="R41" t="n">
-        <v>6949846</v>
+        <v>6949854</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119816718</v>
+        <v>119815859</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6166,37 +6166,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489390</v>
+        <v>489648</v>
       </c>
       <c r="R50" t="n">
-        <v>6949929</v>
+        <v>6949845</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,12 +6250,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119815859</v>
+        <v>119816718</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,37 +6395,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489648</v>
+        <v>489390</v>
       </c>
       <c r="R52" t="n">
-        <v>6949845</v>
+        <v>6949929</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6479,12 +6479,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2367,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119816403</v>
+        <v>119811398</v>
       </c>
       <c r="B17" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,41 +2379,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489456</v>
+        <v>489626</v>
       </c>
       <c r="R17" t="n">
-        <v>6949922</v>
+        <v>6950077</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,22 +2476,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119811398</v>
+        <v>119816403</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,50 +2500,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489626</v>
+        <v>489456</v>
       </c>
       <c r="R18" t="n">
-        <v>6950077</v>
+        <v>6949922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,12 +2588,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119811101</v>
+        <v>119816543</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,39 +2849,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489639</v>
+        <v>489416</v>
       </c>
       <c r="R21" t="n">
-        <v>6950268</v>
+        <v>6949992</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2923,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816543</v>
+        <v>119815905</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,41 +2957,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489416</v>
+        <v>489652</v>
       </c>
       <c r="R22" t="n">
-        <v>6949992</v>
+        <v>6949845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3035,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,22 +3045,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815905</v>
+        <v>119811101</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,41 +3069,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489652</v>
+        <v>489639</v>
       </c>
       <c r="R23" t="n">
-        <v>6949845</v>
+        <v>6950268</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119815859</v>
+        <v>119816718</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6166,37 +6166,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489648</v>
+        <v>489390</v>
       </c>
       <c r="R50" t="n">
-        <v>6949845</v>
+        <v>6949929</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,12 +6250,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119816718</v>
+        <v>119815859</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,37 +6395,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489390</v>
+        <v>489648</v>
       </c>
       <c r="R52" t="n">
-        <v>6949929</v>
+        <v>6949845</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6479,12 +6479,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119852547</v>
+        <v>119849062</v>
       </c>
       <c r="B74" t="n">
         <v>74638</v>
@@ -8938,14 +8938,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489584</v>
+        <v>489573</v>
       </c>
       <c r="R74" t="n">
-        <v>6949881</v>
+        <v>6949724</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9014,7 +9014,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849062</v>
+        <v>119852547</v>
       </c>
       <c r="B75" t="n">
         <v>74638</v>
@@ -9050,14 +9050,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489573</v>
+        <v>489584</v>
       </c>
       <c r="R75" t="n">
-        <v>6949724</v>
+        <v>6949881</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119811561</v>
+        <v>119816718</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489625</v>
+        <v>489390</v>
       </c>
       <c r="R10" t="n">
-        <v>6950089</v>
+        <v>6949929</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816293</v>
+        <v>119815720</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,17 +1704,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489470</v>
+        <v>489670</v>
       </c>
       <c r="R11" t="n">
-        <v>6949911</v>
+        <v>6949846</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1768,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119816571</v>
+        <v>119812494</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,37 +1796,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489386</v>
+        <v>489516</v>
       </c>
       <c r="R12" t="n">
-        <v>6950002</v>
+        <v>6950124</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1885,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119811038</v>
+        <v>119816543</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1909,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489668</v>
+        <v>489416</v>
       </c>
       <c r="R13" t="n">
-        <v>6950267</v>
+        <v>6949992</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119812008</v>
+        <v>119818590</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,47 +2021,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489528</v>
+        <v>489596</v>
       </c>
       <c r="R14" t="n">
-        <v>6950124</v>
+        <v>6949748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816402</v>
+        <v>119816403</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,50 +2133,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489410</v>
+        <v>489456</v>
       </c>
       <c r="R15" t="n">
-        <v>6949906</v>
+        <v>6949922</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,22 +2221,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119817114</v>
+        <v>119811398</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,7 +2268,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2291,14 +2278,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489487</v>
+        <v>489626</v>
       </c>
       <c r="R16" t="n">
-        <v>6949865</v>
+        <v>6950077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811398</v>
+        <v>119811038</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,26 +2387,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489626</v>
+        <v>489668</v>
       </c>
       <c r="R17" t="n">
-        <v>6950077</v>
+        <v>6950267</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2454,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816403</v>
+        <v>119811924</v>
       </c>
       <c r="B18" t="n">
-        <v>82305</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,37 +2482,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489456</v>
+        <v>489533</v>
       </c>
       <c r="R18" t="n">
-        <v>6949922</v>
+        <v>6950132</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,22 +2571,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119816291</v>
+        <v>119816409</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,13 +2623,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489475</v>
+        <v>489456</v>
       </c>
       <c r="R19" t="n">
-        <v>6949863</v>
+        <v>6949922</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,22 +2683,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816509</v>
+        <v>119815902</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,7 +2730,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2757,17 +2740,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489392</v>
+        <v>489634</v>
       </c>
       <c r="R20" t="n">
-        <v>6949873</v>
+        <v>6949843</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,22 +2804,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816543</v>
+        <v>119811346</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,37 +2832,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489416</v>
+        <v>489623</v>
       </c>
       <c r="R21" t="n">
-        <v>6949992</v>
+        <v>6950102</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,22 +2916,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119815905</v>
+        <v>119816272</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,13 +2968,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489652</v>
+        <v>489537</v>
       </c>
       <c r="R22" t="n">
-        <v>6949845</v>
+        <v>6949917</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,22 +3028,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119811101</v>
+        <v>119816697</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,39 +3056,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489639</v>
+        <v>489413</v>
       </c>
       <c r="R23" t="n">
-        <v>6950268</v>
+        <v>6949932</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119811022</v>
+        <v>119811744</v>
       </c>
       <c r="B24" t="n">
-        <v>95455</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,37 +3168,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489658</v>
+        <v>489626</v>
       </c>
       <c r="R24" t="n">
-        <v>6950262</v>
+        <v>6950077</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3249,7 +3232,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3259,7 +3242,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,22 +3257,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816566</v>
+        <v>119816157</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,47 +3281,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489390</v>
+        <v>489537</v>
       </c>
       <c r="R25" t="n">
-        <v>6949914</v>
+        <v>6949917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3370,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,22 +3369,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119816869</v>
+        <v>119812106</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,41 +3393,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489386</v>
+        <v>489537</v>
       </c>
       <c r="R26" t="n">
-        <v>6950031</v>
+        <v>6950131</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3482,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,22 +3481,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119816425</v>
+        <v>119816681</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3554,7 +3528,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3568,10 +3542,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489432</v>
+        <v>489415</v>
       </c>
       <c r="R27" t="n">
-        <v>6949876</v>
+        <v>6949931</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119813023</v>
+        <v>119811823</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3656,37 +3630,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489483</v>
+        <v>489565</v>
       </c>
       <c r="R28" t="n">
-        <v>6950017</v>
+        <v>6950090</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3715,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3699,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3740,22 +3714,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119813032</v>
+        <v>119816425</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,41 +3738,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489482</v>
+        <v>489432</v>
       </c>
       <c r="R29" t="n">
-        <v>6950030</v>
+        <v>6949876</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3827,7 +3810,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3837,7 +3820,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,22 +3835,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119812085</v>
+        <v>119819067</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,37 +3863,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489559</v>
+        <v>489590</v>
       </c>
       <c r="R30" t="n">
-        <v>6950125</v>
+        <v>6949764</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3939,7 +3922,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3949,7 +3932,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3964,22 +3947,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119811823</v>
+        <v>119816455</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,41 +3971,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489565</v>
+        <v>489402</v>
       </c>
       <c r="R31" t="n">
-        <v>6950090</v>
+        <v>6949888</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4051,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4061,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,22 +4064,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119811204</v>
+        <v>119811022</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,21 +4092,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4128,13 +4116,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489659</v>
+        <v>489658</v>
       </c>
       <c r="R32" t="n">
-        <v>6950266</v>
+        <v>6950262</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4163,7 +4151,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4173,7 +4161,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4188,12 +4176,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4203,7 +4191,7 @@
         <v>119817871</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4312,10 +4300,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819067</v>
+        <v>119817114</v>
       </c>
       <c r="B34" t="n">
-        <v>74638</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4324,41 +4312,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489590</v>
+        <v>489487</v>
       </c>
       <c r="R34" t="n">
-        <v>6949764</v>
+        <v>6949865</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4387,7 +4384,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4394,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4412,22 +4409,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119811346</v>
+        <v>119816951</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4436,41 +4433,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489623</v>
+        <v>489386</v>
       </c>
       <c r="R35" t="n">
-        <v>6950102</v>
+        <v>6950031</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4499,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4509,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4524,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119816272</v>
+        <v>119811561</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4552,21 +4558,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4576,13 +4582,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489537</v>
+        <v>489625</v>
       </c>
       <c r="R36" t="n">
-        <v>6949917</v>
+        <v>6950089</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4611,7 +4617,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4621,7 +4627,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4636,22 +4642,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819157</v>
+        <v>119813032</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4664,37 +4670,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489563</v>
+        <v>489482</v>
       </c>
       <c r="R37" t="n">
-        <v>6949770</v>
+        <v>6950030</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4723,7 +4729,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4733,7 +4739,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,22 +4754,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119812106</v>
+        <v>119815905</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,38 +4778,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489537</v>
+        <v>489652</v>
       </c>
       <c r="R38" t="n">
-        <v>6950131</v>
+        <v>6949845</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4835,7 +4841,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4845,7 +4851,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,10 +4878,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119818590</v>
+        <v>119811826</v>
       </c>
       <c r="B39" t="n">
-        <v>79635</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4884,38 +4890,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489596</v>
+        <v>489523</v>
       </c>
       <c r="R39" t="n">
-        <v>6949748</v>
+        <v>6950130</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,10 +4999,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119815720</v>
+        <v>119816402</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4996,38 +5011,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489670</v>
+        <v>489410</v>
       </c>
       <c r="R40" t="n">
-        <v>6949846</v>
+        <v>6949906</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5096,10 +5120,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119817062</v>
+        <v>119815982</v>
       </c>
       <c r="B41" t="n">
-        <v>79144</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,38 +5132,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489451</v>
+        <v>489561</v>
       </c>
       <c r="R41" t="n">
-        <v>6949854</v>
+        <v>6949786</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5208,10 +5241,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119815546</v>
+        <v>119813023</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5224,37 +5257,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489670</v>
+        <v>489483</v>
       </c>
       <c r="R42" t="n">
-        <v>6949842</v>
+        <v>6950017</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5283,7 +5316,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5293,7 +5326,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,22 +5341,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119811058</v>
+        <v>119812085</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,47 +5365,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489643</v>
+        <v>489559</v>
       </c>
       <c r="R43" t="n">
-        <v>6950272</v>
+        <v>6950125</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,10 +5465,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119815992</v>
+        <v>119816291</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5453,47 +5477,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489517</v>
+        <v>489475</v>
       </c>
       <c r="R44" t="n">
-        <v>6949756</v>
+        <v>6949863</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5562,10 +5577,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119811103</v>
+        <v>119811768</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>95478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5578,34 +5593,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489639</v>
+        <v>489601</v>
       </c>
       <c r="R45" t="n">
-        <v>6950275</v>
+        <v>6950078</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5637,7 +5652,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5647,7 +5662,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5674,10 +5689,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119816455</v>
+        <v>119811596</v>
       </c>
       <c r="B46" t="n">
-        <v>56522</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5686,46 +5701,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489402</v>
+        <v>489598</v>
       </c>
       <c r="R46" t="n">
-        <v>6949888</v>
+        <v>6950085</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5754,7 +5773,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5764,7 +5783,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5779,22 +5798,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119811924</v>
+        <v>119817062</v>
       </c>
       <c r="B47" t="n">
-        <v>57463</v>
+        <v>79160</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5807,39 +5826,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489533</v>
+        <v>489451</v>
       </c>
       <c r="R47" t="n">
-        <v>6950132</v>
+        <v>6949854</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5908,10 +5922,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119811596</v>
+        <v>119811103</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,47 +5934,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489598</v>
+        <v>489639</v>
       </c>
       <c r="R48" t="n">
-        <v>6950085</v>
+        <v>6950275</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5992,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6002,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6029,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810875</v>
+        <v>119816566</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6064,7 +6069,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6074,14 +6079,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489650</v>
+        <v>489390</v>
       </c>
       <c r="R49" t="n">
-        <v>6950248</v>
+        <v>6949914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6150,10 +6155,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119816718</v>
+        <v>119810849</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6162,38 +6167,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489390</v>
+        <v>489644</v>
       </c>
       <c r="R50" t="n">
-        <v>6949929</v>
+        <v>6950252</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6225,7 +6239,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6235,7 +6249,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6262,10 +6276,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119812494</v>
+        <v>119816571</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6278,42 +6292,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489516</v>
+        <v>489386</v>
       </c>
       <c r="R51" t="n">
-        <v>6950124</v>
+        <v>6950002</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6342,7 +6351,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6352,7 +6361,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6367,22 +6376,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119815859</v>
+        <v>119811422</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,21 +6404,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6419,13 +6428,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489648</v>
+        <v>489633</v>
       </c>
       <c r="R52" t="n">
-        <v>6949845</v>
+        <v>6950101</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6454,7 +6463,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6464,7 +6473,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6479,22 +6488,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119816697</v>
+        <v>119819157</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6527,14 +6536,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489413</v>
+        <v>489563</v>
       </c>
       <c r="R53" t="n">
-        <v>6949932</v>
+        <v>6949770</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6566,7 +6575,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6576,7 +6585,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6603,10 +6612,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119816597</v>
+        <v>119810875</v>
       </c>
       <c r="B54" t="n">
-        <v>96862</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6615,38 +6624,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489387</v>
+        <v>489650</v>
       </c>
       <c r="R54" t="n">
-        <v>6949914</v>
+        <v>6950248</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6715,10 +6733,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119815982</v>
+        <v>119816597</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>96885</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6727,47 +6745,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489561</v>
+        <v>489387</v>
       </c>
       <c r="R55" t="n">
-        <v>6949786</v>
+        <v>6949914</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6836,10 +6845,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119816681</v>
+        <v>119812008</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6871,7 +6880,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6881,14 +6890,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489415</v>
+        <v>489528</v>
       </c>
       <c r="R56" t="n">
-        <v>6949931</v>
+        <v>6950124</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6957,10 +6966,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119816157</v>
+        <v>119816036</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6969,38 +6978,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489537</v>
+        <v>489554</v>
       </c>
       <c r="R57" t="n">
-        <v>6949917</v>
+        <v>6949859</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7032,7 +7050,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7042,7 +7060,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7057,22 +7075,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119816409</v>
+        <v>119816293</v>
       </c>
       <c r="B58" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7085,21 +7103,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7109,10 +7127,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489456</v>
+        <v>489470</v>
       </c>
       <c r="R58" t="n">
-        <v>6949922</v>
+        <v>6949911</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7144,7 +7162,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7154,7 +7172,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7181,10 +7199,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119815902</v>
+        <v>119811966</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>95478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7193,47 +7211,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489634</v>
+        <v>489533</v>
       </c>
       <c r="R59" t="n">
-        <v>6949843</v>
+        <v>6950117</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7302,10 +7311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811826</v>
+        <v>119811058</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7337,7 +7346,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7351,10 +7360,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489523</v>
+        <v>489643</v>
       </c>
       <c r="R60" t="n">
-        <v>6950130</v>
+        <v>6950272</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7423,10 +7432,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119816036</v>
+        <v>119816509</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7458,7 +7467,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7468,17 +7477,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489554</v>
+        <v>489392</v>
       </c>
       <c r="R61" t="n">
-        <v>6949859</v>
+        <v>6949873</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7507,7 +7516,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7517,7 +7526,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,22 +7541,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119811768</v>
+        <v>119815859</v>
       </c>
       <c r="B62" t="n">
-        <v>95455</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7560,21 +7569,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7584,13 +7593,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489601</v>
+        <v>489648</v>
       </c>
       <c r="R62" t="n">
-        <v>6950078</v>
+        <v>6949845</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7619,7 +7628,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7629,7 +7638,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7644,22 +7653,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119811744</v>
+        <v>119815546</v>
       </c>
       <c r="B63" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7672,42 +7681,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489626</v>
+        <v>489670</v>
       </c>
       <c r="R63" t="n">
-        <v>6950077</v>
+        <v>6949842</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7736,7 +7740,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7746,7 +7750,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7761,22 +7765,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119811966</v>
+        <v>119811101</v>
       </c>
       <c r="B64" t="n">
-        <v>95455</v>
+        <v>57336</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7789,34 +7793,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489533</v>
+        <v>489639</v>
       </c>
       <c r="R64" t="n">
-        <v>6950117</v>
+        <v>6950268</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7885,10 +7894,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810849</v>
+        <v>119815992</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7920,7 +7929,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7930,17 +7939,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489644</v>
+        <v>489517</v>
       </c>
       <c r="R65" t="n">
-        <v>6950252</v>
+        <v>6949756</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7969,7 +7978,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7988,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,22 +8003,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119811422</v>
+        <v>119811204</v>
       </c>
       <c r="B66" t="n">
-        <v>90558</v>
+        <v>90598</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,37 +8031,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489633</v>
+        <v>489659</v>
       </c>
       <c r="R66" t="n">
-        <v>6950101</v>
+        <v>6950266</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8081,7 +8090,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +8100,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8106,22 +8115,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119852071</v>
+        <v>119850649</v>
       </c>
       <c r="B67" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8134,21 +8143,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8158,10 +8167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489392</v>
+        <v>489406</v>
       </c>
       <c r="R67" t="n">
-        <v>6950011</v>
+        <v>6949790</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8193,7 +8202,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8203,7 +8212,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8230,10 +8239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851248</v>
+        <v>119849865</v>
       </c>
       <c r="B68" t="n">
-        <v>82305</v>
+        <v>57689</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8242,41 +8251,55 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489366</v>
+        <v>489413</v>
       </c>
       <c r="R68" t="n">
-        <v>6949996</v>
+        <v>6949801</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8305,7 +8328,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8315,7 +8338,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8342,10 +8370,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851683</v>
+        <v>119851194</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8358,21 +8386,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8382,10 +8410,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489314</v>
+        <v>489391</v>
       </c>
       <c r="R69" t="n">
-        <v>6950058</v>
+        <v>6949965</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8417,7 +8445,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8427,7 +8455,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8454,10 +8482,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119848688</v>
+        <v>119852547</v>
       </c>
       <c r="B70" t="n">
-        <v>74638</v>
+        <v>74654</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8490,14 +8518,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489614</v>
+        <v>489584</v>
       </c>
       <c r="R70" t="n">
-        <v>6949692</v>
+        <v>6949881</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8529,7 +8557,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8539,7 +8567,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8566,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851578</v>
+        <v>119848594</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>74654</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8582,34 +8610,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489328</v>
+        <v>489615</v>
       </c>
       <c r="R71" t="n">
-        <v>6950055</v>
+        <v>6949709</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8641,7 +8669,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8651,7 +8679,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,10 +8706,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119849489</v>
+        <v>119850939</v>
       </c>
       <c r="B72" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8694,34 +8722,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489516</v>
+        <v>489367</v>
       </c>
       <c r="R72" t="n">
-        <v>6949768</v>
+        <v>6949918</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8753,7 +8781,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8763,7 +8791,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8790,10 +8818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850939</v>
+        <v>119851578</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8806,21 +8834,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8830,10 +8858,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489367</v>
+        <v>489328</v>
       </c>
       <c r="R73" t="n">
-        <v>6949918</v>
+        <v>6950055</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8865,7 +8893,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8875,7 +8903,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8902,10 +8930,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849062</v>
+        <v>119851248</v>
       </c>
       <c r="B74" t="n">
-        <v>74638</v>
+        <v>82321</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8918,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489573</v>
+        <v>489366</v>
       </c>
       <c r="R74" t="n">
-        <v>6949724</v>
+        <v>6949996</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8977,7 +9005,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8987,7 +9015,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9014,10 +9042,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119852547</v>
+        <v>119852071</v>
       </c>
       <c r="B75" t="n">
-        <v>74638</v>
+        <v>82321</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9030,34 +9058,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489584</v>
+        <v>489392</v>
       </c>
       <c r="R75" t="n">
-        <v>6949881</v>
+        <v>6950011</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9089,7 +9117,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9099,7 +9127,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9126,10 +9154,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850950</v>
+        <v>119848688</v>
       </c>
       <c r="B76" t="n">
-        <v>82305</v>
+        <v>74654</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9142,34 +9170,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489367</v>
+        <v>489614</v>
       </c>
       <c r="R76" t="n">
-        <v>6949918</v>
+        <v>6949692</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -9201,7 +9229,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9211,7 +9239,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9238,10 +9266,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851194</v>
+        <v>119852338</v>
       </c>
       <c r="B77" t="n">
-        <v>82305</v>
+        <v>56532</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9250,41 +9278,60 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489391</v>
+        <v>489485</v>
       </c>
       <c r="R77" t="n">
-        <v>6949965</v>
+        <v>6950055</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9313,7 +9360,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9323,7 +9370,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9350,10 +9397,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119848818</v>
+        <v>119848365</v>
       </c>
       <c r="B78" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9366,21 +9413,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9390,10 +9437,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489593</v>
+        <v>489632</v>
       </c>
       <c r="R78" t="n">
-        <v>6949732</v>
+        <v>6949678</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9425,7 +9472,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9435,7 +9482,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9465,7 +9512,7 @@
         <v>119848733</v>
       </c>
       <c r="B79" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9574,10 +9621,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119852338</v>
+        <v>119849062</v>
       </c>
       <c r="B80" t="n">
-        <v>56522</v>
+        <v>74654</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9586,60 +9633,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489485</v>
+        <v>489573</v>
       </c>
       <c r="R80" t="n">
-        <v>6950055</v>
+        <v>6949724</v>
       </c>
       <c r="S80" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9668,7 +9696,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9678,7 +9706,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9705,10 +9733,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119848365</v>
+        <v>119850950</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9721,34 +9749,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489632</v>
+        <v>489367</v>
       </c>
       <c r="R81" t="n">
-        <v>6949678</v>
+        <v>6949918</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9780,7 +9808,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9790,7 +9818,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9820,7 +9848,7 @@
         <v>119849171</v>
       </c>
       <c r="B82" t="n">
-        <v>79643</v>
+        <v>79659</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9929,10 +9957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119850649</v>
+        <v>119849489</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9945,34 +9973,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489406</v>
+        <v>489516</v>
       </c>
       <c r="R83" t="n">
-        <v>6949790</v>
+        <v>6949768</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -10004,7 +10032,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10014,7 +10042,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10041,10 +10069,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119849865</v>
+        <v>119851683</v>
       </c>
       <c r="B84" t="n">
-        <v>57679</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,55 +10081,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489413</v>
+        <v>489314</v>
       </c>
       <c r="R84" t="n">
-        <v>6949801</v>
+        <v>6950058</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10130,7 +10144,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10140,12 +10154,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10172,10 +10181,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119848594</v>
+        <v>119848818</v>
       </c>
       <c r="B85" t="n">
-        <v>74638</v>
+        <v>90594</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10188,21 +10197,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,10 +10221,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489615</v>
+        <v>489593</v>
       </c>
       <c r="R85" t="n">
-        <v>6949709</v>
+        <v>6949732</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10247,7 +10256,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10257,7 +10266,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119816718</v>
+        <v>119815720</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,37 +1572,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489390</v>
+        <v>489670</v>
       </c>
       <c r="R10" t="n">
-        <v>6949929</v>
+        <v>6949846</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,22 +1656,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815720</v>
+        <v>119816718</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,37 +1684,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489670</v>
+        <v>489390</v>
       </c>
       <c r="R11" t="n">
-        <v>6949846</v>
+        <v>6949929</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1768,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119812494</v>
+        <v>119818590</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,46 +1792,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489516</v>
+        <v>489596</v>
       </c>
       <c r="R12" t="n">
-        <v>6950124</v>
+        <v>6949748</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,22 +1880,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119816543</v>
+        <v>119812494</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,37 +1908,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489416</v>
+        <v>489516</v>
       </c>
       <c r="R13" t="n">
-        <v>6949992</v>
+        <v>6950124</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,22 +1997,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119818590</v>
+        <v>119816543</v>
       </c>
       <c r="B14" t="n">
-        <v>79651</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,38 +2021,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489596</v>
+        <v>489416</v>
       </c>
       <c r="R14" t="n">
-        <v>6949748</v>
+        <v>6949992</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,12 +2109,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119815902</v>
+        <v>119816272</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,47 +2707,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489634</v>
+        <v>489537</v>
       </c>
       <c r="R20" t="n">
-        <v>6949843</v>
+        <v>6949917</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,22 +2795,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119811346</v>
+        <v>119816697</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,37 +2823,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489623</v>
+        <v>489413</v>
       </c>
       <c r="R21" t="n">
-        <v>6950102</v>
+        <v>6949932</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2891,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,22 +2907,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816272</v>
+        <v>119816157</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2931,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3003,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119816697</v>
+        <v>119815902</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,38 +3043,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489413</v>
+        <v>489634</v>
       </c>
       <c r="R23" t="n">
-        <v>6949932</v>
+        <v>6949843</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119811744</v>
+        <v>119811346</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,42 +3168,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489626</v>
+        <v>489623</v>
       </c>
       <c r="R24" t="n">
-        <v>6950077</v>
+        <v>6950102</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3242,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,22 +3252,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816157</v>
+        <v>119811744</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,38 +3276,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489537</v>
+        <v>489626</v>
       </c>
       <c r="R25" t="n">
-        <v>6949917</v>
+        <v>6950077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,12 +3369,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119811823</v>
+        <v>119816455</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3626,41 +3626,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489565</v>
+        <v>489402</v>
       </c>
       <c r="R28" t="n">
-        <v>6950090</v>
+        <v>6949888</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3689,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3699,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,12 +3719,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3959,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119816455</v>
+        <v>119811823</v>
       </c>
       <c r="B31" t="n">
-        <v>56532</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3971,46 +3976,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489402</v>
+        <v>489565</v>
       </c>
       <c r="R31" t="n">
-        <v>6949888</v>
+        <v>6950090</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,22 +4064,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119811022</v>
+        <v>119817114</v>
       </c>
       <c r="B32" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,41 +4088,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489658</v>
+        <v>489487</v>
       </c>
       <c r="R32" t="n">
-        <v>6950262</v>
+        <v>6949865</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4151,7 +4160,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4161,7 +4170,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,22 +4185,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119817871</v>
+        <v>119816951</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4200,38 +4209,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489587</v>
+        <v>489386</v>
       </c>
       <c r="R33" t="n">
-        <v>6949781</v>
+        <v>6950031</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4263,7 +4281,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4273,7 +4291,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4288,22 +4306,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119817114</v>
+        <v>119811022</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4312,50 +4330,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489487</v>
+        <v>489658</v>
       </c>
       <c r="R34" t="n">
-        <v>6949865</v>
+        <v>6950262</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4384,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4394,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4409,22 +4418,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119816951</v>
+        <v>119817871</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4433,47 +4442,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489386</v>
+        <v>489587</v>
       </c>
       <c r="R35" t="n">
-        <v>6950031</v>
+        <v>6949781</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119812085</v>
+        <v>119816291</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5369,34 +5369,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489559</v>
+        <v>489475</v>
       </c>
       <c r="R43" t="n">
-        <v>6950125</v>
+        <v>6949863</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119816291</v>
+        <v>119812085</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,34 +5481,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489475</v>
+        <v>489559</v>
       </c>
       <c r="R44" t="n">
-        <v>6949863</v>
+        <v>6950125</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6034,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816566</v>
+        <v>119816571</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,47 +6046,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489390</v>
+        <v>489386</v>
       </c>
       <c r="R49" t="n">
-        <v>6949914</v>
+        <v>6950002</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6118,7 +6109,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6128,7 +6119,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,19 +6134,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810849</v>
+        <v>119816566</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -6190,7 +6181,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6200,17 +6191,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489644</v>
+        <v>489390</v>
       </c>
       <c r="R50" t="n">
-        <v>6950252</v>
+        <v>6949914</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6239,7 +6230,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6249,7 +6240,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,22 +6255,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119816571</v>
+        <v>119810849</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6288,41 +6279,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489386</v>
+        <v>489644</v>
       </c>
       <c r="R51" t="n">
-        <v>6950002</v>
+        <v>6950252</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,12 +6376,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7665,10 +7665,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119815546</v>
+        <v>119811204</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7681,37 +7681,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489670</v>
+        <v>489659</v>
       </c>
       <c r="R63" t="n">
-        <v>6949842</v>
+        <v>6950266</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119811101</v>
+        <v>119815546</v>
       </c>
       <c r="B64" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7793,42 +7793,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489639</v>
+        <v>489670</v>
       </c>
       <c r="R64" t="n">
-        <v>6950268</v>
+        <v>6949842</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7857,7 +7852,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7867,7 +7862,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,22 +7877,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119815992</v>
+        <v>119811101</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7906,47 +7901,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489517</v>
+        <v>489639</v>
       </c>
       <c r="R65" t="n">
-        <v>6949756</v>
+        <v>6950268</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119811204</v>
+        <v>119815992</v>
       </c>
       <c r="B66" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8027,38 +8018,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489659</v>
+        <v>489517</v>
       </c>
       <c r="R66" t="n">
-        <v>6950266</v>
+        <v>6949756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8115,12 +8115,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815720</v>
+        <v>119810875</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,38 +1568,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489670</v>
+        <v>489650</v>
       </c>
       <c r="R10" t="n">
-        <v>6949846</v>
+        <v>6950248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816718</v>
+        <v>119816490</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1693,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,13 +1717,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489390</v>
+        <v>489416</v>
       </c>
       <c r="R11" t="n">
-        <v>6949929</v>
+        <v>6949992</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119818590</v>
+        <v>119812494</v>
       </c>
       <c r="B12" t="n">
-        <v>79651</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,41 +1801,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489596</v>
+        <v>489516</v>
       </c>
       <c r="R12" t="n">
-        <v>6949748</v>
+        <v>6950124</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,7 +1869,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1879,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119812494</v>
+        <v>119816403</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,39 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489516</v>
+        <v>489456</v>
       </c>
       <c r="R13" t="n">
-        <v>6950124</v>
+        <v>6949922</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1972,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816543</v>
+        <v>119818590</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,38 +2030,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489416</v>
+        <v>489596</v>
       </c>
       <c r="R14" t="n">
-        <v>6949992</v>
+        <v>6949748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,22 +2118,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816403</v>
+        <v>119811022</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,34 +2146,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489456</v>
+        <v>489658</v>
       </c>
       <c r="R15" t="n">
-        <v>6949922</v>
+        <v>6950262</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119811398</v>
+        <v>119812085</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,47 +2254,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489626</v>
+        <v>489559</v>
       </c>
       <c r="R16" t="n">
-        <v>6950077</v>
+        <v>6950125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811038</v>
+        <v>119816597</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,38 +2366,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489668</v>
+        <v>489387</v>
       </c>
       <c r="R17" t="n">
-        <v>6950267</v>
+        <v>6949914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,22 +2454,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119811924</v>
+        <v>119811596</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,46 +2478,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489533</v>
+        <v>489598</v>
       </c>
       <c r="R18" t="n">
-        <v>6950132</v>
+        <v>6950085</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2560,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,22 +2575,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119816409</v>
+        <v>119811826</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,41 +2599,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489456</v>
+        <v>489523</v>
       </c>
       <c r="R19" t="n">
-        <v>6949922</v>
+        <v>6950130</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816272</v>
+        <v>119811346</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,21 +2724,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,13 +2748,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489537</v>
+        <v>489623</v>
       </c>
       <c r="R20" t="n">
-        <v>6949917</v>
+        <v>6950102</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2770,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,22 +2808,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119816697</v>
+        <v>119811204</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,34 +2836,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489413</v>
+        <v>489659</v>
       </c>
       <c r="R21" t="n">
-        <v>6949932</v>
+        <v>6950266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,22 +2920,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816157</v>
+        <v>119810849</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,41 +2944,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489537</v>
+        <v>489644</v>
       </c>
       <c r="R22" t="n">
-        <v>6949917</v>
+        <v>6950252</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2994,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,19 +3041,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815902</v>
+        <v>119817114</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3066,7 +3088,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3076,14 +3098,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489634</v>
+        <v>489487</v>
       </c>
       <c r="R23" t="n">
-        <v>6949843</v>
+        <v>6949865</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119811346</v>
+        <v>119816293</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,34 +3190,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489623</v>
+        <v>489470</v>
       </c>
       <c r="R24" t="n">
-        <v>6950102</v>
+        <v>6949911</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3227,7 +3249,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3259,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119811744</v>
+        <v>119816566</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,43 +3298,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489626</v>
+        <v>489390</v>
       </c>
       <c r="R25" t="n">
-        <v>6950077</v>
+        <v>6949914</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3381,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119812106</v>
+        <v>119816986</v>
       </c>
       <c r="B26" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,41 +3419,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489537</v>
+        <v>489386</v>
       </c>
       <c r="R26" t="n">
-        <v>6950131</v>
+        <v>6950031</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3456,7 +3491,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3501,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,22 +3516,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119816681</v>
+        <v>119812106</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,50 +3540,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489415</v>
+        <v>489537</v>
       </c>
       <c r="R27" t="n">
-        <v>6949931</v>
+        <v>6950131</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3603,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3613,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3628,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119816455</v>
+        <v>119816425</v>
       </c>
       <c r="B28" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3626,31 +3652,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3659,10 +3689,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489402</v>
+        <v>489432</v>
       </c>
       <c r="R28" t="n">
-        <v>6949888</v>
+        <v>6949876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3761,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119816425</v>
+        <v>119816036</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3766,7 +3796,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3776,14 +3806,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489432</v>
+        <v>489554</v>
       </c>
       <c r="R29" t="n">
-        <v>6949876</v>
+        <v>6949859</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,10 +3882,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819067</v>
+        <v>119811561</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3868,34 +3898,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489590</v>
+        <v>489625</v>
       </c>
       <c r="R30" t="n">
-        <v>6949764</v>
+        <v>6950089</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3927,7 +3957,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3937,7 +3967,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3964,10 +3994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119811823</v>
+        <v>119815720</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3980,21 +4010,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4004,13 +4034,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489565</v>
+        <v>489670</v>
       </c>
       <c r="R31" t="n">
-        <v>6950090</v>
+        <v>6949846</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4039,7 +4069,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4049,7 +4079,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,22 +4094,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119817114</v>
+        <v>119816157</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,47 +4118,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489487</v>
+        <v>489537</v>
       </c>
       <c r="R32" t="n">
-        <v>6949865</v>
+        <v>6949917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4160,7 +4181,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4170,7 +4191,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,19 +4206,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119816951</v>
+        <v>119812008</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -4232,7 +4253,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4242,14 +4263,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489386</v>
+        <v>489528</v>
       </c>
       <c r="R33" t="n">
-        <v>6950031</v>
+        <v>6950124</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,7 +4302,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4291,7 +4312,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4306,22 +4327,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119811022</v>
+        <v>119816571</v>
       </c>
       <c r="B34" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4334,37 +4355,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489658</v>
+        <v>489386</v>
       </c>
       <c r="R34" t="n">
-        <v>6950262</v>
+        <v>6950002</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4393,7 +4414,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4424,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,19 +4439,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119817871</v>
+        <v>119819157</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -4470,10 +4491,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489587</v>
+        <v>489563</v>
       </c>
       <c r="R35" t="n">
-        <v>6949781</v>
+        <v>6949770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4526,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4536,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4542,10 +4563,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119811561</v>
+        <v>119815902</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4554,41 +4575,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489625</v>
+        <v>489634</v>
       </c>
       <c r="R36" t="n">
-        <v>6950089</v>
+        <v>6949843</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4617,7 +4647,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4627,7 +4657,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4642,22 +4672,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119813032</v>
+        <v>119816409</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4670,21 +4700,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4694,10 +4724,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489482</v>
+        <v>489456</v>
       </c>
       <c r="R37" t="n">
-        <v>6950030</v>
+        <v>6949922</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4729,7 +4759,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4739,7 +4769,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4766,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119815905</v>
+        <v>119811768</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4778,25 +4808,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4806,10 +4836,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489652</v>
+        <v>489601</v>
       </c>
       <c r="R38" t="n">
-        <v>6949845</v>
+        <v>6950078</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4841,7 +4871,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4851,7 +4881,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,7 +4908,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119811826</v>
+        <v>119811398</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4913,7 +4943,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4923,14 +4953,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489523</v>
+        <v>489626</v>
       </c>
       <c r="R39" t="n">
-        <v>6950130</v>
+        <v>6950077</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5120,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119815982</v>
+        <v>119811823</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5132,50 +5162,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489561</v>
+        <v>489565</v>
       </c>
       <c r="R41" t="n">
-        <v>6949786</v>
+        <v>6950090</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5204,7 +5225,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5214,7 +5235,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,22 +5250,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119813023</v>
+        <v>119811744</v>
       </c>
       <c r="B42" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5257,34 +5278,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489483</v>
+        <v>489626</v>
       </c>
       <c r="R42" t="n">
-        <v>6950017</v>
+        <v>6950077</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5316,7 +5342,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5326,7 +5352,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,22 +5367,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119816291</v>
+        <v>119816455</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5365,38 +5391,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489475</v>
+        <v>489402</v>
       </c>
       <c r="R43" t="n">
-        <v>6949863</v>
+        <v>6949888</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5465,10 +5496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119812085</v>
+        <v>119811058</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5477,38 +5508,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489559</v>
+        <v>489643</v>
       </c>
       <c r="R44" t="n">
-        <v>6950125</v>
+        <v>6950272</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5577,10 +5617,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119811768</v>
+        <v>119815982</v>
       </c>
       <c r="B45" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5589,41 +5629,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489601</v>
+        <v>489561</v>
       </c>
       <c r="R45" t="n">
-        <v>6950078</v>
+        <v>6949786</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5652,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5662,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5677,22 +5726,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811596</v>
+        <v>119811966</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5701,50 +5750,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489598</v>
+        <v>489533</v>
       </c>
       <c r="R46" t="n">
-        <v>6950085</v>
+        <v>6950117</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5773,7 +5813,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5783,7 +5823,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5798,22 +5838,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119817062</v>
+        <v>119811038</v>
       </c>
       <c r="B47" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5822,38 +5862,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489451</v>
+        <v>489668</v>
       </c>
       <c r="R47" t="n">
-        <v>6949854</v>
+        <v>6950267</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5885,7 +5925,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5895,7 +5935,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5910,22 +5950,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119811103</v>
+        <v>119816272</v>
       </c>
       <c r="B48" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5938,37 +5978,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489639</v>
+        <v>489537</v>
       </c>
       <c r="R48" t="n">
-        <v>6950275</v>
+        <v>6949917</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5997,7 +6037,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6047,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6022,22 +6062,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816571</v>
+        <v>119811101</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6050,34 +6090,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489386</v>
+        <v>489639</v>
       </c>
       <c r="R49" t="n">
-        <v>6950002</v>
+        <v>6950268</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6109,7 +6154,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6119,7 +6164,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6134,22 +6179,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119816566</v>
+        <v>119815905</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6158,50 +6203,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489390</v>
+        <v>489652</v>
       </c>
       <c r="R50" t="n">
-        <v>6949914</v>
+        <v>6949845</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6230,7 +6266,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6240,7 +6276,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6255,22 +6291,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119810849</v>
+        <v>119813023</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6279,50 +6315,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489644</v>
+        <v>489483</v>
       </c>
       <c r="R51" t="n">
-        <v>6950252</v>
+        <v>6950017</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6351,7 +6378,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6361,7 +6388,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,22 +6403,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119811422</v>
+        <v>119815859</v>
       </c>
       <c r="B52" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6404,21 +6431,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6428,13 +6455,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489633</v>
+        <v>489648</v>
       </c>
       <c r="R52" t="n">
-        <v>6950101</v>
+        <v>6949845</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6463,7 +6490,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6473,7 +6500,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6488,22 +6515,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119819157</v>
+        <v>119811103</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6516,37 +6543,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489563</v>
+        <v>489639</v>
       </c>
       <c r="R53" t="n">
-        <v>6949770</v>
+        <v>6950275</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6575,7 +6602,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6585,7 +6612,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,22 +6627,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119810875</v>
+        <v>119811422</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>90576</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6624,50 +6651,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489650</v>
+        <v>489633</v>
       </c>
       <c r="R54" t="n">
-        <v>6950248</v>
+        <v>6950101</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6696,7 +6714,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6706,7 +6724,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6721,22 +6739,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119816597</v>
+        <v>119815546</v>
       </c>
       <c r="B55" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,41 +6763,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489387</v>
+        <v>489670</v>
       </c>
       <c r="R55" t="n">
-        <v>6949914</v>
+        <v>6949842</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6808,7 +6826,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6818,7 +6836,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6833,22 +6851,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119812008</v>
+        <v>119816291</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6857,47 +6875,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489528</v>
+        <v>489475</v>
       </c>
       <c r="R56" t="n">
-        <v>6950124</v>
+        <v>6949863</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6966,10 +6975,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119816036</v>
+        <v>119819067</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>74654</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6978,50 +6987,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489554</v>
+        <v>489590</v>
       </c>
       <c r="R57" t="n">
-        <v>6949859</v>
+        <v>6949764</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7075,19 +7075,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119816293</v>
+        <v>119816697</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -7127,13 +7127,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489470</v>
+        <v>489413</v>
       </c>
       <c r="R58" t="n">
-        <v>6949911</v>
+        <v>6949932</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7187,22 +7187,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119811966</v>
+        <v>119813032</v>
       </c>
       <c r="B59" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7215,37 +7215,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489533</v>
+        <v>489482</v>
       </c>
       <c r="R59" t="n">
-        <v>6950117</v>
+        <v>6950030</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7299,19 +7299,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811058</v>
+        <v>119816509</v>
       </c>
       <c r="B60" t="n">
         <v>97930</v>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7356,17 +7356,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489643</v>
+        <v>489392</v>
       </c>
       <c r="R60" t="n">
-        <v>6950272</v>
+        <v>6949873</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7420,19 +7420,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119816509</v>
+        <v>119816681</v>
       </c>
       <c r="B61" t="n">
         <v>97930</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489392</v>
+        <v>489415</v>
       </c>
       <c r="R61" t="n">
-        <v>6949873</v>
+        <v>6949931</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7541,22 +7541,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119815859</v>
+        <v>119817062</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7569,34 +7569,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489648</v>
+        <v>489451</v>
       </c>
       <c r="R62" t="n">
-        <v>6949845</v>
+        <v>6949854</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7653,22 +7653,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119811204</v>
+        <v>119817871</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7681,34 +7681,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489659</v>
+        <v>489587</v>
       </c>
       <c r="R63" t="n">
-        <v>6950266</v>
+        <v>6949781</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7765,22 +7765,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119815546</v>
+        <v>119816718</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7793,34 +7793,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489670</v>
+        <v>489390</v>
       </c>
       <c r="R64" t="n">
-        <v>6949842</v>
+        <v>6949929</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7889,10 +7889,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119811101</v>
+        <v>119815992</v>
       </c>
       <c r="B65" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7901,43 +7901,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489639</v>
+        <v>489517</v>
       </c>
       <c r="R65" t="n">
-        <v>6950268</v>
+        <v>6949756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8006,10 +8010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119815992</v>
+        <v>119811924</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8018,47 +8022,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489517</v>
+        <v>489533</v>
       </c>
       <c r="R66" t="n">
-        <v>6949756</v>
+        <v>6950132</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119850649</v>
+        <v>119851683</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489406</v>
+        <v>489314</v>
       </c>
       <c r="R67" t="n">
-        <v>6949790</v>
+        <v>6950058</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8239,10 +8239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849865</v>
+        <v>119852338</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>56532</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8255,21 +8255,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8282,9 +8282,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8293,13 +8298,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489413</v>
+        <v>489485</v>
       </c>
       <c r="R68" t="n">
-        <v>6949801</v>
+        <v>6950055</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8328,7 +8333,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8338,12 +8343,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8370,7 +8370,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851194</v>
+        <v>119850950</v>
       </c>
       <c r="B69" t="n">
         <v>82321</v>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489391</v>
+        <v>489367</v>
       </c>
       <c r="R69" t="n">
-        <v>6949965</v>
+        <v>6949918</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8482,7 +8482,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119852547</v>
+        <v>119848594</v>
       </c>
       <c r="B70" t="n">
         <v>74654</v>
@@ -8518,14 +8518,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489584</v>
+        <v>489615</v>
       </c>
       <c r="R70" t="n">
-        <v>6949881</v>
+        <v>6949709</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8594,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119848594</v>
+        <v>119848818</v>
       </c>
       <c r="B71" t="n">
-        <v>74654</v>
+        <v>90594</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8610,21 +8610,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489615</v>
+        <v>489593</v>
       </c>
       <c r="R71" t="n">
-        <v>6949709</v>
+        <v>6949732</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8706,10 +8706,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850939</v>
+        <v>119849062</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8722,34 +8722,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489367</v>
+        <v>489573</v>
       </c>
       <c r="R72" t="n">
-        <v>6949918</v>
+        <v>6949724</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8818,10 +8818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851578</v>
+        <v>119848365</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8834,34 +8834,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489328</v>
+        <v>489632</v>
       </c>
       <c r="R73" t="n">
-        <v>6950055</v>
+        <v>6949678</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8930,10 +8930,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119851248</v>
+        <v>119850939</v>
       </c>
       <c r="B74" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8946,21 +8946,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489366</v>
+        <v>489367</v>
       </c>
       <c r="R74" t="n">
-        <v>6949996</v>
+        <v>6949918</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9042,10 +9042,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119852071</v>
+        <v>119848733</v>
       </c>
       <c r="B75" t="n">
-        <v>82321</v>
+        <v>90598</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9058,34 +9058,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489392</v>
+        <v>489600</v>
       </c>
       <c r="R75" t="n">
-        <v>6950011</v>
+        <v>6949713</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9154,10 +9154,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119848688</v>
+        <v>119851248</v>
       </c>
       <c r="B76" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9170,34 +9170,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489614</v>
+        <v>489366</v>
       </c>
       <c r="R76" t="n">
-        <v>6949692</v>
+        <v>6949996</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9266,10 +9266,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119852338</v>
+        <v>119851578</v>
       </c>
       <c r="B77" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9278,60 +9278,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489485</v>
+        <v>489328</v>
       </c>
       <c r="R77" t="n">
         <v>6950055</v>
       </c>
       <c r="S77" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9360,7 +9341,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9370,7 +9351,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9397,10 +9378,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119848365</v>
+        <v>119849171</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9409,25 +9390,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9437,10 +9418,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489632</v>
+        <v>489554</v>
       </c>
       <c r="R78" t="n">
-        <v>6949678</v>
+        <v>6949730</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9472,7 +9453,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9482,7 +9463,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9509,10 +9490,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119848733</v>
+        <v>119852547</v>
       </c>
       <c r="B79" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9525,34 +9506,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489600</v>
+        <v>489584</v>
       </c>
       <c r="R79" t="n">
-        <v>6949713</v>
+        <v>6949881</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9584,7 +9565,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9594,7 +9575,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9621,10 +9602,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119849062</v>
+        <v>119851194</v>
       </c>
       <c r="B80" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9637,34 +9618,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489573</v>
+        <v>489391</v>
       </c>
       <c r="R80" t="n">
-        <v>6949724</v>
+        <v>6949965</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9696,7 +9677,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9706,7 +9687,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9733,7 +9714,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850950</v>
+        <v>119852071</v>
       </c>
       <c r="B81" t="n">
         <v>82321</v>
@@ -9773,10 +9754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489367</v>
+        <v>489392</v>
       </c>
       <c r="R81" t="n">
-        <v>6949918</v>
+        <v>6950011</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9808,7 +9789,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9818,7 +9799,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9845,10 +9826,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119849171</v>
+        <v>119850649</v>
       </c>
       <c r="B82" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9857,38 +9838,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489554</v>
+        <v>489406</v>
       </c>
       <c r="R82" t="n">
-        <v>6949730</v>
+        <v>6949790</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9920,7 +9901,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9930,7 +9911,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9957,10 +9938,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119849489</v>
+        <v>119849865</v>
       </c>
       <c r="B83" t="n">
-        <v>82321</v>
+        <v>57689</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9969,41 +9950,55 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489516</v>
+        <v>489413</v>
       </c>
       <c r="R83" t="n">
-        <v>6949768</v>
+        <v>6949801</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10032,7 +10027,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10042,7 +10037,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10069,10 +10069,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851683</v>
+        <v>119848688</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10085,34 +10085,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489314</v>
+        <v>489614</v>
       </c>
       <c r="R84" t="n">
-        <v>6950058</v>
+        <v>6949692</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10181,10 +10181,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119848818</v>
+        <v>119849489</v>
       </c>
       <c r="B85" t="n">
-        <v>90594</v>
+        <v>82321</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10197,21 +10197,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10221,10 +10221,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489593</v>
+        <v>489516</v>
       </c>
       <c r="R85" t="n">
-        <v>6949732</v>
+        <v>6949768</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119818590</v>
+        <v>119816597</v>
       </c>
       <c r="B14" t="n">
-        <v>79651</v>
+        <v>96885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,34 +2034,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489596</v>
+        <v>489387</v>
       </c>
       <c r="R14" t="n">
-        <v>6949748</v>
+        <v>6949914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119811022</v>
+        <v>119812085</v>
       </c>
       <c r="B15" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489658</v>
+        <v>489559</v>
       </c>
       <c r="R15" t="n">
-        <v>6950262</v>
+        <v>6950125</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,22 +2230,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119812085</v>
+        <v>119818590</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>79651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,38 +2254,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489559</v>
+        <v>489596</v>
       </c>
       <c r="R16" t="n">
-        <v>6950125</v>
+        <v>6949748</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119816597</v>
+        <v>119811022</v>
       </c>
       <c r="B17" t="n">
-        <v>96885</v>
+        <v>95478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,41 +2366,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489387</v>
+        <v>489658</v>
       </c>
       <c r="R17" t="n">
-        <v>6949914</v>
+        <v>6950262</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,12 +2454,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119816293</v>
+        <v>119816566</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3186,41 +3186,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489470</v>
+        <v>489390</v>
       </c>
       <c r="R24" t="n">
-        <v>6949911</v>
+        <v>6949914</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3249,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3259,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,22 +3283,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816566</v>
+        <v>119816293</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,50 +3307,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489390</v>
+        <v>489470</v>
       </c>
       <c r="R25" t="n">
-        <v>6949914</v>
+        <v>6949911</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,12 +3395,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119816409</v>
+        <v>119811768</v>
       </c>
       <c r="B37" t="n">
-        <v>74654</v>
+        <v>95478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489456</v>
+        <v>489601</v>
       </c>
       <c r="R37" t="n">
-        <v>6949922</v>
+        <v>6950078</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119811768</v>
+        <v>119816409</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>74654</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,34 +4812,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489601</v>
+        <v>489456</v>
       </c>
       <c r="R38" t="n">
-        <v>6950078</v>
+        <v>6949922</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119811823</v>
+        <v>119811966</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>95478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5166,37 +5166,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489565</v>
+        <v>489533</v>
       </c>
       <c r="R41" t="n">
-        <v>6950090</v>
+        <v>6950117</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5250,22 +5250,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119811744</v>
+        <v>119811823</v>
       </c>
       <c r="B42" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5278,42 +5278,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489626</v>
+        <v>489565</v>
       </c>
       <c r="R42" t="n">
-        <v>6950077</v>
+        <v>6950090</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5342,7 +5337,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5352,7 +5347,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5367,22 +5362,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119816455</v>
+        <v>119811744</v>
       </c>
       <c r="B43" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5391,43 +5386,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489402</v>
+        <v>489626</v>
       </c>
       <c r="R43" t="n">
-        <v>6949888</v>
+        <v>6950077</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5491,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119811058</v>
+        <v>119816455</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,47 +5503,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489643</v>
+        <v>489402</v>
       </c>
       <c r="R44" t="n">
-        <v>6950272</v>
+        <v>6949888</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5617,7 +5608,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119815982</v>
+        <v>119811058</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5652,7 +5643,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5662,14 +5653,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489561</v>
+        <v>489643</v>
       </c>
       <c r="R45" t="n">
-        <v>6949786</v>
+        <v>6950272</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5738,10 +5729,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811966</v>
+        <v>119815982</v>
       </c>
       <c r="B46" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5750,38 +5741,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489533</v>
+        <v>489561</v>
       </c>
       <c r="R46" t="n">
-        <v>6950117</v>
+        <v>6949786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5850,10 +5850,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119811038</v>
+        <v>119811101</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5862,38 +5862,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489668</v>
+        <v>489639</v>
       </c>
       <c r="R47" t="n">
-        <v>6950267</v>
+        <v>6950268</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5925,7 +5930,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5935,7 +5940,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5950,22 +5955,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119816272</v>
+        <v>119811038</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5974,38 +5979,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489537</v>
+        <v>489668</v>
       </c>
       <c r="R48" t="n">
-        <v>6949917</v>
+        <v>6950267</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6037,7 +6042,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6047,7 +6052,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6074,10 +6079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119811101</v>
+        <v>119816272</v>
       </c>
       <c r="B49" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6090,39 +6095,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489639</v>
+        <v>489537</v>
       </c>
       <c r="R49" t="n">
-        <v>6950268</v>
+        <v>6949917</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,12 +6179,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119815992</v>
+        <v>119811924</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7901,47 +7901,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489517</v>
+        <v>489533</v>
       </c>
       <c r="R65" t="n">
-        <v>6949756</v>
+        <v>6950132</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8010,10 +8006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119811924</v>
+        <v>119815992</v>
       </c>
       <c r="B66" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,43 +8018,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489533</v>
+        <v>489517</v>
       </c>
       <c r="R66" t="n">
-        <v>6950132</v>
+        <v>6949756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119849062</v>
+        <v>119850939</v>
       </c>
       <c r="B72" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8722,34 +8722,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489573</v>
+        <v>489367</v>
       </c>
       <c r="R72" t="n">
-        <v>6949724</v>
+        <v>6949918</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8818,10 +8818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119848365</v>
+        <v>119849062</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8834,21 +8834,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489632</v>
+        <v>489573</v>
       </c>
       <c r="R73" t="n">
-        <v>6949678</v>
+        <v>6949724</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8930,7 +8930,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850939</v>
+        <v>119848365</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8966,14 +8966,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489367</v>
+        <v>489632</v>
       </c>
       <c r="R74" t="n">
-        <v>6949918</v>
+        <v>6949678</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119810875</v>
+        <v>119816272</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,47 +1568,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489650</v>
+        <v>489537</v>
       </c>
       <c r="R10" t="n">
-        <v>6950248</v>
+        <v>6949917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,22 +1656,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816490</v>
+        <v>119816036</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,38 +1680,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489416</v>
+        <v>489554</v>
       </c>
       <c r="R11" t="n">
-        <v>6949992</v>
+        <v>6949859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119812494</v>
+        <v>119816869</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,46 +1801,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489516</v>
+        <v>489386</v>
       </c>
       <c r="R12" t="n">
-        <v>6950124</v>
+        <v>6950031</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1889,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119816403</v>
+        <v>119811038</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,41 +1913,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489456</v>
+        <v>489668</v>
       </c>
       <c r="R13" t="n">
-        <v>6949922</v>
+        <v>6950267</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,22 +2001,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816597</v>
+        <v>119816509</v>
       </c>
       <c r="B14" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,41 +2025,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489387</v>
+        <v>489392</v>
       </c>
       <c r="R14" t="n">
-        <v>6949914</v>
+        <v>6949873</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,22 +2122,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119812085</v>
+        <v>119815982</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,38 +2146,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489559</v>
+        <v>489561</v>
       </c>
       <c r="R15" t="n">
-        <v>6950125</v>
+        <v>6949786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119818590</v>
+        <v>119816425</v>
       </c>
       <c r="B16" t="n">
-        <v>79651</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,38 +2267,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489596</v>
+        <v>489432</v>
       </c>
       <c r="R16" t="n">
-        <v>6949748</v>
+        <v>6949876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119811022</v>
+        <v>119812085</v>
       </c>
       <c r="B17" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,21 +2392,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,13 +2416,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489658</v>
+        <v>489559</v>
       </c>
       <c r="R17" t="n">
-        <v>6950262</v>
+        <v>6950125</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,22 +2476,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119811596</v>
+        <v>119816291</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,50 +2500,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489598</v>
+        <v>489475</v>
       </c>
       <c r="R18" t="n">
-        <v>6950085</v>
+        <v>6949863</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,22 +2588,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119811826</v>
+        <v>119816571</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,47 +2612,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489523</v>
+        <v>489386</v>
       </c>
       <c r="R19" t="n">
-        <v>6950130</v>
+        <v>6950002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2700,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119811346</v>
+        <v>119816543</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,37 +2728,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489623</v>
+        <v>489416</v>
       </c>
       <c r="R20" t="n">
-        <v>6950102</v>
+        <v>6949992</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2797,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,22 +2812,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119811204</v>
+        <v>119812106</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,21 +2840,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,13 +2864,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489659</v>
+        <v>489537</v>
       </c>
       <c r="R21" t="n">
-        <v>6950266</v>
+        <v>6950131</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2909,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,19 +2924,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119810849</v>
+        <v>119816402</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2967,7 +2971,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2977,17 +2981,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489644</v>
+        <v>489410</v>
       </c>
       <c r="R22" t="n">
-        <v>6950252</v>
+        <v>6949906</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,19 +3045,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119817114</v>
+        <v>119815902</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3088,7 +3092,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3098,14 +3102,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489487</v>
+        <v>489634</v>
       </c>
       <c r="R23" t="n">
-        <v>6949865</v>
+        <v>6949843</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,10 +3178,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119816566</v>
+        <v>119812494</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3186,50 +3190,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489390</v>
+        <v>489516</v>
       </c>
       <c r="R24" t="n">
-        <v>6949914</v>
+        <v>6950124</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,22 +3283,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119816293</v>
+        <v>119815905</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3307,38 +3307,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489470</v>
+        <v>489652</v>
       </c>
       <c r="R25" t="n">
-        <v>6949911</v>
+        <v>6949845</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119816986</v>
+        <v>119811924</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,47 +3419,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489386</v>
+        <v>489533</v>
       </c>
       <c r="R26" t="n">
-        <v>6950031</v>
+        <v>6950132</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3491,7 +3487,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3497,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3516,22 +3512,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119812106</v>
+        <v>119811422</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3544,34 +3540,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489537</v>
+        <v>489633</v>
       </c>
       <c r="R27" t="n">
-        <v>6950131</v>
+        <v>6950101</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3603,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119816425</v>
+        <v>119817062</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3652,47 +3648,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489432</v>
+        <v>489451</v>
       </c>
       <c r="R28" t="n">
-        <v>6949876</v>
+        <v>6949854</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119816036</v>
+        <v>119819157</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,47 +3760,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489554</v>
+        <v>489563</v>
       </c>
       <c r="R29" t="n">
-        <v>6949859</v>
+        <v>6949770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3845,7 +3823,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3855,7 +3833,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3882,10 +3860,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119811561</v>
+        <v>119816157</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,25 +3872,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3922,13 +3900,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489625</v>
+        <v>489537</v>
       </c>
       <c r="R30" t="n">
-        <v>6950089</v>
+        <v>6949917</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3957,7 +3935,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3967,7 +3945,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,22 +3960,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119815720</v>
+        <v>119816597</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4006,38 +3984,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489670</v>
+        <v>489387</v>
       </c>
       <c r="R31" t="n">
-        <v>6949846</v>
+        <v>6949914</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4106,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119816157</v>
+        <v>119817114</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4118,38 +4096,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489537</v>
+        <v>489487</v>
       </c>
       <c r="R32" t="n">
-        <v>6949917</v>
+        <v>6949865</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4181,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4191,7 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,12 +4193,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4339,10 +4326,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119816571</v>
+        <v>119811966</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,34 +4342,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489386</v>
+        <v>489533</v>
       </c>
       <c r="R34" t="n">
-        <v>6950002</v>
+        <v>6950117</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4414,7 +4401,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4424,7 +4411,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4439,22 +4426,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819157</v>
+        <v>119810849</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4463,41 +4450,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489563</v>
+        <v>489644</v>
       </c>
       <c r="R35" t="n">
-        <v>6949770</v>
+        <v>6950252</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4526,7 +4522,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4536,7 +4532,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4551,19 +4547,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119815902</v>
+        <v>119810875</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4598,7 +4594,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4608,14 +4604,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489634</v>
+        <v>489650</v>
       </c>
       <c r="R36" t="n">
-        <v>6949843</v>
+        <v>6950248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4684,10 +4680,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119811768</v>
+        <v>119816455</v>
       </c>
       <c r="B37" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4696,41 +4692,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489601</v>
+        <v>489402</v>
       </c>
       <c r="R37" t="n">
-        <v>6950078</v>
+        <v>6949888</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4759,7 +4760,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4770,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4784,22 +4785,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119816409</v>
+        <v>119817871</v>
       </c>
       <c r="B38" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,37 +4813,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489456</v>
+        <v>489587</v>
       </c>
       <c r="R38" t="n">
-        <v>6949922</v>
+        <v>6949781</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4896,22 +4897,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119811398</v>
+        <v>119811022</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4920,50 +4921,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489626</v>
+        <v>489658</v>
       </c>
       <c r="R39" t="n">
-        <v>6950077</v>
+        <v>6950262</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4992,7 +4984,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5002,7 +4994,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5017,22 +5009,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119816402</v>
+        <v>119816403</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,50 +5033,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489410</v>
+        <v>489456</v>
       </c>
       <c r="R40" t="n">
-        <v>6949906</v>
+        <v>6949922</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5113,7 +5096,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5106,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5138,22 +5121,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119811966</v>
+        <v>119813023</v>
       </c>
       <c r="B41" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5166,34 +5149,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489533</v>
+        <v>489483</v>
       </c>
       <c r="R41" t="n">
-        <v>6950117</v>
+        <v>6950017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5225,7 +5208,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5235,7 +5218,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5250,22 +5233,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119811823</v>
+        <v>119816409</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5278,34 +5261,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489565</v>
+        <v>489456</v>
       </c>
       <c r="R42" t="n">
-        <v>6950090</v>
+        <v>6949922</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5337,7 +5320,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5347,7 +5330,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5374,10 +5357,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119811744</v>
+        <v>119816697</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5390,39 +5373,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489626</v>
+        <v>489413</v>
       </c>
       <c r="R43" t="n">
-        <v>6950077</v>
+        <v>6949932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5491,10 +5469,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119816455</v>
+        <v>119811561</v>
       </c>
       <c r="B44" t="n">
-        <v>56532</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5503,46 +5481,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489402</v>
+        <v>489625</v>
       </c>
       <c r="R44" t="n">
-        <v>6949888</v>
+        <v>6950089</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5571,7 +5544,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5581,7 +5554,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5596,19 +5569,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119811058</v>
+        <v>119815992</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5643,7 +5616,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5653,14 +5626,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489643</v>
+        <v>489517</v>
       </c>
       <c r="R45" t="n">
-        <v>6950272</v>
+        <v>6949756</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5729,10 +5702,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119815982</v>
+        <v>119811101</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5741,47 +5714,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489561</v>
+        <v>489639</v>
       </c>
       <c r="R46" t="n">
-        <v>6949786</v>
+        <v>6950268</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5850,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119811101</v>
+        <v>119811943</v>
       </c>
       <c r="B47" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5866,39 +5835,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489639</v>
+        <v>489659</v>
       </c>
       <c r="R47" t="n">
-        <v>6950268</v>
+        <v>6950266</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5930,7 +5894,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5940,7 +5904,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5955,22 +5919,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119811038</v>
+        <v>119818590</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>79651</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5979,38 +5943,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489668</v>
+        <v>489596</v>
       </c>
       <c r="R48" t="n">
-        <v>6950267</v>
+        <v>6949748</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6042,7 +6006,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6052,7 +6016,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6067,22 +6031,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119816272</v>
+        <v>119819067</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6095,37 +6059,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489537</v>
+        <v>489590</v>
       </c>
       <c r="R49" t="n">
-        <v>6949917</v>
+        <v>6949764</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6154,7 +6118,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6164,7 +6128,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,22 +6143,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119815905</v>
+        <v>119811826</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6203,41 +6167,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489652</v>
+        <v>489523</v>
       </c>
       <c r="R50" t="n">
-        <v>6949845</v>
+        <v>6950130</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6266,7 +6239,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6276,7 +6249,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6291,22 +6264,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119813023</v>
+        <v>119811346</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6319,37 +6292,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489483</v>
+        <v>489623</v>
       </c>
       <c r="R51" t="n">
-        <v>6950017</v>
+        <v>6950102</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6378,7 +6351,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6388,7 +6361,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6403,22 +6376,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119815859</v>
+        <v>119811744</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6431,34 +6404,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489648</v>
+        <v>489626</v>
       </c>
       <c r="R52" t="n">
-        <v>6949845</v>
+        <v>6950077</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6490,7 +6468,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6500,7 +6478,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6515,22 +6493,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119811103</v>
+        <v>119816293</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6543,34 +6521,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489639</v>
+        <v>489470</v>
       </c>
       <c r="R53" t="n">
-        <v>6950275</v>
+        <v>6949911</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6602,7 +6580,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6612,7 +6590,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6639,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119811422</v>
+        <v>119815720</v>
       </c>
       <c r="B54" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6655,21 +6633,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6679,13 +6657,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489633</v>
+        <v>489670</v>
       </c>
       <c r="R54" t="n">
-        <v>6950101</v>
+        <v>6949846</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6714,7 +6692,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6724,7 +6702,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6739,22 +6717,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119815546</v>
+        <v>119813032</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6767,34 +6745,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489670</v>
+        <v>489482</v>
       </c>
       <c r="R55" t="n">
-        <v>6949842</v>
+        <v>6950030</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6826,7 +6804,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6836,7 +6814,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6863,10 +6841,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119816291</v>
+        <v>119811823</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6879,37 +6857,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489475</v>
+        <v>489565</v>
       </c>
       <c r="R56" t="n">
-        <v>6949863</v>
+        <v>6950090</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6938,7 +6916,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6948,7 +6926,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6963,22 +6941,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119819067</v>
+        <v>119811768</v>
       </c>
       <c r="B57" t="n">
-        <v>74654</v>
+        <v>95478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6991,34 +6969,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489590</v>
+        <v>489601</v>
       </c>
       <c r="R57" t="n">
-        <v>6949764</v>
+        <v>6950078</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7050,7 +7028,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7060,7 +7038,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7087,10 +7065,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119816697</v>
+        <v>119811103</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7103,37 +7081,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489413</v>
+        <v>489639</v>
       </c>
       <c r="R58" t="n">
-        <v>6949932</v>
+        <v>6950275</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,7 +7140,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7172,7 +7150,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7187,22 +7165,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119813032</v>
+        <v>119816718</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7215,21 +7193,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7239,10 +7217,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489482</v>
+        <v>489390</v>
       </c>
       <c r="R59" t="n">
-        <v>6950030</v>
+        <v>6949929</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7274,7 +7252,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7284,7 +7262,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7311,7 +7289,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119816509</v>
+        <v>119811596</v>
       </c>
       <c r="B60" t="n">
         <v>97930</v>
@@ -7356,14 +7334,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489392</v>
+        <v>489598</v>
       </c>
       <c r="R60" t="n">
-        <v>6949873</v>
+        <v>6950085</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7395,7 +7373,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7405,7 +7383,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7553,10 +7531,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119817062</v>
+        <v>119816566</v>
       </c>
       <c r="B62" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7565,38 +7543,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489451</v>
+        <v>489390</v>
       </c>
       <c r="R62" t="n">
-        <v>6949854</v>
+        <v>6949914</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7665,10 +7652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119817871</v>
+        <v>119811398</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7677,38 +7664,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489587</v>
+        <v>489626</v>
       </c>
       <c r="R63" t="n">
-        <v>6949781</v>
+        <v>6950077</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7777,10 +7773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119816718</v>
+        <v>119811058</v>
       </c>
       <c r="B64" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7789,41 +7785,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489390</v>
+        <v>489643</v>
       </c>
       <c r="R64" t="n">
-        <v>6949929</v>
+        <v>6950272</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7852,7 +7857,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7862,7 +7867,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7877,22 +7882,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119811924</v>
+        <v>119815546</v>
       </c>
       <c r="B65" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7905,42 +7910,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489533</v>
+        <v>489670</v>
       </c>
       <c r="R65" t="n">
-        <v>6950132</v>
+        <v>6949842</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,22 +7994,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119815992</v>
+        <v>119815859</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8018,47 +8018,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489517</v>
+        <v>489648</v>
       </c>
       <c r="R66" t="n">
-        <v>6949756</v>
+        <v>6949845</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8090,7 +8081,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8100,7 +8091,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8115,22 +8106,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119851683</v>
+        <v>119848594</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8143,34 +8134,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489314</v>
+        <v>489615</v>
       </c>
       <c r="R67" t="n">
-        <v>6950058</v>
+        <v>6949709</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8202,7 +8193,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8212,7 +8203,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8239,10 +8230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119852338</v>
+        <v>119848733</v>
       </c>
       <c r="B68" t="n">
-        <v>56532</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8251,60 +8242,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489485</v>
+        <v>489600</v>
       </c>
       <c r="R68" t="n">
-        <v>6950055</v>
+        <v>6949713</v>
       </c>
       <c r="S68" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8333,7 +8305,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8343,7 +8315,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8370,10 +8342,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119850950</v>
+        <v>119849865</v>
       </c>
       <c r="B69" t="n">
-        <v>82321</v>
+        <v>57689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8382,41 +8354,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489367</v>
+        <v>489413</v>
       </c>
       <c r="R69" t="n">
-        <v>6949918</v>
+        <v>6949801</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8445,7 +8431,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8455,7 +8441,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8482,10 +8473,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119848594</v>
+        <v>119848818</v>
       </c>
       <c r="B70" t="n">
-        <v>74654</v>
+        <v>90594</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8498,21 +8489,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8522,10 +8513,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489615</v>
+        <v>489593</v>
       </c>
       <c r="R70" t="n">
-        <v>6949709</v>
+        <v>6949732</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8557,7 +8548,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8567,7 +8558,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8594,10 +8585,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119848818</v>
+        <v>119850950</v>
       </c>
       <c r="B71" t="n">
-        <v>90594</v>
+        <v>82321</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8610,34 +8601,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489593</v>
+        <v>489367</v>
       </c>
       <c r="R71" t="n">
-        <v>6949732</v>
+        <v>6949918</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8669,7 +8660,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8679,7 +8670,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8706,10 +8697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850939</v>
+        <v>119849062</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8722,34 +8713,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489367</v>
+        <v>489573</v>
       </c>
       <c r="R72" t="n">
-        <v>6949918</v>
+        <v>6949724</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8781,7 +8772,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8791,7 +8782,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8818,10 +8809,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119849062</v>
+        <v>119848365</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8834,21 +8825,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8858,10 +8849,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489573</v>
+        <v>489632</v>
       </c>
       <c r="R73" t="n">
-        <v>6949724</v>
+        <v>6949678</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8893,7 +8884,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8903,7 +8894,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8930,10 +8921,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119848365</v>
+        <v>119852547</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8946,34 +8937,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489632</v>
+        <v>489584</v>
       </c>
       <c r="R74" t="n">
-        <v>6949678</v>
+        <v>6949881</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9005,7 +8996,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9015,7 +9006,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9042,10 +9033,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119848733</v>
+        <v>119851683</v>
       </c>
       <c r="B75" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9058,34 +9049,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489600</v>
+        <v>489314</v>
       </c>
       <c r="R75" t="n">
-        <v>6949713</v>
+        <v>6950058</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9117,7 +9108,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9127,7 +9118,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9154,7 +9145,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851248</v>
+        <v>119852071</v>
       </c>
       <c r="B76" t="n">
         <v>82321</v>
@@ -9194,10 +9185,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489366</v>
+        <v>489392</v>
       </c>
       <c r="R76" t="n">
-        <v>6949996</v>
+        <v>6950011</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -9229,7 +9220,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9239,7 +9230,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9266,10 +9257,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851578</v>
+        <v>119850649</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9282,21 +9273,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9306,10 +9297,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489328</v>
+        <v>489406</v>
       </c>
       <c r="R77" t="n">
-        <v>6950055</v>
+        <v>6949790</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9341,7 +9332,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9351,7 +9342,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9378,10 +9369,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119849171</v>
+        <v>119849489</v>
       </c>
       <c r="B78" t="n">
-        <v>79659</v>
+        <v>82321</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9390,25 +9381,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9418,10 +9409,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489554</v>
+        <v>489516</v>
       </c>
       <c r="R78" t="n">
-        <v>6949730</v>
+        <v>6949768</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9453,7 +9444,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9463,7 +9454,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9490,7 +9481,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119852547</v>
+        <v>119848688</v>
       </c>
       <c r="B79" t="n">
         <v>74654</v>
@@ -9526,14 +9517,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489584</v>
+        <v>489614</v>
       </c>
       <c r="R79" t="n">
-        <v>6949881</v>
+        <v>6949692</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9565,7 +9556,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9575,7 +9566,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9602,10 +9593,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851194</v>
+        <v>119849171</v>
       </c>
       <c r="B80" t="n">
-        <v>82321</v>
+        <v>79659</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9614,38 +9605,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489391</v>
+        <v>489554</v>
       </c>
       <c r="R80" t="n">
-        <v>6949965</v>
+        <v>6949730</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9677,7 +9668,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9687,7 +9678,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9714,7 +9705,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119852071</v>
+        <v>119851194</v>
       </c>
       <c r="B81" t="n">
         <v>82321</v>
@@ -9754,10 +9745,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489392</v>
+        <v>489391</v>
       </c>
       <c r="R81" t="n">
-        <v>6950011</v>
+        <v>6949965</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9789,7 +9780,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9799,7 +9790,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9826,7 +9817,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850649</v>
+        <v>119850939</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -9866,10 +9857,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489406</v>
+        <v>489367</v>
       </c>
       <c r="R82" t="n">
-        <v>6949790</v>
+        <v>6949918</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9901,7 +9892,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9911,7 +9902,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9938,10 +9929,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119849865</v>
+        <v>119851248</v>
       </c>
       <c r="B83" t="n">
-        <v>57689</v>
+        <v>82321</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9950,55 +9941,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489413</v>
+        <v>489366</v>
       </c>
       <c r="R83" t="n">
-        <v>6949801</v>
+        <v>6949996</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10027,7 +10004,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10037,12 +10014,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10069,10 +10041,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119848688</v>
+        <v>119852338</v>
       </c>
       <c r="B84" t="n">
-        <v>74654</v>
+        <v>56532</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10081,41 +10053,60 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489614</v>
+        <v>489485</v>
       </c>
       <c r="R84" t="n">
-        <v>6949692</v>
+        <v>6950055</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10144,7 +10135,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10154,7 +10145,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10181,10 +10172,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849489</v>
+        <v>119851578</v>
       </c>
       <c r="B85" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10197,34 +10188,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489516</v>
+        <v>489328</v>
       </c>
       <c r="R85" t="n">
-        <v>6949768</v>
+        <v>6950055</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10256,7 +10247,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10266,7 +10257,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -8473,10 +8473,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119848818</v>
+        <v>119850950</v>
       </c>
       <c r="B70" t="n">
-        <v>90594</v>
+        <v>82321</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8489,34 +8489,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489593</v>
+        <v>489367</v>
       </c>
       <c r="R70" t="n">
-        <v>6949732</v>
+        <v>6949918</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8585,10 +8585,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119850950</v>
+        <v>119848818</v>
       </c>
       <c r="B71" t="n">
-        <v>82321</v>
+        <v>90594</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8601,34 +8601,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489367</v>
+        <v>489593</v>
       </c>
       <c r="R71" t="n">
-        <v>6949918</v>
+        <v>6949732</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8809,10 +8809,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119848365</v>
+        <v>119852547</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8825,34 +8825,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489632</v>
+        <v>489584</v>
       </c>
       <c r="R73" t="n">
-        <v>6949678</v>
+        <v>6949881</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8921,10 +8921,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119852547</v>
+        <v>119848365</v>
       </c>
       <c r="B74" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8937,34 +8937,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489584</v>
+        <v>489632</v>
       </c>
       <c r="R74" t="n">
-        <v>6949881</v>
+        <v>6949678</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9481,10 +9481,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119848688</v>
+        <v>119851194</v>
       </c>
       <c r="B79" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9497,34 +9497,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489614</v>
+        <v>489391</v>
       </c>
       <c r="R79" t="n">
-        <v>6949692</v>
+        <v>6949965</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9705,10 +9705,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119851194</v>
+        <v>119848688</v>
       </c>
       <c r="B81" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9721,34 +9721,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489391</v>
+        <v>489614</v>
       </c>
       <c r="R81" t="n">
-        <v>6949965</v>
+        <v>6949692</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -8118,10 +8118,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119848594</v>
+        <v>119849865</v>
       </c>
       <c r="B67" t="n">
-        <v>74654</v>
+        <v>57689</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8130,41 +8130,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489615</v>
+        <v>489413</v>
       </c>
       <c r="R67" t="n">
-        <v>6949709</v>
+        <v>6949801</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8193,7 +8207,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8203,7 +8217,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8230,10 +8249,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119848733</v>
+        <v>119849062</v>
       </c>
       <c r="B68" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8246,21 +8265,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8270,10 +8289,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489600</v>
+        <v>489573</v>
       </c>
       <c r="R68" t="n">
-        <v>6949713</v>
+        <v>6949724</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8305,7 +8324,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8315,7 +8334,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8342,10 +8361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119849865</v>
+        <v>119848733</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>90598</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8354,55 +8373,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489413</v>
+        <v>489600</v>
       </c>
       <c r="R69" t="n">
-        <v>6949801</v>
+        <v>6949713</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8431,7 +8436,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8441,12 +8446,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8473,10 +8473,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119850950</v>
+        <v>119851578</v>
       </c>
       <c r="B70" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8489,21 +8489,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489367</v>
+        <v>489328</v>
       </c>
       <c r="R70" t="n">
-        <v>6949918</v>
+        <v>6950055</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8585,10 +8585,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119848818</v>
+        <v>119851248</v>
       </c>
       <c r="B71" t="n">
-        <v>90594</v>
+        <v>82321</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8601,34 +8601,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489593</v>
+        <v>489366</v>
       </c>
       <c r="R71" t="n">
-        <v>6949732</v>
+        <v>6949996</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8697,10 +8697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119849062</v>
+        <v>119852071</v>
       </c>
       <c r="B72" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8713,34 +8713,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489573</v>
+        <v>489392</v>
       </c>
       <c r="R72" t="n">
-        <v>6949724</v>
+        <v>6950011</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8809,10 +8809,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119852547</v>
+        <v>119848365</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8825,34 +8825,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489584</v>
+        <v>489632</v>
       </c>
       <c r="R73" t="n">
-        <v>6949881</v>
+        <v>6949678</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8921,7 +8921,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119848365</v>
+        <v>119850939</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8957,14 +8957,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489632</v>
+        <v>489367</v>
       </c>
       <c r="R74" t="n">
-        <v>6949678</v>
+        <v>6949918</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9033,10 +9033,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119851683</v>
+        <v>119848594</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9049,34 +9049,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489314</v>
+        <v>489615</v>
       </c>
       <c r="R75" t="n">
-        <v>6950058</v>
+        <v>6949709</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9145,10 +9145,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119852071</v>
+        <v>119850649</v>
       </c>
       <c r="B76" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9161,21 +9161,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9185,10 +9185,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489392</v>
+        <v>489406</v>
       </c>
       <c r="R76" t="n">
-        <v>6950011</v>
+        <v>6949790</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9257,10 +9257,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119850649</v>
+        <v>119848818</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9273,34 +9273,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489406</v>
+        <v>489593</v>
       </c>
       <c r="R77" t="n">
-        <v>6949790</v>
+        <v>6949732</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9481,10 +9481,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851194</v>
+        <v>119852338</v>
       </c>
       <c r="B79" t="n">
-        <v>82321</v>
+        <v>56532</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9493,41 +9493,60 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489391</v>
+        <v>489485</v>
       </c>
       <c r="R79" t="n">
-        <v>6949965</v>
+        <v>6950055</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9556,7 +9575,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9566,7 +9585,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9817,7 +9836,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850939</v>
+        <v>119851683</v>
       </c>
       <c r="B82" t="n">
         <v>78542</v>
@@ -9857,10 +9876,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489367</v>
+        <v>489314</v>
       </c>
       <c r="R82" t="n">
-        <v>6949918</v>
+        <v>6950058</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9892,7 +9911,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9902,7 +9921,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9929,10 +9948,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851248</v>
+        <v>119852547</v>
       </c>
       <c r="B83" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9945,34 +9964,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489366</v>
+        <v>489584</v>
       </c>
       <c r="R83" t="n">
-        <v>6949996</v>
+        <v>6949881</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -10004,7 +10023,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10014,7 +10033,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10041,10 +10060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119852338</v>
+        <v>119851194</v>
       </c>
       <c r="B84" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10053,60 +10072,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489485</v>
+        <v>489391</v>
       </c>
       <c r="R84" t="n">
-        <v>6950055</v>
+        <v>6949965</v>
       </c>
       <c r="S84" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10172,10 +10172,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119851578</v>
+        <v>119850950</v>
       </c>
       <c r="B85" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10188,21 +10188,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489328</v>
+        <v>489367</v>
       </c>
       <c r="R85" t="n">
-        <v>6950055</v>
+        <v>6949918</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10282,6 +10282,245 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121702304</v>
+      </c>
+      <c r="B86" t="n">
+        <v>55959</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>489446</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6949920</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121702691</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57357</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>489502</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6949992</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10284,10 +10284,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121702304</v>
+        <v>121702691</v>
       </c>
       <c r="B86" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10300,27 +10300,32 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10329,13 +10334,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489446</v>
+        <v>489502</v>
       </c>
       <c r="R86" t="n">
-        <v>6949920</v>
+        <v>6949992</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10364,7 +10369,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10379,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10401,10 +10406,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121702691</v>
+        <v>121702304</v>
       </c>
       <c r="B87" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10417,32 +10422,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489502</v>
+        <v>489446</v>
       </c>
       <c r="R87" t="n">
-        <v>6949992</v>
+        <v>6949920</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10284,10 +10284,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121702691</v>
+        <v>121702304</v>
       </c>
       <c r="B86" t="n">
-        <v>57357</v>
+        <v>55959</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10300,32 +10300,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10334,13 +10329,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489502</v>
+        <v>489446</v>
       </c>
       <c r="R86" t="n">
-        <v>6949992</v>
+        <v>6949920</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10369,7 +10364,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10379,7 +10374,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10406,10 +10401,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121702304</v>
+        <v>121702691</v>
       </c>
       <c r="B87" t="n">
-        <v>55959</v>
+        <v>57357</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10422,27 +10417,32 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489446</v>
+        <v>489502</v>
       </c>
       <c r="R87" t="n">
-        <v>6949920</v>
+        <v>6949992</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10633,6 +10633,448 @@
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>130228933</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>489377</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6949891</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130229051</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>489372</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6949896</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>130229400</v>
+      </c>
+      <c r="B91" t="n">
+        <v>56931</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Källmyren, Källmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>489591</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6950201</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>130228419</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92359</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>489596</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6950061</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10635,10 +10635,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130228933</v>
+        <v>130229051</v>
       </c>
       <c r="B89" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,26 +10663,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489377</v>
+        <v>489372</v>
       </c>
       <c r="R89" t="n">
-        <v>6949891</v>
+        <v>6949896</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10714,7 +10705,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10724,7 +10715,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10751,10 +10742,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B90" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10779,17 +10770,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R90" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10861,7 +10861,7 @@
         <v>130229400</v>
       </c>
       <c r="B91" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10638,7 +10638,7 @@
         <v>130228933</v>
       </c>
       <c r="B89" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>130229051</v>
       </c>
       <c r="B90" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10638,7 +10638,7 @@
         <v>130228933</v>
       </c>
       <c r="B89" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>130229051</v>
       </c>
       <c r="B90" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>130229400</v>
       </c>
       <c r="B91" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10635,10 +10635,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130228933</v>
+        <v>130229051</v>
       </c>
       <c r="B89" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,26 +10663,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489377</v>
+        <v>489372</v>
       </c>
       <c r="R89" t="n">
-        <v>6949891</v>
+        <v>6949896</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10714,7 +10705,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10724,7 +10715,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10751,10 +10742,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B90" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10779,17 +10770,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R90" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10635,10 +10635,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B89" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,17 +10663,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R89" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10705,7 +10714,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10715,7 +10724,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10742,10 +10751,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130228933</v>
+        <v>130229051</v>
       </c>
       <c r="B90" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10770,26 +10779,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489377</v>
+        <v>489372</v>
       </c>
       <c r="R90" t="n">
-        <v>6949891</v>
+        <v>6949896</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10635,10 +10635,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130228933</v>
+        <v>130229051</v>
       </c>
       <c r="B89" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,26 +10663,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489377</v>
+        <v>489372</v>
       </c>
       <c r="R89" t="n">
-        <v>6949891</v>
+        <v>6949896</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10714,7 +10705,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10724,7 +10715,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10751,10 +10742,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B90" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10779,17 +10770,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R90" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10861,7 +10861,7 @@
         <v>130229400</v>
       </c>
       <c r="B91" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -10635,10 +10635,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B89" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,17 +10663,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R89" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10705,7 +10714,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10715,7 +10724,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10742,10 +10751,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130228933</v>
+        <v>130229051</v>
       </c>
       <c r="B90" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10770,26 +10779,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489377</v>
+        <v>489372</v>
       </c>
       <c r="R90" t="n">
-        <v>6949891</v>
+        <v>6949896</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10973,7 +10973,7 @@
         <v>130228419</v>
       </c>
       <c r="B92" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115598923</v>
+        <v>119811022</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489536</v>
+        <v>489658</v>
       </c>
       <c r="R2" t="n">
-        <v>6950097</v>
+        <v>6950262</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115599985</v>
+        <v>119811768</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489536</v>
+        <v>489601</v>
       </c>
       <c r="R3" t="n">
-        <v>6950097</v>
+        <v>6950078</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,65 +877,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115600853</v>
+        <v>119811966</v>
       </c>
       <c r="B4" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1642</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489536</v>
+        <v>489533</v>
       </c>
       <c r="R4" t="n">
-        <v>6950097</v>
+        <v>6950117</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115597799</v>
+        <v>119812106</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489536</v>
+        <v>489537</v>
       </c>
       <c r="R5" t="n">
-        <v>6950097</v>
+        <v>6950131</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,17 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,27 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117566267</v>
+        <v>119811422</v>
       </c>
       <c r="B6" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489669</v>
+        <v>489633</v>
       </c>
       <c r="R6" t="n">
-        <v>6949829</v>
+        <v>6950101</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,27 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117566902</v>
+        <v>119811103</v>
       </c>
       <c r="B7" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,37 +1221,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen (Källmyrtjärnen), Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489669</v>
+        <v>489639</v>
       </c>
       <c r="R7" t="n">
-        <v>6949829</v>
+        <v>6950275</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,27 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119244889</v>
+        <v>119811346</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,37 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489479</v>
+        <v>489623</v>
       </c>
       <c r="R8" t="n">
-        <v>6949818</v>
+        <v>6950102</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,27 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119245053</v>
+        <v>119811561</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,37 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489479</v>
+        <v>489625</v>
       </c>
       <c r="R9" t="n">
-        <v>6949818</v>
+        <v>6950089</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,27 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119816272</v>
+        <v>119812085</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,34 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489537</v>
+        <v>489559</v>
       </c>
       <c r="R10" t="n">
-        <v>6949917</v>
+        <v>6950125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,74 +1626,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816036</v>
+        <v>119813032</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489554</v>
+        <v>489482</v>
       </c>
       <c r="R11" t="n">
-        <v>6949859</v>
+        <v>6950030</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,27 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119816869</v>
+        <v>119848818</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,37 +1756,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489386</v>
+        <v>489593</v>
       </c>
       <c r="R12" t="n">
-        <v>6950031</v>
+        <v>6949732</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,22 +1810,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,65 +1840,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119811038</v>
+        <v>119816403</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489668</v>
+        <v>489456</v>
       </c>
       <c r="R13" t="n">
-        <v>6950267</v>
+        <v>6949922</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,71 +1947,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816509</v>
+        <v>119849489</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489392</v>
+        <v>489516</v>
       </c>
       <c r="R14" t="n">
-        <v>6949873</v>
+        <v>6949768</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2092,22 +2024,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,62 +2066,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119815982</v>
+        <v>119850950</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489561</v>
+        <v>489367</v>
       </c>
       <c r="R15" t="n">
-        <v>6949786</v>
+        <v>6949918</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,22 +2131,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,74 +2161,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816425</v>
+        <v>119851194</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489432</v>
+        <v>489391</v>
       </c>
       <c r="R16" t="n">
-        <v>6949876</v>
+        <v>6949965</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,27 +2268,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119812085</v>
+        <v>119851248</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,37 +2291,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489559</v>
+        <v>489366</v>
       </c>
       <c r="R17" t="n">
-        <v>6950125</v>
+        <v>6949996</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2446,22 +2345,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,27 +2375,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816291</v>
+        <v>119852071</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489475</v>
+        <v>489392</v>
       </c>
       <c r="R18" t="n">
-        <v>6949863</v>
+        <v>6950011</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,22 +2452,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,62 +2482,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119816571</v>
+        <v>130228419</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489386</v>
+        <v>489596</v>
       </c>
       <c r="R19" t="n">
-        <v>6950002</v>
+        <v>6950061</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,22 +2559,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,27 +2589,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816543</v>
+        <v>119816157</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,34 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489416</v>
+        <v>489537</v>
       </c>
       <c r="R20" t="n">
-        <v>6949992</v>
+        <v>6949917</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2797,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,15 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119812106</v>
+        <v>117566267</v>
       </c>
       <c r="B21" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2840,37 +2719,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489537</v>
+        <v>489669</v>
       </c>
       <c r="R21" t="n">
-        <v>6950131</v>
+        <v>6949829</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2894,22 +2773,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,74 +2803,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119816402</v>
+        <v>119815905</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489410</v>
+        <v>489652</v>
       </c>
       <c r="R22" t="n">
-        <v>6949906</v>
+        <v>6949845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,27 +2910,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119815902</v>
+        <v>117566902</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3073,43 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489634</v>
+        <v>489669</v>
       </c>
       <c r="R23" t="n">
-        <v>6949843</v>
+        <v>6949829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3136,22 +2987,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3166,70 +3017,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119812494</v>
+        <v>119244889</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489516</v>
+        <v>489479</v>
       </c>
       <c r="R24" t="n">
-        <v>6950124</v>
+        <v>6949818</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3253,22 +3094,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,49 +3124,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119815905</v>
+        <v>119815546</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3335,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489652</v>
+        <v>489670</v>
       </c>
       <c r="R25" t="n">
-        <v>6949845</v>
+        <v>6949842</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3370,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,55 +3243,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119811924</v>
+        <v>119815720</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489533</v>
+        <v>489670</v>
       </c>
       <c r="R26" t="n">
-        <v>6950132</v>
+        <v>6949846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3524,37 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119811422</v>
+        <v>119815859</v>
       </c>
       <c r="B27" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3564,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489633</v>
+        <v>489648</v>
       </c>
       <c r="R27" t="n">
-        <v>6950101</v>
+        <v>6949845</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3599,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,62 +3445,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119817062</v>
+        <v>119816272</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489451</v>
+        <v>489537</v>
       </c>
       <c r="R28" t="n">
-        <v>6949854</v>
+        <v>6949917</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3711,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3721,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3736,31 +3552,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819157</v>
+        <v>119816291</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3784,14 +3595,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489563</v>
+        <v>489475</v>
       </c>
       <c r="R29" t="n">
-        <v>6949770</v>
+        <v>6949863</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3823,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3833,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,53 +3671,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119816157</v>
+        <v>119816293</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489537</v>
+        <v>489470</v>
       </c>
       <c r="R30" t="n">
-        <v>6949917</v>
+        <v>6949911</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3935,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3945,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,49 +3766,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119816597</v>
+        <v>119816490</v>
       </c>
       <c r="B31" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489387</v>
+        <v>489416</v>
       </c>
       <c r="R31" t="n">
-        <v>6949914</v>
+        <v>6949992</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4047,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4072,27 +3873,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119817114</v>
+        <v>119816571</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,43 +3896,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489487</v>
+        <v>489386</v>
       </c>
       <c r="R32" t="n">
-        <v>6949865</v>
+        <v>6950002</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4168,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4193,27 +3980,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119812008</v>
+        <v>119816697</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4221,43 +4003,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489528</v>
+        <v>489413</v>
       </c>
       <c r="R33" t="n">
-        <v>6950124</v>
+        <v>6949932</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,50 +4099,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119811966</v>
+        <v>119817871</v>
       </c>
       <c r="B34" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489533</v>
+        <v>489587</v>
       </c>
       <c r="R34" t="n">
-        <v>6950117</v>
+        <v>6949781</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4438,15 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119810849</v>
+        <v>119819157</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4454,46 +4217,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489644</v>
+        <v>489563</v>
       </c>
       <c r="R35" t="n">
-        <v>6950252</v>
+        <v>6949770</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4522,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4532,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,27 +4301,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119810875</v>
+        <v>119848365</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4575,46 +4324,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489650</v>
+        <v>489632</v>
       </c>
       <c r="R36" t="n">
-        <v>6950248</v>
+        <v>6949678</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4638,22 +4378,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,70 +4408,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119816455</v>
+        <v>119850649</v>
       </c>
       <c r="B37" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489402</v>
+        <v>489406</v>
       </c>
       <c r="R37" t="n">
-        <v>6949888</v>
+        <v>6949790</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4755,22 +4485,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,31 +4515,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119817871</v>
+        <v>119850939</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4833,17 +4558,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489587</v>
+        <v>489367</v>
       </c>
       <c r="R38" t="n">
-        <v>6949781</v>
+        <v>6949918</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4867,22 +4592,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4897,62 +4622,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119811022</v>
+        <v>119851683</v>
       </c>
       <c r="B39" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489658</v>
+        <v>489314</v>
       </c>
       <c r="R39" t="n">
-        <v>6950262</v>
+        <v>6950058</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4979,22 +4699,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,15 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119816403</v>
+        <v>119816409</v>
       </c>
       <c r="B40" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5037,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5096,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5106,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5133,15 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119813023</v>
+        <v>119819067</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5149,37 +4859,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489483</v>
+        <v>489590</v>
       </c>
       <c r="R41" t="n">
-        <v>6950017</v>
+        <v>6949764</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5208,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5218,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5233,27 +4943,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119816409</v>
+        <v>119848594</v>
       </c>
       <c r="B42" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5281,14 +4986,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489456</v>
+        <v>489615</v>
       </c>
       <c r="R42" t="n">
-        <v>6949922</v>
+        <v>6949709</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5315,22 +5020,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,15 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119816697</v>
+        <v>119848688</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5373,37 +5073,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489413</v>
+        <v>489614</v>
       </c>
       <c r="R43" t="n">
-        <v>6949932</v>
+        <v>6949692</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5427,22 +5127,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5457,27 +5157,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119811561</v>
+        <v>119849062</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5485,34 +5180,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489625</v>
+        <v>489573</v>
       </c>
       <c r="R44" t="n">
-        <v>6950089</v>
+        <v>6949724</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5539,22 +5234,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5581,62 +5276,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119815992</v>
+        <v>119852547</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>489517</v>
+        <v>489584</v>
       </c>
       <c r="R45" t="n">
-        <v>6949756</v>
+        <v>6949881</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5660,22 +5341,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,27 +5371,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119811101</v>
+        <v>119817062</v>
       </c>
       <c r="B46" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5718,39 +5394,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>489639</v>
+        <v>489451</v>
       </c>
       <c r="R46" t="n">
-        <v>6950268</v>
+        <v>6949854</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5819,15 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119811943</v>
+        <v>115598923</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,37 +5501,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>489659</v>
+        <v>489536</v>
       </c>
       <c r="R47" t="n">
-        <v>6950266</v>
+        <v>6950097</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5889,22 +5555,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5931,37 +5587,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119818590</v>
+        <v>119245053</v>
       </c>
       <c r="B48" t="n">
-        <v>79651</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5971,10 +5622,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>489596</v>
+        <v>489479</v>
       </c>
       <c r="R48" t="n">
-        <v>6949748</v>
+        <v>6949818</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6001,22 +5652,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6031,27 +5682,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119819067</v>
+        <v>119813023</v>
       </c>
       <c r="B49" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,37 +5705,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>489590</v>
+        <v>489483</v>
       </c>
       <c r="R49" t="n">
-        <v>6949764</v>
+        <v>6950017</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6118,7 +5764,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6128,7 +5774,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,74 +5789,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119811826</v>
+        <v>119851578</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>489523</v>
+        <v>489328</v>
       </c>
       <c r="R50" t="n">
-        <v>6950130</v>
+        <v>6950055</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6234,22 +5866,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,65 +5896,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119811346</v>
+        <v>119818590</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>489623</v>
+        <v>489596</v>
       </c>
       <c r="R51" t="n">
-        <v>6950102</v>
+        <v>6949748</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6351,7 +5978,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6361,7 +5988,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,70 +6003,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119811744</v>
+        <v>119849171</v>
       </c>
       <c r="B52" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>489626</v>
+        <v>489554</v>
       </c>
       <c r="R52" t="n">
-        <v>6950077</v>
+        <v>6949730</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6463,22 +6080,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6493,65 +6110,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119816293</v>
+        <v>115599985</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489470</v>
+        <v>489536</v>
       </c>
       <c r="R53" t="n">
-        <v>6949911</v>
+        <v>6950097</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6575,22 +6187,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6605,62 +6217,62 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119815720</v>
+        <v>119811101</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489670</v>
+        <v>489639</v>
       </c>
       <c r="R54" t="n">
-        <v>6949846</v>
+        <v>6950268</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6729,53 +6341,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119813032</v>
+        <v>119811744</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489482</v>
+        <v>489626</v>
       </c>
       <c r="R55" t="n">
-        <v>6950030</v>
+        <v>6950077</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6804,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6814,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6829,27 +6441,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119811823</v>
+        <v>115597799</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6857,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6881,13 +6488,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489565</v>
+        <v>489536</v>
       </c>
       <c r="R56" t="n">
-        <v>6950090</v>
+        <v>6950097</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6911,22 +6518,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6941,27 +6543,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119811768</v>
+        <v>119812494</v>
       </c>
       <c r="B57" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6969,34 +6566,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489601</v>
+        <v>489516</v>
       </c>
       <c r="R57" t="n">
-        <v>6950078</v>
+        <v>6950124</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -7028,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7038,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7065,15 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119811103</v>
+        <v>121702691</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7081,37 +6678,47 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489639</v>
+        <v>489502</v>
       </c>
       <c r="R58" t="n">
-        <v>6950275</v>
+        <v>6949992</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7135,22 +6742,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7177,53 +6784,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119816718</v>
+        <v>119816455</v>
       </c>
       <c r="B59" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489390</v>
+        <v>489402</v>
       </c>
       <c r="R59" t="n">
-        <v>6949929</v>
+        <v>6949888</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7252,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7262,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7277,74 +6884,79 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119811596</v>
+        <v>119852338</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489598</v>
+        <v>489485</v>
       </c>
       <c r="R60" t="n">
-        <v>6950085</v>
+        <v>6950055</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7368,22 +6980,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7410,59 +7022,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119816681</v>
+        <v>130229400</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489415</v>
+        <v>489591</v>
       </c>
       <c r="R61" t="n">
-        <v>6949931</v>
+        <v>6950201</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7489,22 +7092,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7519,59 +7122,59 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119816566</v>
+        <v>119849865</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7580,10 +7183,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489390</v>
+        <v>489413</v>
       </c>
       <c r="R62" t="n">
-        <v>6949914</v>
+        <v>6949801</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7610,22 +7213,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7640,71 +7248,62 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119811398</v>
+        <v>119811924</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489626</v>
+        <v>489533</v>
       </c>
       <c r="R63" t="n">
-        <v>6950077</v>
+        <v>6950132</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7773,59 +7372,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119811058</v>
+        <v>121702304</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489643</v>
+        <v>489446</v>
       </c>
       <c r="R64" t="n">
-        <v>6950272</v>
+        <v>6949920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7852,22 +7442,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,62 +7472,66 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119815546</v>
+        <v>119810849</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489670</v>
+        <v>489644</v>
       </c>
       <c r="R65" t="n">
-        <v>6949842</v>
+        <v>6950252</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7969,7 +7563,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7979,7 +7573,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8006,50 +7600,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119815859</v>
+        <v>119810875</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489648</v>
+        <v>489650</v>
       </c>
       <c r="R66" t="n">
-        <v>6949845</v>
+        <v>6950248</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8081,7 +7679,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8091,7 +7689,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8106,76 +7704,66 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849865</v>
+        <v>119810961</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489413</v>
+        <v>489669</v>
       </c>
       <c r="R67" t="n">
-        <v>6949801</v>
+        <v>6950252</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8202,27 +7790,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Sång och observerad fågel</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8237,65 +7820,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849062</v>
+        <v>119811038</v>
       </c>
       <c r="B68" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489573</v>
+        <v>489668</v>
       </c>
       <c r="R68" t="n">
-        <v>6949724</v>
+        <v>6950267</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8319,22 +7897,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8349,65 +7927,69 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119848733</v>
+        <v>119811058</v>
       </c>
       <c r="B69" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489600</v>
+        <v>489643</v>
       </c>
       <c r="R69" t="n">
-        <v>6949713</v>
+        <v>6950272</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8431,22 +8013,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8461,65 +8043,69 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119851578</v>
+        <v>119811398</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489328</v>
+        <v>489626</v>
       </c>
       <c r="R70" t="n">
-        <v>6950055</v>
+        <v>6950077</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8543,22 +8129,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8573,62 +8159,66 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851248</v>
+        <v>119811596</v>
       </c>
       <c r="B71" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489366</v>
+        <v>489598</v>
       </c>
       <c r="R71" t="n">
-        <v>6949996</v>
+        <v>6950085</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8655,22 +8245,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8697,53 +8287,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119852071</v>
+        <v>119811826</v>
       </c>
       <c r="B72" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489392</v>
+        <v>489523</v>
       </c>
       <c r="R72" t="n">
-        <v>6950011</v>
+        <v>6950130</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8767,22 +8361,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8797,65 +8391,69 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119848365</v>
+        <v>119812008</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489632</v>
+        <v>489528</v>
       </c>
       <c r="R73" t="n">
-        <v>6949678</v>
+        <v>6950124</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8879,22 +8477,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8909,65 +8507,69 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850939</v>
+        <v>119812313</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489367</v>
+        <v>489527</v>
       </c>
       <c r="R74" t="n">
-        <v>6949918</v>
+        <v>6950174</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8991,22 +8593,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9021,65 +8623,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119848594</v>
+        <v>119812447</v>
       </c>
       <c r="B75" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489615</v>
+        <v>489521</v>
       </c>
       <c r="R75" t="n">
-        <v>6949709</v>
+        <v>6950157</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9103,22 +8709,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9133,65 +8739,69 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850649</v>
+        <v>119815902</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489406</v>
+        <v>489634</v>
       </c>
       <c r="R76" t="n">
-        <v>6949790</v>
+        <v>6949843</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9215,22 +8825,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9245,65 +8855,69 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119848818</v>
+        <v>119815982</v>
       </c>
       <c r="B77" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489593</v>
+        <v>489561</v>
       </c>
       <c r="R77" t="n">
-        <v>6949732</v>
+        <v>6949786</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9327,22 +8941,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9357,65 +8971,69 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119849489</v>
+        <v>119815992</v>
       </c>
       <c r="B78" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489516</v>
+        <v>489517</v>
       </c>
       <c r="R78" t="n">
-        <v>6949768</v>
+        <v>6949756</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9439,22 +9057,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9469,84 +9087,69 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119852338</v>
+        <v>119816036</v>
       </c>
       <c r="B79" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489485</v>
+        <v>489554</v>
       </c>
       <c r="R79" t="n">
-        <v>6950055</v>
+        <v>6949859</v>
       </c>
       <c r="S79" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9570,22 +9173,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9600,65 +9203,69 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119849171</v>
+        <v>119816402</v>
       </c>
       <c r="B80" t="n">
-        <v>79659</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489554</v>
+        <v>489410</v>
       </c>
       <c r="R80" t="n">
-        <v>6949730</v>
+        <v>6949906</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9682,22 +9289,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9712,65 +9319,69 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119848688</v>
+        <v>119816425</v>
       </c>
       <c r="B81" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489614</v>
+        <v>489432</v>
       </c>
       <c r="R81" t="n">
-        <v>6949692</v>
+        <v>6949876</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9794,22 +9405,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9824,62 +9435,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119851683</v>
+        <v>119816509</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489314</v>
+        <v>489392</v>
       </c>
       <c r="R82" t="n">
-        <v>6950058</v>
+        <v>6949873</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9906,22 +9521,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9948,53 +9563,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119852547</v>
+        <v>119816566</v>
       </c>
       <c r="B83" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489584</v>
+        <v>489390</v>
       </c>
       <c r="R83" t="n">
-        <v>6949881</v>
+        <v>6949914</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10018,22 +9637,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,65 +9667,69 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851194</v>
+        <v>119816681</v>
       </c>
       <c r="B84" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489391</v>
+        <v>489415</v>
       </c>
       <c r="R84" t="n">
-        <v>6949965</v>
+        <v>6949931</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10130,22 +9753,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10160,49 +9783,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119850950</v>
+        <v>119816869</v>
       </c>
       <c r="B85" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10212,13 +9830,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489367</v>
+        <v>489386</v>
       </c>
       <c r="R85" t="n">
-        <v>6949918</v>
+        <v>6950031</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10242,22 +9860,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10272,55 +9890,54 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121702304</v>
+        <v>119817114</v>
       </c>
       <c r="B86" t="n">
-        <v>55971</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10329,10 +9946,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489446</v>
+        <v>489487</v>
       </c>
       <c r="R86" t="n">
-        <v>6949920</v>
+        <v>6949865</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10359,22 +9976,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10389,60 +10006,54 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121702691</v>
+        <v>130228933</v>
       </c>
       <c r="B87" t="n">
-        <v>57369</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10451,13 +10062,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489502</v>
+        <v>489377</v>
       </c>
       <c r="R87" t="n">
-        <v>6949992</v>
+        <v>6949891</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10481,22 +10092,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10523,53 +10134,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124446830</v>
+        <v>130229051</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489575</v>
+        <v>489372</v>
       </c>
       <c r="R88" t="n">
-        <v>6950094</v>
+        <v>6949896</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10593,22 +10199,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10623,66 +10229,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130228933</v>
+        <v>119816597</v>
       </c>
       <c r="B89" t="n">
-        <v>98957</v>
+        <v>97983</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489377</v>
+        <v>489387</v>
       </c>
       <c r="R89" t="n">
-        <v>6949891</v>
+        <v>6949914</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10709,22 +10306,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10739,341 +10336,15 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>130229051</v>
-      </c>
-      <c r="B90" t="n">
-        <v>98957</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Kåren, Kåren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>489372</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6949896</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>130229400</v>
-      </c>
-      <c r="B91" t="n">
-        <v>57044</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Källmyren, Källmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>489591</v>
-      </c>
-      <c r="R91" t="n">
-        <v>6950201</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>130228419</v>
-      </c>
-      <c r="B92" t="n">
-        <v>92483</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>489596</v>
-      </c>
-      <c r="R92" t="n">
-        <v>6950061</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7134,10 +7134,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119849865</v>
+        <v>135342355</v>
       </c>
       <c r="B62" t="n">
-        <v>58327</v>
+        <v>57162</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7145,48 +7145,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489413</v>
+        <v>489807</v>
       </c>
       <c r="R62" t="n">
-        <v>6949801</v>
+        <v>6949428</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7213,27 +7199,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Sång och observerad fågel</t>
+          <t>Tjäderhöna med fem kycklingar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7248,62 +7234,71 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119811924</v>
+        <v>119849865</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489533</v>
+        <v>489413</v>
       </c>
       <c r="R63" t="n">
-        <v>6950132</v>
+        <v>6949801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7330,22 +7325,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7360,22 +7360,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121702304</v>
+        <v>119811924</v>
       </c>
       <c r="B64" t="n">
-        <v>56522</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7383,39 +7383,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489446</v>
+        <v>489533</v>
       </c>
       <c r="R64" t="n">
-        <v>6949920</v>
+        <v>6950132</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7442,22 +7442,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7472,69 +7472,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810849</v>
+        <v>121702304</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>56522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489644</v>
+        <v>489446</v>
       </c>
       <c r="R65" t="n">
-        <v>6950252</v>
+        <v>6949920</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7558,22 +7554,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7600,7 +7596,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810875</v>
+        <v>119810849</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7630,7 +7626,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7644,13 +7640,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489650</v>
+        <v>489644</v>
       </c>
       <c r="R66" t="n">
-        <v>6950248</v>
+        <v>6950252</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7679,7 +7675,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7689,7 +7685,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7704,19 +7700,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810961</v>
+        <v>119810875</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7746,7 +7742,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7760,10 +7756,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489669</v>
+        <v>489650</v>
       </c>
       <c r="R67" t="n">
-        <v>6950252</v>
+        <v>6950248</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7828,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119811038</v>
+        <v>119810961</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7860,17 +7856,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489668</v>
+        <v>489669</v>
       </c>
       <c r="R68" t="n">
-        <v>6950267</v>
+        <v>6950252</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7902,7 +7907,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7912,7 +7917,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7927,19 +7932,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119811058</v>
+        <v>119811038</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7967,26 +7972,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489643</v>
+        <v>489668</v>
       </c>
       <c r="R69" t="n">
-        <v>6950272</v>
+        <v>6950267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8018,7 +8014,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8028,7 +8024,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8043,19 +8039,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119811398</v>
+        <v>119811058</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8085,7 +8081,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8095,14 +8091,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489626</v>
+        <v>489643</v>
       </c>
       <c r="R70" t="n">
-        <v>6950077</v>
+        <v>6950272</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8171,7 +8167,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119811596</v>
+        <v>119811398</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8201,7 +8197,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8215,13 +8211,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489598</v>
+        <v>489626</v>
       </c>
       <c r="R71" t="n">
-        <v>6950085</v>
+        <v>6950077</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8250,7 +8246,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8260,7 +8256,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8275,19 +8271,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119811826</v>
+        <v>119811596</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8317,7 +8313,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8327,17 +8323,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489523</v>
+        <v>489598</v>
       </c>
       <c r="R72" t="n">
-        <v>6950130</v>
+        <v>6950085</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8366,7 +8362,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8376,7 +8372,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8391,19 +8387,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119812008</v>
+        <v>119811826</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8433,7 +8429,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8447,10 +8443,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489528</v>
+        <v>489523</v>
       </c>
       <c r="R73" t="n">
-        <v>6950124</v>
+        <v>6950130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8519,7 +8515,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119812313</v>
+        <v>119812008</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8549,7 +8545,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8563,10 +8559,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489527</v>
+        <v>489528</v>
       </c>
       <c r="R74" t="n">
-        <v>6950174</v>
+        <v>6950124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8635,7 +8631,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119812447</v>
+        <v>119812313</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8665,7 +8661,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8679,10 +8675,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489521</v>
+        <v>489527</v>
       </c>
       <c r="R75" t="n">
-        <v>6950157</v>
+        <v>6950174</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8751,7 +8747,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119815902</v>
+        <v>119812447</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8781,7 +8777,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8791,14 +8787,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489634</v>
+        <v>489521</v>
       </c>
       <c r="R76" t="n">
-        <v>6949843</v>
+        <v>6950157</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8867,7 +8863,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119815982</v>
+        <v>119815902</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8897,7 +8893,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8907,14 +8903,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489561</v>
+        <v>489634</v>
       </c>
       <c r="R77" t="n">
-        <v>6949786</v>
+        <v>6949843</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8983,7 +8979,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119815992</v>
+        <v>119815982</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -9013,7 +9009,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9027,10 +9023,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489517</v>
+        <v>489561</v>
       </c>
       <c r="R78" t="n">
-        <v>6949756</v>
+        <v>6949786</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9095,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119816036</v>
+        <v>119815992</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9129,7 +9125,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9139,14 +9135,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489554</v>
+        <v>489517</v>
       </c>
       <c r="R79" t="n">
-        <v>6949859</v>
+        <v>6949756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9215,7 +9211,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119816402</v>
+        <v>119816036</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9245,7 +9241,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9255,14 +9251,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489410</v>
+        <v>489554</v>
       </c>
       <c r="R80" t="n">
-        <v>6949906</v>
+        <v>6949859</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9331,7 +9327,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119816425</v>
+        <v>119816402</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9361,7 +9357,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9375,10 +9371,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489432</v>
+        <v>489410</v>
       </c>
       <c r="R81" t="n">
-        <v>6949876</v>
+        <v>6949906</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9447,7 +9443,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119816509</v>
+        <v>119816425</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9477,7 +9473,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9491,13 +9487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489392</v>
+        <v>489432</v>
       </c>
       <c r="R82" t="n">
-        <v>6949873</v>
+        <v>6949876</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9526,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9536,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9551,19 +9547,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119816566</v>
+        <v>119816509</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9593,7 +9589,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9607,13 +9603,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489390</v>
+        <v>489392</v>
       </c>
       <c r="R83" t="n">
-        <v>6949914</v>
+        <v>6949873</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9642,7 +9638,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9652,7 +9648,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9667,19 +9663,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119816681</v>
+        <v>119816566</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9723,10 +9719,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489415</v>
+        <v>489390</v>
       </c>
       <c r="R84" t="n">
-        <v>6949931</v>
+        <v>6949914</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9795,7 +9791,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119816869</v>
+        <v>119816681</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9823,17 +9819,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489386</v>
+        <v>489415</v>
       </c>
       <c r="R85" t="n">
-        <v>6950031</v>
+        <v>6949931</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9865,7 +9870,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9875,7 +9880,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9890,19 +9895,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119817114</v>
+        <v>119816869</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9930,26 +9935,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489487</v>
+        <v>489386</v>
       </c>
       <c r="R86" t="n">
-        <v>6949865</v>
+        <v>6950031</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9981,7 +9977,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9991,7 +9987,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10006,19 +10002,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130228933</v>
+        <v>119817114</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10048,7 +10044,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10062,10 +10058,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489377</v>
+        <v>489487</v>
       </c>
       <c r="R87" t="n">
-        <v>6949891</v>
+        <v>6949865</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10092,22 +10088,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10122,19 +10118,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10162,17 +10158,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R88" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10204,7 +10209,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10214,7 +10219,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10241,32 +10246,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119816597</v>
+        <v>130229051</v>
       </c>
       <c r="B89" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10276,10 +10281,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489387</v>
+        <v>489372</v>
       </c>
       <c r="R89" t="n">
-        <v>6949914</v>
+        <v>6949896</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10306,22 +10311,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10336,15 +10341,122 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>119816597</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>489387</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6949914</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
           <t>Marielle Löthman</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
+      <c r="AX90" t="inlineStr">
         <is>
           <t>Marielle Löthman</t>
         </is>
       </c>
-      <c r="AY89" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812106</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811422</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811103</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811346</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811561</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812085</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813032</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848818</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816403</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849489</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850950</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851194</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851248</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852071</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228419</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816157</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566267</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815905</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566902</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119244889</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815546</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815720</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815859</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816272</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816291</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816293</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816490</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816571</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816697</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119817871</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819157</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848365</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850649</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850939</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851683</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816409</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819067</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848594</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848688</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849062</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852547</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119817062</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5584,6 +5814,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115598923</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5691,6 +5926,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119245053</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5798,6 +6038,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813023</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5905,6 +6150,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851578</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6012,6 +6262,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119818590</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6119,6 +6374,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849171</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6226,6 +6486,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115599985</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6338,6 +6603,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811101</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811744</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6552,6 +6827,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115597799</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812494</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6781,6 +7066,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121702691</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6893,6 +7183,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816455</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7019,6 +7314,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852338</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7131,6 +7431,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229400</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7243,6 +7548,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342355</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7369,6 +7679,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849865</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7481,6 +7796,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811924</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7593,6 +7913,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121702304</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7709,6 +8034,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810849</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7825,6 +8155,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810875</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7941,6 +8276,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810961</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8048,6 +8388,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811038</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8164,6 +8509,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811058</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8280,6 +8630,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811398</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8396,6 +8751,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811596</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8512,6 +8872,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119811826</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8628,6 +8993,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812008</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8744,6 +9114,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812313</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8860,6 +9235,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119812447</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8976,6 +9356,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815902</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9092,6 +9477,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815982</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9208,6 +9598,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815992</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9324,6 +9719,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816036</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9440,6 +9840,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816402</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9556,6 +9961,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816425</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9672,6 +10082,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816509</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9788,6 +10203,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816566</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9904,6 +10324,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816681</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10011,6 +10436,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816869</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10127,6 +10557,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119817114</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10243,6 +10678,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228933</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10350,6 +10790,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229051</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10457,8 +10902,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119816597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
         <v>135342355</v>
       </c>
       <c r="B62" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ89"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7439,10 +7439,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119849865</v>
+        <v>135342355</v>
       </c>
       <c r="B62" t="n">
-        <v>58327</v>
+        <v>57167</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7450,48 +7450,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarptjärnen, Åsvarptjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489413</v>
+        <v>489807</v>
       </c>
       <c r="R62" t="n">
-        <v>6949801</v>
+        <v>6949428</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7518,27 +7504,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Sång och observerad fågel</t>
+          <t>Tjäderhöna med fem kycklingar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7553,67 +7539,76 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119849865</t>
+          <t>https://artportalen.se/Sighting/135342355</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119811924</v>
+        <v>119849865</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>489533</v>
+        <v>489413</v>
       </c>
       <c r="R63" t="n">
-        <v>6950132</v>
+        <v>6949801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7640,22 +7635,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Sång och observerad fågel</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7670,27 +7670,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811924</t>
+          <t>https://artportalen.se/Sighting/119849865</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121702304</v>
+        <v>119811924</v>
       </c>
       <c r="B64" t="n">
-        <v>56522</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7698,39 +7698,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>489446</v>
+        <v>489533</v>
       </c>
       <c r="R64" t="n">
-        <v>6949920</v>
+        <v>6950132</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7757,22 +7757,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7787,74 +7787,70 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121702304</t>
+          <t>https://artportalen.se/Sighting/119811924</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810849</v>
+        <v>121702304</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>56522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489644</v>
+        <v>489446</v>
       </c>
       <c r="R65" t="n">
-        <v>6950252</v>
+        <v>6949920</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7878,22 +7874,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,13 +7915,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810849</t>
+          <t>https://artportalen.se/Sighting/121702304</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810875</v>
+        <v>119810849</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7955,7 +7951,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7969,13 +7965,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489650</v>
+        <v>489644</v>
       </c>
       <c r="R66" t="n">
-        <v>6950248</v>
+        <v>6950252</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8004,7 +8000,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8014,7 +8010,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8029,24 +8025,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810875</t>
+          <t>https://artportalen.se/Sighting/119810849</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810961</v>
+        <v>119810875</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8076,7 +8072,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8090,10 +8086,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489669</v>
+        <v>489650</v>
       </c>
       <c r="R67" t="n">
-        <v>6950252</v>
+        <v>6950248</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8161,13 +8157,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810961</t>
+          <t>https://artportalen.se/Sighting/119810875</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119811038</v>
+        <v>119810961</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8195,17 +8191,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489668</v>
+        <v>489669</v>
       </c>
       <c r="R68" t="n">
-        <v>6950267</v>
+        <v>6950252</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8237,7 +8242,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8247,7 +8252,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8262,24 +8267,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811038</t>
+          <t>https://artportalen.se/Sighting/119810961</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119811058</v>
+        <v>119811038</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8307,26 +8312,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489643</v>
+        <v>489668</v>
       </c>
       <c r="R69" t="n">
-        <v>6950272</v>
+        <v>6950267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8358,7 +8354,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8368,7 +8364,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8383,24 +8379,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811058</t>
+          <t>https://artportalen.se/Sighting/119811038</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119811398</v>
+        <v>119811058</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8430,7 +8426,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8440,14 +8436,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489626</v>
+        <v>489643</v>
       </c>
       <c r="R70" t="n">
-        <v>6950077</v>
+        <v>6950272</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8515,13 +8511,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811398</t>
+          <t>https://artportalen.se/Sighting/119811058</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119811596</v>
+        <v>119811398</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8551,7 +8547,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8565,13 +8561,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489598</v>
+        <v>489626</v>
       </c>
       <c r="R71" t="n">
-        <v>6950085</v>
+        <v>6950077</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8600,7 +8596,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8610,7 +8606,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8625,24 +8621,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811596</t>
+          <t>https://artportalen.se/Sighting/119811398</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119811826</v>
+        <v>119811596</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8672,7 +8668,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8682,17 +8678,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489523</v>
+        <v>489598</v>
       </c>
       <c r="R72" t="n">
-        <v>6950130</v>
+        <v>6950085</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8721,7 +8717,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8731,7 +8727,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,24 +8742,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811826</t>
+          <t>https://artportalen.se/Sighting/119811596</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119812008</v>
+        <v>119811826</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8793,7 +8789,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8807,10 +8803,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489528</v>
+        <v>489523</v>
       </c>
       <c r="R73" t="n">
-        <v>6950124</v>
+        <v>6950130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8878,13 +8874,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812008</t>
+          <t>https://artportalen.se/Sighting/119811826</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119812313</v>
+        <v>119812008</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8914,7 +8910,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8928,10 +8924,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489527</v>
+        <v>489528</v>
       </c>
       <c r="R74" t="n">
-        <v>6950174</v>
+        <v>6950124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8999,13 +8995,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812313</t>
+          <t>https://artportalen.se/Sighting/119812008</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119812447</v>
+        <v>119812313</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -9035,7 +9031,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9049,10 +9045,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489521</v>
+        <v>489527</v>
       </c>
       <c r="R75" t="n">
-        <v>6950157</v>
+        <v>6950174</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9120,13 +9116,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812447</t>
+          <t>https://artportalen.se/Sighting/119812313</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119815902</v>
+        <v>119812447</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -9156,7 +9152,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9166,14 +9162,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489634</v>
+        <v>489521</v>
       </c>
       <c r="R76" t="n">
-        <v>6949843</v>
+        <v>6950157</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9241,13 +9237,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815902</t>
+          <t>https://artportalen.se/Sighting/119812447</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119815982</v>
+        <v>119815902</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -9277,7 +9273,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9287,14 +9283,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489561</v>
+        <v>489634</v>
       </c>
       <c r="R77" t="n">
-        <v>6949786</v>
+        <v>6949843</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9362,13 +9358,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815982</t>
+          <t>https://artportalen.se/Sighting/119815902</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119815992</v>
+        <v>119815982</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -9398,7 +9394,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9412,10 +9408,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489517</v>
+        <v>489561</v>
       </c>
       <c r="R78" t="n">
-        <v>6949756</v>
+        <v>6949786</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9483,13 +9479,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815992</t>
+          <t>https://artportalen.se/Sighting/119815982</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119816036</v>
+        <v>119815992</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9519,7 +9515,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9529,14 +9525,14 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489554</v>
+        <v>489517</v>
       </c>
       <c r="R79" t="n">
-        <v>6949859</v>
+        <v>6949756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9604,13 +9600,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816036</t>
+          <t>https://artportalen.se/Sighting/119815992</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119816402</v>
+        <v>119816036</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9640,7 +9636,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9650,14 +9646,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489410</v>
+        <v>489554</v>
       </c>
       <c r="R80" t="n">
-        <v>6949906</v>
+        <v>6949859</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9725,13 +9721,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816402</t>
+          <t>https://artportalen.se/Sighting/119816036</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119816425</v>
+        <v>119816402</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9761,7 +9757,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9775,10 +9771,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489432</v>
+        <v>489410</v>
       </c>
       <c r="R81" t="n">
-        <v>6949876</v>
+        <v>6949906</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9846,13 +9842,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816425</t>
+          <t>https://artportalen.se/Sighting/119816402</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119816509</v>
+        <v>119816425</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9882,7 +9878,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9896,13 +9892,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489392</v>
+        <v>489432</v>
       </c>
       <c r="R82" t="n">
-        <v>6949873</v>
+        <v>6949876</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9931,7 +9927,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9941,7 +9937,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9956,24 +9952,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816509</t>
+          <t>https://artportalen.se/Sighting/119816425</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119816566</v>
+        <v>119816509</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10003,7 +9999,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10017,13 +10013,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489390</v>
+        <v>489392</v>
       </c>
       <c r="R83" t="n">
-        <v>6949914</v>
+        <v>6949873</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10052,7 +10048,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10062,7 +10058,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10077,24 +10073,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816566</t>
+          <t>https://artportalen.se/Sighting/119816509</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119816681</v>
+        <v>119816566</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -10138,10 +10134,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489415</v>
+        <v>489390</v>
       </c>
       <c r="R84" t="n">
-        <v>6949931</v>
+        <v>6949914</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10209,13 +10205,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816681</t>
+          <t>https://artportalen.se/Sighting/119816566</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119816869</v>
+        <v>119816681</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -10243,17 +10239,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489386</v>
+        <v>489415</v>
       </c>
       <c r="R85" t="n">
-        <v>6950031</v>
+        <v>6949931</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10285,7 +10290,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10295,7 +10300,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10310,24 +10315,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816869</t>
+          <t>https://artportalen.se/Sighting/119816681</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119817114</v>
+        <v>119816869</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10355,26 +10360,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489487</v>
+        <v>489386</v>
       </c>
       <c r="R86" t="n">
-        <v>6949865</v>
+        <v>6950031</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10406,7 +10402,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10416,7 +10412,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10431,24 +10427,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119817114</t>
+          <t>https://artportalen.se/Sighting/119816869</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130228933</v>
+        <v>119817114</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10478,7 +10474,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10492,10 +10488,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489377</v>
+        <v>489487</v>
       </c>
       <c r="R87" t="n">
-        <v>6949891</v>
+        <v>6949865</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10522,22 +10518,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10552,24 +10548,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130228933</t>
+          <t>https://artportalen.se/Sighting/119817114</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10597,17 +10593,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R88" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10639,7 +10644,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10649,7 +10654,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10675,38 +10680,38 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130229051</t>
+          <t>https://artportalen.se/Sighting/130228933</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119816597</v>
+        <v>130229051</v>
       </c>
       <c r="B89" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10716,10 +10721,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489387</v>
+        <v>489372</v>
       </c>
       <c r="R89" t="n">
-        <v>6949914</v>
+        <v>6949896</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10746,22 +10751,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10776,16 +10781,128 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229051</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>119816597</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>489387</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6949914</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119816597</t>
         </is>
@@ -10881,6 +10998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ90"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7804,50 +7804,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121702304</v>
+        <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>56522</v>
+        <v>58138</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>489446</v>
+        <v>489664</v>
       </c>
       <c r="R65" t="n">
-        <v>6949920</v>
+        <v>6949620</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7874,22 +7869,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7915,63 +7900,59 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121702304</t>
+          <t>https://artportalen.se/Sighting/136237597</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810849</v>
+        <v>121702304</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>56522</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>489644</v>
+        <v>489446</v>
       </c>
       <c r="R66" t="n">
-        <v>6950252</v>
+        <v>6949920</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7995,22 +7976,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8036,13 +8017,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810849</t>
+          <t>https://artportalen.se/Sighting/121702304</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810875</v>
+        <v>119810849</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8072,7 +8053,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8086,13 +8067,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489650</v>
+        <v>489644</v>
       </c>
       <c r="R67" t="n">
-        <v>6950248</v>
+        <v>6950252</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8121,7 +8102,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8131,7 +8112,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8146,24 +8127,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810875</t>
+          <t>https://artportalen.se/Sighting/119810849</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810961</v>
+        <v>119810875</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8193,7 +8174,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8207,10 +8188,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489669</v>
+        <v>489650</v>
       </c>
       <c r="R68" t="n">
-        <v>6950252</v>
+        <v>6950248</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8278,13 +8259,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119810961</t>
+          <t>https://artportalen.se/Sighting/119810875</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119811038</v>
+        <v>119810961</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8312,17 +8293,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489668</v>
+        <v>489669</v>
       </c>
       <c r="R69" t="n">
-        <v>6950267</v>
+        <v>6950252</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8354,7 +8344,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8364,7 +8354,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8379,24 +8369,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811038</t>
+          <t>https://artportalen.se/Sighting/119810961</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119811058</v>
+        <v>119811038</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8424,26 +8414,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489643</v>
+        <v>489668</v>
       </c>
       <c r="R70" t="n">
-        <v>6950272</v>
+        <v>6950267</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8475,7 +8456,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8485,7 +8466,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8500,24 +8481,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811058</t>
+          <t>https://artportalen.se/Sighting/119811038</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119811398</v>
+        <v>119811058</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8547,7 +8528,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8557,14 +8538,14 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489626</v>
+        <v>489643</v>
       </c>
       <c r="R71" t="n">
-        <v>6950077</v>
+        <v>6950272</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8632,13 +8613,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811398</t>
+          <t>https://artportalen.se/Sighting/119811058</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119811596</v>
+        <v>119811398</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8668,7 +8649,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8682,13 +8663,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489598</v>
+        <v>489626</v>
       </c>
       <c r="R72" t="n">
-        <v>6950085</v>
+        <v>6950077</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8717,7 +8698,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8727,7 +8708,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,24 +8723,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811596</t>
+          <t>https://artportalen.se/Sighting/119811398</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119811826</v>
+        <v>119811596</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8789,7 +8770,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8799,17 +8780,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Källmyren, Källmyren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489523</v>
+        <v>489598</v>
       </c>
       <c r="R73" t="n">
-        <v>6950130</v>
+        <v>6950085</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8838,7 +8819,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8848,7 +8829,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8863,24 +8844,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119811826</t>
+          <t>https://artportalen.se/Sighting/119811596</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119812008</v>
+        <v>119811826</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8910,7 +8891,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8924,10 +8905,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489528</v>
+        <v>489523</v>
       </c>
       <c r="R74" t="n">
-        <v>6950124</v>
+        <v>6950130</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8995,13 +8976,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812008</t>
+          <t>https://artportalen.se/Sighting/119811826</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119812313</v>
+        <v>119812008</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -9031,7 +9012,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9045,10 +9026,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>489527</v>
+        <v>489528</v>
       </c>
       <c r="R75" t="n">
-        <v>6950174</v>
+        <v>6950124</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9116,13 +9097,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812313</t>
+          <t>https://artportalen.se/Sighting/119812008</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119812447</v>
+        <v>119812313</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -9152,7 +9133,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9166,10 +9147,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489521</v>
+        <v>489527</v>
       </c>
       <c r="R76" t="n">
-        <v>6950157</v>
+        <v>6950174</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9237,13 +9218,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119812447</t>
+          <t>https://artportalen.se/Sighting/119812313</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119815902</v>
+        <v>119812447</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -9273,7 +9254,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9283,14 +9264,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Källmyren, Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489634</v>
+        <v>489521</v>
       </c>
       <c r="R77" t="n">
-        <v>6949843</v>
+        <v>6950157</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9358,13 +9339,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815902</t>
+          <t>https://artportalen.se/Sighting/119812447</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119815982</v>
+        <v>119815902</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -9394,7 +9375,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9404,14 +9385,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åsvarpet, Åsvarpet, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489561</v>
+        <v>489634</v>
       </c>
       <c r="R78" t="n">
-        <v>6949786</v>
+        <v>6949843</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9479,13 +9460,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815982</t>
+          <t>https://artportalen.se/Sighting/119815902</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119815992</v>
+        <v>119815982</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9515,7 +9496,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9529,10 +9510,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489517</v>
+        <v>489561</v>
       </c>
       <c r="R79" t="n">
-        <v>6949756</v>
+        <v>6949786</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9600,13 +9581,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119815992</t>
+          <t>https://artportalen.se/Sighting/119815982</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119816036</v>
+        <v>119815992</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9636,7 +9617,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9646,14 +9627,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
+          <t>Åsvarpet, Åsvarpet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489554</v>
+        <v>489517</v>
       </c>
       <c r="R80" t="n">
-        <v>6949859</v>
+        <v>6949756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9721,13 +9702,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816036</t>
+          <t>https://artportalen.se/Sighting/119815992</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119816402</v>
+        <v>119816036</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9757,7 +9738,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9767,14 +9748,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kåren, Kåren, Jmt</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489410</v>
+        <v>489554</v>
       </c>
       <c r="R81" t="n">
-        <v>6949906</v>
+        <v>6949859</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9842,13 +9823,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816402</t>
+          <t>https://artportalen.se/Sighting/119816036</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119816425</v>
+        <v>119816402</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9878,7 +9859,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9892,10 +9873,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489432</v>
+        <v>489410</v>
       </c>
       <c r="R82" t="n">
-        <v>6949876</v>
+        <v>6949906</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9963,13 +9944,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816425</t>
+          <t>https://artportalen.se/Sighting/119816402</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119816509</v>
+        <v>119816425</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9999,7 +9980,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10013,13 +9994,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489392</v>
+        <v>489432</v>
       </c>
       <c r="R83" t="n">
-        <v>6949873</v>
+        <v>6949876</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10048,7 +10029,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10058,7 +10039,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10073,24 +10054,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816509</t>
+          <t>https://artportalen.se/Sighting/119816425</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119816566</v>
+        <v>119816509</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -10120,7 +10101,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10134,13 +10115,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489390</v>
+        <v>489392</v>
       </c>
       <c r="R84" t="n">
-        <v>6949914</v>
+        <v>6949873</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10169,7 +10150,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10179,7 +10160,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10194,24 +10175,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816566</t>
+          <t>https://artportalen.se/Sighting/119816509</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119816681</v>
+        <v>119816566</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -10255,10 +10236,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489415</v>
+        <v>489390</v>
       </c>
       <c r="R85" t="n">
-        <v>6949931</v>
+        <v>6949914</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10326,13 +10307,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816681</t>
+          <t>https://artportalen.se/Sighting/119816566</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119816869</v>
+        <v>119816681</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10360,17 +10341,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489386</v>
+        <v>489415</v>
       </c>
       <c r="R86" t="n">
-        <v>6950031</v>
+        <v>6949931</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10402,7 +10392,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10412,7 +10402,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10427,24 +10417,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119816869</t>
+          <t>https://artportalen.se/Sighting/119816681</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119817114</v>
+        <v>119816869</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10472,26 +10462,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489487</v>
+        <v>489386</v>
       </c>
       <c r="R87" t="n">
-        <v>6949865</v>
+        <v>6950031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10523,7 +10504,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10533,7 +10514,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10548,24 +10529,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119817114</t>
+          <t>https://artportalen.se/Sighting/119816869</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130228933</v>
+        <v>119817114</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10595,7 +10576,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10609,10 +10590,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489377</v>
+        <v>489487</v>
       </c>
       <c r="R88" t="n">
-        <v>6949891</v>
+        <v>6949865</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10639,22 +10620,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10669,24 +10650,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130228933</t>
+          <t>https://artportalen.se/Sighting/119817114</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130229051</v>
+        <v>130228933</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10714,17 +10695,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåren, Kåren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489372</v>
+        <v>489377</v>
       </c>
       <c r="R89" t="n">
-        <v>6949896</v>
+        <v>6949891</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10756,7 +10746,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10766,7 +10756,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10792,38 +10782,38 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130229051</t>
+          <t>https://artportalen.se/Sighting/130228933</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119816597</v>
+        <v>130229051</v>
       </c>
       <c r="B90" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10833,10 +10823,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489387</v>
+        <v>489372</v>
       </c>
       <c r="R90" t="n">
-        <v>6949914</v>
+        <v>6949896</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10863,22 +10853,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10893,16 +10883,128 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130229051</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>119816597</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kåren, Kåren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>489387</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6949914</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119816597</t>
         </is>
@@ -10999,6 +11101,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
